--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -8431,8 +8431,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:H868" totalsRowShown="0">
-  <x:autoFilter ref="A1:H868"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:H869" totalsRowShown="0">
+  <x:autoFilter ref="A1:H869"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -8815,7 +8815,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:H868"/>
+  <x:dimension ref="A1:H869"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="9" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -29969,10 +29969,10 @@
     </x:row>
     <x:row r="814" spans="1:8">
       <x:c r="A814" s="1" t="s">
-        <x:v>292</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B814" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C814" s="1" t="s">
         <x:v>1808</x:v>
@@ -29995,25 +29995,25 @@
     </x:row>
     <x:row r="815" spans="1:8">
       <x:c r="A815" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B815" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="C815" s="1" t="s">
-        <x:v>1811</x:v>
+        <x:v>1808</x:v>
       </x:c>
       <x:c r="D815" s="1" t="s">
-        <x:v>1812</x:v>
+        <x:v>1809</x:v>
       </x:c>
       <x:c r="E815" s="1" t="s">
-        <x:v>1813</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="F815" s="1" t="s">
-        <x:v>876</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="G815" s="1">
-        <x:v>1500</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="H815" s="1" t="s">
         <x:v>14</x:v>
@@ -30021,10 +30021,10 @@
     </x:row>
     <x:row r="816" spans="1:8">
       <x:c r="A816" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B816" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C816" s="1" t="s">
         <x:v>1811</x:v>
@@ -30039,7 +30039,7 @@
         <x:v>876</x:v>
       </x:c>
       <x:c r="G816" s="1">
-        <x:v>2500</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="H816" s="1" t="s">
         <x:v>14</x:v>
@@ -30047,25 +30047,25 @@
     </x:row>
     <x:row r="817" spans="1:8">
       <x:c r="A817" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B817" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C817" s="1" t="s">
-        <x:v>1814</x:v>
+        <x:v>1811</x:v>
       </x:c>
       <x:c r="D817" s="1" t="s">
-        <x:v>1815</x:v>
+        <x:v>1812</x:v>
       </x:c>
       <x:c r="E817" s="1" t="s">
-        <x:v>1816</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="F817" s="1" t="s">
-        <x:v>170</x:v>
+        <x:v>876</x:v>
       </x:c>
       <x:c r="G817" s="1">
-        <x:v>1000</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="H817" s="1" t="s">
         <x:v>14</x:v>
@@ -30073,28 +30073,28 @@
     </x:row>
     <x:row r="818" spans="1:8">
       <x:c r="A818" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B818" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C818" s="1" t="s">
-        <x:v>1817</x:v>
+        <x:v>1814</x:v>
       </x:c>
       <x:c r="D818" s="1" t="s">
-        <x:v>1818</x:v>
+        <x:v>1815</x:v>
       </x:c>
       <x:c r="E818" s="1" t="s">
-        <x:v>1819</x:v>
+        <x:v>1816</x:v>
       </x:c>
       <x:c r="F818" s="1" t="s">
-        <x:v>313</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="G818" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="H818" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="819" spans="1:8">
@@ -30105,16 +30105,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C819" s="1" t="s">
-        <x:v>1820</x:v>
+        <x:v>1817</x:v>
       </x:c>
       <x:c r="D819" s="1" t="s">
-        <x:v>1821</x:v>
+        <x:v>1818</x:v>
       </x:c>
       <x:c r="E819" s="1" t="s">
-        <x:v>1822</x:v>
+        <x:v>1819</x:v>
       </x:c>
       <x:c r="F819" s="1" t="s">
-        <x:v>516</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="G819" s="1">
         <x:v>50</x:v>
@@ -30131,16 +30131,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C820" s="1" t="s">
-        <x:v>1823</x:v>
+        <x:v>1820</x:v>
       </x:c>
       <x:c r="D820" s="1" t="s">
-        <x:v>1824</x:v>
+        <x:v>1821</x:v>
       </x:c>
       <x:c r="E820" s="1" t="s">
-        <x:v>1825</x:v>
+        <x:v>1822</x:v>
       </x:c>
       <x:c r="F820" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="G820" s="1">
         <x:v>50</x:v>
@@ -30157,16 +30157,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C821" s="1" t="s">
-        <x:v>1826</x:v>
+        <x:v>1823</x:v>
       </x:c>
       <x:c r="D821" s="1" t="s">
-        <x:v>1827</x:v>
+        <x:v>1824</x:v>
       </x:c>
       <x:c r="E821" s="1" t="s">
-        <x:v>1828</x:v>
+        <x:v>1825</x:v>
       </x:c>
       <x:c r="F821" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="G821" s="1">
         <x:v>50</x:v>
@@ -30183,16 +30183,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C822" s="1" t="s">
-        <x:v>1829</x:v>
+        <x:v>1826</x:v>
       </x:c>
       <x:c r="D822" s="1" t="s">
-        <x:v>1830</x:v>
+        <x:v>1827</x:v>
       </x:c>
       <x:c r="E822" s="1" t="s">
-        <x:v>1831</x:v>
+        <x:v>1828</x:v>
       </x:c>
       <x:c r="F822" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G822" s="1">
         <x:v>50</x:v>
@@ -30209,16 +30209,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C823" s="1" t="s">
-        <x:v>1832</x:v>
+        <x:v>1829</x:v>
       </x:c>
       <x:c r="D823" s="1" t="s">
-        <x:v>1833</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="E823" s="1" t="s">
-        <x:v>1834</x:v>
+        <x:v>1831</x:v>
       </x:c>
       <x:c r="F823" s="1" t="s">
-        <x:v>203</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G823" s="1">
         <x:v>50</x:v>
@@ -30235,16 +30235,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C824" s="1" t="s">
-        <x:v>1835</x:v>
+        <x:v>1832</x:v>
       </x:c>
       <x:c r="D824" s="1" t="s">
-        <x:v>1836</x:v>
+        <x:v>1833</x:v>
       </x:c>
       <x:c r="E824" s="1" t="s">
-        <x:v>1837</x:v>
+        <x:v>1834</x:v>
       </x:c>
       <x:c r="F824" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="G824" s="1">
         <x:v>50</x:v>
@@ -30261,16 +30261,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C825" s="1" t="s">
-        <x:v>1838</x:v>
+        <x:v>1835</x:v>
       </x:c>
       <x:c r="D825" s="1" t="s">
-        <x:v>1839</x:v>
+        <x:v>1836</x:v>
       </x:c>
       <x:c r="E825" s="1" t="s">
-        <x:v>1840</x:v>
+        <x:v>1837</x:v>
       </x:c>
       <x:c r="F825" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G825" s="1">
         <x:v>50</x:v>
@@ -30287,13 +30287,13 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C826" s="1" t="s">
-        <x:v>1841</x:v>
+        <x:v>1838</x:v>
       </x:c>
       <x:c r="D826" s="1" t="s">
-        <x:v>1842</x:v>
+        <x:v>1839</x:v>
       </x:c>
       <x:c r="E826" s="1" t="s">
-        <x:v>1843</x:v>
+        <x:v>1840</x:v>
       </x:c>
       <x:c r="F826" s="1" t="s">
         <x:v>47</x:v>
@@ -30313,16 +30313,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C827" s="1" t="s">
-        <x:v>1844</x:v>
+        <x:v>1841</x:v>
       </x:c>
       <x:c r="D827" s="1" t="s">
-        <x:v>1845</x:v>
+        <x:v>1842</x:v>
       </x:c>
       <x:c r="E827" s="1" t="s">
-        <x:v>1846</x:v>
+        <x:v>1843</x:v>
       </x:c>
       <x:c r="F827" s="1" t="s">
-        <x:v>203</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G827" s="1">
         <x:v>50</x:v>
@@ -30339,13 +30339,13 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C828" s="1" t="s">
-        <x:v>1847</x:v>
+        <x:v>1844</x:v>
       </x:c>
       <x:c r="D828" s="1" t="s">
-        <x:v>1848</x:v>
+        <x:v>1845</x:v>
       </x:c>
       <x:c r="E828" s="1" t="s">
-        <x:v>1849</x:v>
+        <x:v>1846</x:v>
       </x:c>
       <x:c r="F828" s="1" t="s">
         <x:v>203</x:v>
@@ -30359,10 +30359,10 @@
     </x:row>
     <x:row r="829" spans="1:8">
       <x:c r="A829" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B829" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C829" s="1" t="s">
         <x:v>1847</x:v>
@@ -30377,18 +30377,18 @@
         <x:v>203</x:v>
       </x:c>
       <x:c r="G829" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H829" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="830" spans="1:8">
       <x:c r="A830" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B830" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C830" s="1" t="s">
         <x:v>1847</x:v>
@@ -30403,18 +30403,18 @@
         <x:v>203</x:v>
       </x:c>
       <x:c r="G830" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="H830" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="831" spans="1:8">
       <x:c r="A831" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B831" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C831" s="1" t="s">
         <x:v>1847</x:v>
@@ -30437,62 +30437,62 @@
     </x:row>
     <x:row r="832" spans="1:8">
       <x:c r="A832" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B832" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C832" s="1" t="s">
-        <x:v>1850</x:v>
+        <x:v>1847</x:v>
       </x:c>
       <x:c r="D832" s="1" t="s">
-        <x:v>1851</x:v>
+        <x:v>1848</x:v>
       </x:c>
       <x:c r="E832" s="1" t="s">
-        <x:v>1852</x:v>
+        <x:v>1849</x:v>
       </x:c>
       <x:c r="F832" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="G832" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="H832" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="833" spans="1:8">
       <x:c r="A833" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B833" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C833" s="1" t="s">
-        <x:v>1853</x:v>
+        <x:v>1850</x:v>
       </x:c>
       <x:c r="D833" s="1" t="s">
-        <x:v>1854</x:v>
+        <x:v>1851</x:v>
       </x:c>
       <x:c r="E833" s="1" t="s">
-        <x:v>1855</x:v>
+        <x:v>1852</x:v>
       </x:c>
       <x:c r="F833" s="1" t="s">
-        <x:v>183</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="G833" s="1">
-        <x:v>2500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H833" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="834" spans="1:8">
       <x:c r="A834" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B834" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C834" s="1" t="s">
         <x:v>1853</x:v>
@@ -30507,7 +30507,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="G834" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="H834" s="1" t="s">
         <x:v>14</x:v>
@@ -30515,28 +30515,28 @@
     </x:row>
     <x:row r="835" spans="1:8">
       <x:c r="A835" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B835" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C835" s="1" t="s">
-        <x:v>1856</x:v>
+        <x:v>1853</x:v>
       </x:c>
       <x:c r="D835" s="1" t="s">
-        <x:v>1857</x:v>
+        <x:v>1854</x:v>
       </x:c>
       <x:c r="E835" s="1" t="s">
-        <x:v>1858</x:v>
+        <x:v>1855</x:v>
       </x:c>
       <x:c r="F835" s="1" t="s">
-        <x:v>1859</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="G835" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="H835" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="836" spans="1:8">
@@ -30547,16 +30547,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C836" s="1" t="s">
-        <x:v>1860</x:v>
+        <x:v>1856</x:v>
       </x:c>
       <x:c r="D836" s="1" t="s">
-        <x:v>1861</x:v>
+        <x:v>1857</x:v>
       </x:c>
       <x:c r="E836" s="1" t="s">
-        <x:v>1862</x:v>
+        <x:v>1858</x:v>
       </x:c>
       <x:c r="F836" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>1859</x:v>
       </x:c>
       <x:c r="G836" s="1">
         <x:v>50</x:v>
@@ -30573,16 +30573,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C837" s="1" t="s">
-        <x:v>1863</x:v>
+        <x:v>1860</x:v>
       </x:c>
       <x:c r="D837" s="1" t="s">
-        <x:v>1864</x:v>
+        <x:v>1861</x:v>
       </x:c>
       <x:c r="E837" s="1" t="s">
-        <x:v>1865</x:v>
+        <x:v>1862</x:v>
       </x:c>
       <x:c r="F837" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G837" s="1">
         <x:v>50</x:v>
@@ -30599,16 +30599,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C838" s="1" t="s">
-        <x:v>1866</x:v>
+        <x:v>1863</x:v>
       </x:c>
       <x:c r="D838" s="1" t="s">
-        <x:v>1867</x:v>
+        <x:v>1864</x:v>
       </x:c>
       <x:c r="E838" s="1" t="s">
-        <x:v>1868</x:v>
+        <x:v>1865</x:v>
       </x:c>
       <x:c r="F838" s="1" t="s">
-        <x:v>220</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G838" s="1">
         <x:v>50</x:v>
@@ -30625,16 +30625,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C839" s="1" t="s">
-        <x:v>1869</x:v>
+        <x:v>1866</x:v>
       </x:c>
       <x:c r="D839" s="1" t="s">
-        <x:v>1870</x:v>
+        <x:v>1867</x:v>
       </x:c>
       <x:c r="E839" s="1" t="s">
-        <x:v>1871</x:v>
+        <x:v>1868</x:v>
       </x:c>
       <x:c r="F839" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G839" s="1">
         <x:v>50</x:v>
@@ -30651,16 +30651,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C840" s="1" t="s">
-        <x:v>1872</x:v>
+        <x:v>1869</x:v>
       </x:c>
       <x:c r="D840" s="1" t="s">
-        <x:v>1873</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="E840" s="1" t="s">
-        <x:v>1874</x:v>
+        <x:v>1871</x:v>
       </x:c>
       <x:c r="F840" s="1" t="s">
-        <x:v>601</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="G840" s="1">
         <x:v>50</x:v>
@@ -30677,16 +30677,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C841" s="1" t="s">
-        <x:v>1875</x:v>
+        <x:v>1872</x:v>
       </x:c>
       <x:c r="D841" s="1" t="s">
-        <x:v>1876</x:v>
+        <x:v>1873</x:v>
       </x:c>
       <x:c r="E841" s="1" t="s">
-        <x:v>1877</x:v>
+        <x:v>1874</x:v>
       </x:c>
       <x:c r="F841" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="G841" s="1">
         <x:v>50</x:v>
@@ -30703,16 +30703,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C842" s="1" t="s">
-        <x:v>1878</x:v>
+        <x:v>1875</x:v>
       </x:c>
       <x:c r="D842" s="1" t="s">
-        <x:v>1879</x:v>
+        <x:v>1876</x:v>
       </x:c>
       <x:c r="E842" s="1" t="s">
-        <x:v>1880</x:v>
+        <x:v>1877</x:v>
       </x:c>
       <x:c r="F842" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="G842" s="1">
         <x:v>50</x:v>
@@ -30729,16 +30729,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C843" s="1" t="s">
-        <x:v>1881</x:v>
+        <x:v>1878</x:v>
       </x:c>
       <x:c r="D843" s="1" t="s">
-        <x:v>1882</x:v>
+        <x:v>1879</x:v>
       </x:c>
       <x:c r="E843" s="1" t="s">
-        <x:v>1883</x:v>
+        <x:v>1880</x:v>
       </x:c>
       <x:c r="F843" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G843" s="1">
         <x:v>50</x:v>
@@ -30749,54 +30749,54 @@
     </x:row>
     <x:row r="844" spans="1:8">
       <x:c r="A844" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B844" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C844" s="1" t="s">
-        <x:v>1884</x:v>
+        <x:v>1881</x:v>
       </x:c>
       <x:c r="D844" s="1" t="s">
-        <x:v>1885</x:v>
+        <x:v>1882</x:v>
       </x:c>
       <x:c r="E844" s="1" t="s">
-        <x:v>1886</x:v>
+        <x:v>1883</x:v>
       </x:c>
       <x:c r="F844" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G844" s="1">
-        <x:v>3500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H844" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="845" spans="1:8">
       <x:c r="A845" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B845" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C845" s="1" t="s">
-        <x:v>1887</x:v>
+        <x:v>1884</x:v>
       </x:c>
       <x:c r="D845" s="1" t="s">
-        <x:v>1888</x:v>
+        <x:v>1885</x:v>
       </x:c>
       <x:c r="E845" s="1" t="s">
-        <x:v>1889</x:v>
+        <x:v>1886</x:v>
       </x:c>
       <x:c r="F845" s="1" t="s">
-        <x:v>1025</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G845" s="1">
-        <x:v>50</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="H845" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="846" spans="1:8">
@@ -30807,16 +30807,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C846" s="1" t="s">
-        <x:v>1890</x:v>
+        <x:v>1887</x:v>
       </x:c>
       <x:c r="D846" s="1" t="s">
-        <x:v>1891</x:v>
+        <x:v>1888</x:v>
       </x:c>
       <x:c r="E846" s="1" t="s">
-        <x:v>1892</x:v>
+        <x:v>1889</x:v>
       </x:c>
       <x:c r="F846" s="1" t="s">
-        <x:v>203</x:v>
+        <x:v>1025</x:v>
       </x:c>
       <x:c r="G846" s="1">
         <x:v>50</x:v>
@@ -30833,16 +30833,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C847" s="1" t="s">
-        <x:v>1893</x:v>
+        <x:v>1890</x:v>
       </x:c>
       <x:c r="D847" s="1" t="s">
-        <x:v>1894</x:v>
+        <x:v>1891</x:v>
       </x:c>
       <x:c r="E847" s="1" t="s">
-        <x:v>1895</x:v>
+        <x:v>1892</x:v>
       </x:c>
       <x:c r="F847" s="1" t="s">
-        <x:v>699</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="G847" s="1">
         <x:v>50</x:v>
@@ -30859,16 +30859,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C848" s="1" t="s">
-        <x:v>1896</x:v>
+        <x:v>1893</x:v>
       </x:c>
       <x:c r="D848" s="1" t="s">
-        <x:v>1897</x:v>
+        <x:v>1894</x:v>
       </x:c>
       <x:c r="E848" s="1" t="s">
-        <x:v>1898</x:v>
+        <x:v>1895</x:v>
       </x:c>
       <x:c r="F848" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="G848" s="1">
         <x:v>50</x:v>
@@ -30885,16 +30885,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C849" s="1" t="s">
-        <x:v>1899</x:v>
+        <x:v>1896</x:v>
       </x:c>
       <x:c r="D849" s="1" t="s">
-        <x:v>1900</x:v>
+        <x:v>1897</x:v>
       </x:c>
       <x:c r="E849" s="1" t="s">
-        <x:v>1901</x:v>
+        <x:v>1898</x:v>
       </x:c>
       <x:c r="F849" s="1" t="s">
-        <x:v>252</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G849" s="1">
         <x:v>50</x:v>
@@ -30911,16 +30911,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C850" s="1" t="s">
-        <x:v>1902</x:v>
+        <x:v>1899</x:v>
       </x:c>
       <x:c r="D850" s="1" t="s">
-        <x:v>1903</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="E850" s="1" t="s">
-        <x:v>1904</x:v>
+        <x:v>1901</x:v>
       </x:c>
       <x:c r="F850" s="1" t="s">
-        <x:v>183</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="G850" s="1">
         <x:v>50</x:v>
@@ -30937,16 +30937,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C851" s="1" t="s">
-        <x:v>1905</x:v>
+        <x:v>1902</x:v>
       </x:c>
       <x:c r="D851" s="1" t="s">
-        <x:v>1906</x:v>
+        <x:v>1903</x:v>
       </x:c>
       <x:c r="E851" s="1" t="s">
-        <x:v>1907</x:v>
+        <x:v>1904</x:v>
       </x:c>
       <x:c r="F851" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="G851" s="1">
         <x:v>50</x:v>
@@ -30963,16 +30963,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C852" s="1" t="s">
-        <x:v>1908</x:v>
+        <x:v>1905</x:v>
       </x:c>
       <x:c r="D852" s="1" t="s">
-        <x:v>1909</x:v>
+        <x:v>1906</x:v>
       </x:c>
       <x:c r="E852" s="1" t="s">
-        <x:v>1910</x:v>
+        <x:v>1907</x:v>
       </x:c>
       <x:c r="F852" s="1" t="s">
-        <x:v>361</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="G852" s="1">
         <x:v>50</x:v>
@@ -30989,30 +30989,30 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C853" s="1" t="s">
-        <x:v>1911</x:v>
+        <x:v>1908</x:v>
       </x:c>
       <x:c r="D853" s="1" t="s">
-        <x:v>1912</x:v>
+        <x:v>1909</x:v>
       </x:c>
       <x:c r="E853" s="1" t="s">
-        <x:v>1913</x:v>
+        <x:v>1910</x:v>
       </x:c>
       <x:c r="F853" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="G853" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H853" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="854" spans="1:8">
       <x:c r="A854" s="1" t="s">
-        <x:v>292</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B854" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C854" s="1" t="s">
         <x:v>1911</x:v>
@@ -31030,33 +31030,33 @@
         <x:v>2000</x:v>
       </x:c>
       <x:c r="H854" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="855" spans="1:8">
       <x:c r="A855" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B855" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="C855" s="1" t="s">
-        <x:v>1914</x:v>
+        <x:v>1911</x:v>
       </x:c>
       <x:c r="D855" s="1" t="s">
-        <x:v>1915</x:v>
+        <x:v>1912</x:v>
       </x:c>
       <x:c r="E855" s="1" t="s">
-        <x:v>1916</x:v>
+        <x:v>1913</x:v>
       </x:c>
       <x:c r="F855" s="1" t="s">
-        <x:v>746</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G855" s="1">
-        <x:v>50</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="H855" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="856" spans="1:8">
@@ -31067,16 +31067,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C856" s="1" t="s">
-        <x:v>1917</x:v>
+        <x:v>1914</x:v>
       </x:c>
       <x:c r="D856" s="1" t="s">
-        <x:v>1918</x:v>
+        <x:v>1915</x:v>
       </x:c>
       <x:c r="E856" s="1" t="s">
-        <x:v>1919</x:v>
+        <x:v>1916</x:v>
       </x:c>
       <x:c r="F856" s="1" t="s">
-        <x:v>252</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="G856" s="1">
         <x:v>50</x:v>
@@ -31093,16 +31093,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C857" s="1" t="s">
-        <x:v>1920</x:v>
+        <x:v>1917</x:v>
       </x:c>
       <x:c r="D857" s="1" t="s">
-        <x:v>1921</x:v>
+        <x:v>1918</x:v>
       </x:c>
       <x:c r="E857" s="1" t="s">
-        <x:v>1922</x:v>
+        <x:v>1919</x:v>
       </x:c>
       <x:c r="F857" s="1" t="s">
-        <x:v>248</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="G857" s="1">
         <x:v>50</x:v>
@@ -31131,18 +31131,18 @@
         <x:v>248</x:v>
       </x:c>
       <x:c r="G858" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H858" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="859" spans="1:8">
       <x:c r="A859" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B859" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C859" s="1" t="s">
         <x:v>1920</x:v>
@@ -31157,7 +31157,7 @@
         <x:v>248</x:v>
       </x:c>
       <x:c r="G859" s="1">
-        <x:v>5800</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="H859" s="1" t="s">
         <x:v>50</x:v>
@@ -31165,28 +31165,28 @@
     </x:row>
     <x:row r="860" spans="1:8">
       <x:c r="A860" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B860" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C860" s="1" t="s">
-        <x:v>1923</x:v>
+        <x:v>1920</x:v>
       </x:c>
       <x:c r="D860" s="1" t="s">
-        <x:v>1924</x:v>
+        <x:v>1921</x:v>
       </x:c>
       <x:c r="E860" s="1" t="s">
-        <x:v>1925</x:v>
+        <x:v>1922</x:v>
       </x:c>
       <x:c r="F860" s="1" t="s">
-        <x:v>516</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="G860" s="1">
-        <x:v>50</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="H860" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="861" spans="1:8">
@@ -31197,16 +31197,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C861" s="1" t="s">
-        <x:v>1926</x:v>
+        <x:v>1923</x:v>
       </x:c>
       <x:c r="D861" s="1" t="s">
-        <x:v>1927</x:v>
+        <x:v>1924</x:v>
       </x:c>
       <x:c r="E861" s="1" t="s">
-        <x:v>1928</x:v>
+        <x:v>1925</x:v>
       </x:c>
       <x:c r="F861" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="G861" s="1">
         <x:v>50</x:v>
@@ -31217,36 +31217,36 @@
     </x:row>
     <x:row r="862" spans="1:8">
       <x:c r="A862" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B862" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C862" s="1" t="s">
-        <x:v>1929</x:v>
+        <x:v>1926</x:v>
       </x:c>
       <x:c r="D862" s="1" t="s">
-        <x:v>1930</x:v>
+        <x:v>1927</x:v>
       </x:c>
       <x:c r="E862" s="1" t="s">
-        <x:v>1931</x:v>
+        <x:v>1928</x:v>
       </x:c>
       <x:c r="F862" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="G862" s="1">
-        <x:v>2700</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H862" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="863" spans="1:8">
       <x:c r="A863" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B863" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C863" s="1" t="s">
         <x:v>1929</x:v>
@@ -31261,7 +31261,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="G863" s="1">
-        <x:v>1000</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="H863" s="1" t="s">
         <x:v>103</x:v>
@@ -31269,10 +31269,10 @@
     </x:row>
     <x:row r="864" spans="1:8">
       <x:c r="A864" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B864" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C864" s="1" t="s">
         <x:v>1929</x:v>
@@ -31287,7 +31287,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="G864" s="1">
-        <x:v>1500</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="H864" s="1" t="s">
         <x:v>103</x:v>
@@ -31313,18 +31313,18 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="G865" s="1">
-        <x:v>5000</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="H865" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="866" spans="1:8">
       <x:c r="A866" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B866" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C866" s="1" t="s">
         <x:v>1929</x:v>
@@ -31339,7 +31339,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="G866" s="1">
-        <x:v>2000</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="H866" s="1" t="s">
         <x:v>14</x:v>
@@ -31347,10 +31347,10 @@
     </x:row>
     <x:row r="867" spans="1:8">
       <x:c r="A867" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B867" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C867" s="1" t="s">
         <x:v>1929</x:v>
@@ -31365,7 +31365,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="G867" s="1">
-        <x:v>4500</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="H867" s="1" t="s">
         <x:v>14</x:v>
@@ -31373,27 +31373,53 @@
     </x:row>
     <x:row r="868" spans="1:8">
       <x:c r="A868" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B868" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C868" s="1" t="s">
+        <x:v>1929</x:v>
+      </x:c>
+      <x:c r="D868" s="1" t="s">
+        <x:v>1930</x:v>
+      </x:c>
+      <x:c r="E868" s="1" t="s">
+        <x:v>1931</x:v>
+      </x:c>
+      <x:c r="F868" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G868" s="1">
+        <x:v>4500</x:v>
+      </x:c>
+      <x:c r="H868" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="869" spans="1:8">
+      <x:c r="A869" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B869" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C869" s="1" t="s">
         <x:v>1932</x:v>
       </x:c>
-      <x:c r="D868" s="1" t="s">
+      <x:c r="D869" s="1" t="s">
         <x:v>1933</x:v>
       </x:c>
-      <x:c r="E868" s="1" t="s">
+      <x:c r="E869" s="1" t="s">
         <x:v>1934</x:v>
       </x:c>
-      <x:c r="F868" s="1" t="s">
+      <x:c r="F869" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="G868" s="1">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H868" s="1" t="s">
+      <x:c r="G869" s="1">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H869" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
     </x:row>
@@ -34154,7 +34180,7 @@
         <x:v>2020</x:v>
       </x:c>
       <x:c r="H105" s="1">
-        <x:v>1000</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:8">
@@ -53474,7 +53500,7 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="C83" s="1">
-        <x:v>2000</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:3">

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -36973,10 +36973,10 @@
         <x:v>293</x:v>
       </x:c>
       <x:c r="C213" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="D213" s="1" t="s">
-        <x:v>642</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="E213" s="1" t="s">
         <x:v>640</x:v>
@@ -36988,7 +36988,7 @@
         <x:v>2101</x:v>
       </x:c>
       <x:c r="H213" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="214" spans="1:8">
@@ -36999,10 +36999,10 @@
         <x:v>293</x:v>
       </x:c>
       <x:c r="C214" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="D214" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="E214" s="1" t="s">
         <x:v>640</x:v>
@@ -37014,7 +37014,7 @@
         <x:v>2101</x:v>
       </x:c>
       <x:c r="H214" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="215" spans="1:8">
@@ -40639,10 +40639,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C354" s="1" t="s">
-        <x:v>1715</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="D354" s="1" t="s">
-        <x:v>1716</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="E354" s="1" t="s">
         <x:v>930</x:v>
@@ -40654,7 +40654,7 @@
         <x:v>2200</x:v>
       </x:c>
       <x:c r="H354" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="355" spans="1:8">
@@ -40665,10 +40665,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C355" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>1715</x:v>
       </x:c>
       <x:c r="D355" s="1" t="s">
-        <x:v>929</x:v>
+        <x:v>1716</x:v>
       </x:c>
       <x:c r="E355" s="1" t="s">
         <x:v>930</x:v>
@@ -40680,7 +40680,7 @@
         <x:v>2200</x:v>
       </x:c>
       <x:c r="H355" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="356" spans="1:8">

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -36973,10 +36973,10 @@
         <x:v>293</x:v>
       </x:c>
       <x:c r="C213" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="D213" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="E213" s="1" t="s">
         <x:v>640</x:v>
@@ -36988,7 +36988,7 @@
         <x:v>2101</x:v>
       </x:c>
       <x:c r="H213" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="214" spans="1:8">
@@ -36999,10 +36999,10 @@
         <x:v>293</x:v>
       </x:c>
       <x:c r="C214" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="D214" s="1" t="s">
-        <x:v>642</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="E214" s="1" t="s">
         <x:v>640</x:v>
@@ -37014,7 +37014,7 @@
         <x:v>2101</x:v>
       </x:c>
       <x:c r="H214" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="215" spans="1:8">

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -36973,10 +36973,10 @@
         <x:v>293</x:v>
       </x:c>
       <x:c r="C213" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="D213" s="1" t="s">
-        <x:v>642</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="E213" s="1" t="s">
         <x:v>640</x:v>
@@ -36988,7 +36988,7 @@
         <x:v>2101</x:v>
       </x:c>
       <x:c r="H213" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="214" spans="1:8">
@@ -36999,10 +36999,10 @@
         <x:v>293</x:v>
       </x:c>
       <x:c r="C214" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="D214" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="E214" s="1" t="s">
         <x:v>640</x:v>
@@ -37014,7 +37014,7 @@
         <x:v>2101</x:v>
       </x:c>
       <x:c r="H214" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="215" spans="1:8">

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -36973,10 +36973,10 @@
         <x:v>293</x:v>
       </x:c>
       <x:c r="C213" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="D213" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="E213" s="1" t="s">
         <x:v>640</x:v>
@@ -36988,7 +36988,7 @@
         <x:v>2101</x:v>
       </x:c>
       <x:c r="H213" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="214" spans="1:8">
@@ -36999,10 +36999,10 @@
         <x:v>293</x:v>
       </x:c>
       <x:c r="C214" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="D214" s="1" t="s">
-        <x:v>642</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="E214" s="1" t="s">
         <x:v>640</x:v>
@@ -37014,7 +37014,7 @@
         <x:v>2101</x:v>
       </x:c>
       <x:c r="H214" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="215" spans="1:8">
@@ -40639,10 +40639,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C354" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>1715</x:v>
       </x:c>
       <x:c r="D354" s="1" t="s">
-        <x:v>929</x:v>
+        <x:v>1716</x:v>
       </x:c>
       <x:c r="E354" s="1" t="s">
         <x:v>930</x:v>
@@ -40654,7 +40654,7 @@
         <x:v>2200</x:v>
       </x:c>
       <x:c r="H354" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="355" spans="1:8">
@@ -40665,10 +40665,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C355" s="1" t="s">
-        <x:v>1715</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="D355" s="1" t="s">
-        <x:v>1716</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="E355" s="1" t="s">
         <x:v>930</x:v>
@@ -40680,7 +40680,7 @@
         <x:v>2200</x:v>
       </x:c>
       <x:c r="H355" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="356" spans="1:8">

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -40639,10 +40639,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C354" s="1" t="s">
-        <x:v>1715</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="D354" s="1" t="s">
-        <x:v>1716</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="E354" s="1" t="s">
         <x:v>930</x:v>
@@ -40654,7 +40654,7 @@
         <x:v>2200</x:v>
       </x:c>
       <x:c r="H354" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="355" spans="1:8">
@@ -40665,10 +40665,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C355" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>1715</x:v>
       </x:c>
       <x:c r="D355" s="1" t="s">
-        <x:v>929</x:v>
+        <x:v>1716</x:v>
       </x:c>
       <x:c r="E355" s="1" t="s">
         <x:v>930</x:v>
@@ -40680,7 +40680,7 @@
         <x:v>2200</x:v>
       </x:c>
       <x:c r="H355" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="356" spans="1:8">

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -37005,10 +37005,10 @@
         <x:v>293</x:v>
       </x:c>
       <x:c r="C213" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="D213" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="E213" s="1" t="s">
         <x:v>640</x:v>
@@ -37020,7 +37020,7 @@
         <x:v>2104</x:v>
       </x:c>
       <x:c r="H213" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="214" spans="1:8">
@@ -37031,10 +37031,10 @@
         <x:v>293</x:v>
       </x:c>
       <x:c r="C214" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="D214" s="1" t="s">
-        <x:v>642</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="E214" s="1" t="s">
         <x:v>640</x:v>
@@ -37046,7 +37046,7 @@
         <x:v>2104</x:v>
       </x:c>
       <x:c r="H214" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="215" spans="1:8">
@@ -40671,10 +40671,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C354" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>1718</x:v>
       </x:c>
       <x:c r="D354" s="1" t="s">
-        <x:v>929</x:v>
+        <x:v>1719</x:v>
       </x:c>
       <x:c r="E354" s="1" t="s">
         <x:v>930</x:v>
@@ -40686,7 +40686,7 @@
         <x:v>2203</x:v>
       </x:c>
       <x:c r="H354" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="355" spans="1:8">
@@ -40697,10 +40697,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C355" s="1" t="s">
-        <x:v>1718</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="D355" s="1" t="s">
-        <x:v>1719</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="E355" s="1" t="s">
         <x:v>930</x:v>
@@ -40712,7 +40712,7 @@
         <x:v>2203</x:v>
       </x:c>
       <x:c r="H355" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="356" spans="1:8">

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -37005,10 +37005,10 @@
         <x:v>293</x:v>
       </x:c>
       <x:c r="C213" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="D213" s="1" t="s">
-        <x:v>642</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="E213" s="1" t="s">
         <x:v>640</x:v>
@@ -37020,7 +37020,7 @@
         <x:v>2104</x:v>
       </x:c>
       <x:c r="H213" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="214" spans="1:8">
@@ -37031,10 +37031,10 @@
         <x:v>293</x:v>
       </x:c>
       <x:c r="C214" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="D214" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="E214" s="1" t="s">
         <x:v>640</x:v>
@@ -37046,7 +37046,7 @@
         <x:v>2104</x:v>
       </x:c>
       <x:c r="H214" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="215" spans="1:8">
@@ -40671,10 +40671,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C354" s="1" t="s">
-        <x:v>1718</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="D354" s="1" t="s">
-        <x:v>1719</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="E354" s="1" t="s">
         <x:v>930</x:v>
@@ -40686,7 +40686,7 @@
         <x:v>2203</x:v>
       </x:c>
       <x:c r="H354" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="355" spans="1:8">
@@ -40697,10 +40697,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C355" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>1718</x:v>
       </x:c>
       <x:c r="D355" s="1" t="s">
-        <x:v>929</x:v>
+        <x:v>1719</x:v>
       </x:c>
       <x:c r="E355" s="1" t="s">
         <x:v>930</x:v>
@@ -40712,7 +40712,7 @@
         <x:v>2203</x:v>
       </x:c>
       <x:c r="H355" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="356" spans="1:8">

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -40671,10 +40671,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C354" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>1718</x:v>
       </x:c>
       <x:c r="D354" s="1" t="s">
-        <x:v>929</x:v>
+        <x:v>1719</x:v>
       </x:c>
       <x:c r="E354" s="1" t="s">
         <x:v>930</x:v>
@@ -40686,7 +40686,7 @@
         <x:v>2203</x:v>
       </x:c>
       <x:c r="H354" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="355" spans="1:8">
@@ -40697,10 +40697,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C355" s="1" t="s">
-        <x:v>1718</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="D355" s="1" t="s">
-        <x:v>1719</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="E355" s="1" t="s">
         <x:v>930</x:v>
@@ -40712,7 +40712,7 @@
         <x:v>2203</x:v>
       </x:c>
       <x:c r="H355" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="356" spans="1:8">

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -37008,10 +37008,10 @@
         <x:v>293</x:v>
       </x:c>
       <x:c r="C213" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="D213" s="1" t="s">
-        <x:v>642</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="E213" s="1" t="s">
         <x:v>640</x:v>
@@ -37023,7 +37023,7 @@
         <x:v>2104</x:v>
       </x:c>
       <x:c r="H213" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="214" spans="1:8">
@@ -37034,10 +37034,10 @@
         <x:v>293</x:v>
       </x:c>
       <x:c r="C214" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="D214" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="E214" s="1" t="s">
         <x:v>640</x:v>
@@ -37049,7 +37049,7 @@
         <x:v>2104</x:v>
       </x:c>
       <x:c r="H214" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="215" spans="1:8">

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -40804,10 +40804,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C355" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>1718</x:v>
       </x:c>
       <x:c r="D355" s="1" t="s">
-        <x:v>929</x:v>
+        <x:v>1719</x:v>
       </x:c>
       <x:c r="E355" s="1" t="s">
         <x:v>930</x:v>
@@ -40819,7 +40819,7 @@
         <x:v>2203</x:v>
       </x:c>
       <x:c r="H355" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="356" spans="1:8">
@@ -40830,10 +40830,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C356" s="1" t="s">
-        <x:v>1718</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="D356" s="1" t="s">
-        <x:v>1719</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="E356" s="1" t="s">
         <x:v>930</x:v>
@@ -40845,7 +40845,7 @@
         <x:v>2203</x:v>
       </x:c>
       <x:c r="H356" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="357" spans="1:8">

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -37127,10 +37127,10 @@
         <x:v>293</x:v>
       </x:c>
       <x:c r="C213" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="D213" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="E213" s="1" t="s">
         <x:v>640</x:v>
@@ -37142,7 +37142,7 @@
         <x:v>2104</x:v>
       </x:c>
       <x:c r="H213" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="214" spans="1:8">
@@ -37153,10 +37153,10 @@
         <x:v>293</x:v>
       </x:c>
       <x:c r="C214" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="D214" s="1" t="s">
-        <x:v>642</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="E214" s="1" t="s">
         <x:v>640</x:v>
@@ -37168,7 +37168,7 @@
         <x:v>2104</x:v>
       </x:c>
       <x:c r="H214" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="215" spans="1:8">
@@ -40819,10 +40819,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C355" s="1" t="s">
-        <x:v>1718</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="D355" s="1" t="s">
-        <x:v>1719</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="E355" s="1" t="s">
         <x:v>930</x:v>
@@ -40834,7 +40834,7 @@
         <x:v>2203</x:v>
       </x:c>
       <x:c r="H355" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="356" spans="1:8">
@@ -40845,10 +40845,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C356" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>1718</x:v>
       </x:c>
       <x:c r="D356" s="1" t="s">
-        <x:v>929</x:v>
+        <x:v>1719</x:v>
       </x:c>
       <x:c r="E356" s="1" t="s">
         <x:v>930</x:v>
@@ -40860,7 +40860,7 @@
         <x:v>2203</x:v>
       </x:c>
       <x:c r="H356" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="357" spans="1:8">
@@ -62227,7 +62227,7 @@
         <x:v>2587</x:v>
       </x:c>
       <x:c r="I74" s="1">
-        <x:v>5730541</x:v>
+        <x:v>17851755</x:v>
       </x:c>
       <x:c r="J74" s="1" t="s">
         <x:v>2581</x:v>
@@ -67649,7 +67649,7 @@
         <x:v>2587</x:v>
       </x:c>
       <x:c r="I71" s="1">
-        <x:v>5730541</x:v>
+        <x:v>17851755</x:v>
       </x:c>
       <x:c r="J71" s="1" t="s">
         <x:v>2581</x:v>
@@ -71066,7 +71066,7 @@
         <x:v>936</x:v>
       </x:c>
       <x:c r="B64" s="1">
-        <x:v>7215640</x:v>
+        <x:v>19336854</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
         <x:v>2581</x:v>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -40819,10 +40819,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C355" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>1718</x:v>
       </x:c>
       <x:c r="D355" s="1" t="s">
-        <x:v>929</x:v>
+        <x:v>1719</x:v>
       </x:c>
       <x:c r="E355" s="1" t="s">
         <x:v>930</x:v>
@@ -40834,7 +40834,7 @@
         <x:v>2203</x:v>
       </x:c>
       <x:c r="H355" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="356" spans="1:8">
@@ -40845,10 +40845,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C356" s="1" t="s">
-        <x:v>1718</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="D356" s="1" t="s">
-        <x:v>1719</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="E356" s="1" t="s">
         <x:v>930</x:v>
@@ -40860,7 +40860,7 @@
         <x:v>2203</x:v>
       </x:c>
       <x:c r="H356" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="357" spans="1:8">

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -37179,10 +37179,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="C214" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="D214" s="1" t="s">
-        <x:v>642</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="E214" s="1" t="s">
         <x:v>640</x:v>
@@ -37194,7 +37194,7 @@
         <x:v>2104</x:v>
       </x:c>
       <x:c r="H214" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="215" spans="1:8">
@@ -37205,10 +37205,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="C215" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="D215" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="E215" s="1" t="s">
         <x:v>640</x:v>
@@ -37220,7 +37220,7 @@
         <x:v>2104</x:v>
       </x:c>
       <x:c r="H215" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="216" spans="1:8">
@@ -40871,10 +40871,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C356" s="1" t="s">
-        <x:v>1718</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="D356" s="1" t="s">
-        <x:v>1719</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="E356" s="1" t="s">
         <x:v>930</x:v>
@@ -40886,7 +40886,7 @@
         <x:v>2203</x:v>
       </x:c>
       <x:c r="H356" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="357" spans="1:8">
@@ -40897,10 +40897,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C357" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>1718</x:v>
       </x:c>
       <x:c r="D357" s="1" t="s">
-        <x:v>929</x:v>
+        <x:v>1719</x:v>
       </x:c>
       <x:c r="E357" s="1" t="s">
         <x:v>930</x:v>
@@ -40912,7 +40912,7 @@
         <x:v>2203</x:v>
       </x:c>
       <x:c r="H357" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="358" spans="1:8">

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -62279,7 +62279,7 @@
         <x:v>2587</x:v>
       </x:c>
       <x:c r="I74" s="1">
-        <x:v>17851755</x:v>
+        <x:v>18060379</x:v>
       </x:c>
       <x:c r="J74" s="1" t="s">
         <x:v>2581</x:v>
@@ -67701,7 +67701,7 @@
         <x:v>2587</x:v>
       </x:c>
       <x:c r="I71" s="1">
-        <x:v>17851755</x:v>
+        <x:v>18060379</x:v>
       </x:c>
       <x:c r="J71" s="1" t="s">
         <x:v>2581</x:v>
@@ -71118,7 +71118,7 @@
         <x:v>936</x:v>
       </x:c>
       <x:c r="B64" s="1">
-        <x:v>19336854</x:v>
+        <x:v>19545478</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
         <x:v>2581</x:v>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -37179,10 +37179,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="C214" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="D214" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="E214" s="1" t="s">
         <x:v>640</x:v>
@@ -37194,7 +37194,7 @@
         <x:v>2104</x:v>
       </x:c>
       <x:c r="H214" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="215" spans="1:8">
@@ -37205,10 +37205,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="C215" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="D215" s="1" t="s">
-        <x:v>642</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="E215" s="1" t="s">
         <x:v>640</x:v>
@@ -37220,7 +37220,7 @@
         <x:v>2104</x:v>
       </x:c>
       <x:c r="H215" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="216" spans="1:8">
@@ -40871,10 +40871,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C356" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>1718</x:v>
       </x:c>
       <x:c r="D356" s="1" t="s">
-        <x:v>929</x:v>
+        <x:v>1719</x:v>
       </x:c>
       <x:c r="E356" s="1" t="s">
         <x:v>930</x:v>
@@ -40886,7 +40886,7 @@
         <x:v>2203</x:v>
       </x:c>
       <x:c r="H356" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="357" spans="1:8">
@@ -40897,10 +40897,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C357" s="1" t="s">
-        <x:v>1718</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="D357" s="1" t="s">
-        <x:v>1719</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="E357" s="1" t="s">
         <x:v>930</x:v>
@@ -40912,7 +40912,7 @@
         <x:v>2203</x:v>
       </x:c>
       <x:c r="H357" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="358" spans="1:8">

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -40927,10 +40927,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C356" s="1" t="s">
-        <x:v>1718</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="D356" s="1" t="s">
-        <x:v>1719</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="E356" s="1" t="s">
         <x:v>930</x:v>
@@ -40942,7 +40942,7 @@
         <x:v>2203</x:v>
       </x:c>
       <x:c r="H356" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="357" spans="1:8">
@@ -40953,10 +40953,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C357" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>1718</x:v>
       </x:c>
       <x:c r="D357" s="1" t="s">
-        <x:v>929</x:v>
+        <x:v>1719</x:v>
       </x:c>
       <x:c r="E357" s="1" t="s">
         <x:v>930</x:v>
@@ -40968,7 +40968,7 @@
         <x:v>2203</x:v>
       </x:c>
       <x:c r="H357" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="358" spans="1:8">
@@ -59885,7 +59885,7 @@
         <x:v>2588</x:v>
       </x:c>
       <x:c r="I4" s="1">
-        <x:v>69725</x:v>
+        <x:v>145696</x:v>
       </x:c>
       <x:c r="J4" s="1" t="s">
         <x:v>2579</x:v>
@@ -66360,7 +66360,7 @@
         <x:v>2588</x:v>
       </x:c>
       <x:c r="I189" s="1">
-        <x:v>348625</x:v>
+        <x:v>424596</x:v>
       </x:c>
       <x:c r="J189" s="1" t="s">
         <x:v>2610</x:v>
@@ -66698,7 +66698,7 @@
         <x:v>2588</x:v>
       </x:c>
       <x:c r="I4" s="1">
-        <x:v>69725</x:v>
+        <x:v>145696</x:v>
       </x:c>
       <x:c r="J4" s="1" t="s">
         <x:v>2579</x:v>
@@ -72170,7 +72170,7 @@
         <x:v>2588</x:v>
       </x:c>
       <x:c r="I175" s="1">
-        <x:v>348625</x:v>
+        <x:v>424596</x:v>
       </x:c>
       <x:c r="J175" s="1" t="s">
         <x:v>2610</x:v>
@@ -72399,7 +72399,7 @@
         <x:v>148</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>69725</x:v>
+        <x:v>145696</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>2579</x:v>
@@ -74115,7 +74115,7 @@
         <x:v>2792</x:v>
       </x:c>
       <x:c r="B160" s="1">
-        <x:v>348625</x:v>
+        <x:v>424596</x:v>
       </x:c>
       <x:c r="C160" s="1" t="s">
         <x:v>2610</x:v>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -37235,10 +37235,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="C214" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="D214" s="1" t="s">
-        <x:v>642</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="E214" s="1" t="s">
         <x:v>640</x:v>
@@ -37250,7 +37250,7 @@
         <x:v>2104</x:v>
       </x:c>
       <x:c r="H214" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="215" spans="1:8">
@@ -37261,10 +37261,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="C215" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="D215" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="E215" s="1" t="s">
         <x:v>640</x:v>
@@ -37276,7 +37276,7 @@
         <x:v>2104</x:v>
       </x:c>
       <x:c r="H215" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="216" spans="1:8">
@@ -40927,10 +40927,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C356" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>1718</x:v>
       </x:c>
       <x:c r="D356" s="1" t="s">
-        <x:v>929</x:v>
+        <x:v>1719</x:v>
       </x:c>
       <x:c r="E356" s="1" t="s">
         <x:v>930</x:v>
@@ -40942,7 +40942,7 @@
         <x:v>2203</x:v>
       </x:c>
       <x:c r="H356" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="357" spans="1:8">
@@ -40953,10 +40953,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C357" s="1" t="s">
-        <x:v>1718</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="D357" s="1" t="s">
-        <x:v>1719</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="E357" s="1" t="s">
         <x:v>930</x:v>
@@ -40968,7 +40968,7 @@
         <x:v>2203</x:v>
       </x:c>
       <x:c r="H357" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="358" spans="1:8">

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -40927,10 +40927,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C356" s="1" t="s">
-        <x:v>1718</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="D356" s="1" t="s">
-        <x:v>1719</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="E356" s="1" t="s">
         <x:v>930</x:v>
@@ -40942,7 +40942,7 @@
         <x:v>2203</x:v>
       </x:c>
       <x:c r="H356" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="357" spans="1:8">
@@ -40953,10 +40953,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C357" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>1718</x:v>
       </x:c>
       <x:c r="D357" s="1" t="s">
-        <x:v>929</x:v>
+        <x:v>1719</x:v>
       </x:c>
       <x:c r="E357" s="1" t="s">
         <x:v>930</x:v>
@@ -40968,7 +40968,7 @@
         <x:v>2203</x:v>
       </x:c>
       <x:c r="H357" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="358" spans="1:8">

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -8257,6 +8257,15 @@
   </x:si>
   <x:si>
     <x:t>ONDER JR, ROBERT FRANK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S4NE00207</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSBORN, DAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IND</x:t>
   </x:si>
   <x:si>
     <x:t>19</x:t>
@@ -8531,8 +8540,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K194" totalsRowShown="0">
-  <x:autoFilter ref="A1:K194"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K195" totalsRowShown="0">
+  <x:autoFilter ref="A1:K195"/>
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -8551,8 +8560,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J180" totalsRowShown="0">
-  <x:autoFilter ref="A1:J180"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J181" totalsRowShown="0">
+  <x:autoFilter ref="A1:J181"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -8570,8 +8579,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C165" totalsRowShown="0">
-  <x:autoFilter ref="A1:C165"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C166" totalsRowShown="0">
+  <x:autoFilter ref="A1:C166"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -40927,10 +40936,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C356" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>1718</x:v>
       </x:c>
       <x:c r="D356" s="1" t="s">
-        <x:v>929</x:v>
+        <x:v>1719</x:v>
       </x:c>
       <x:c r="E356" s="1" t="s">
         <x:v>930</x:v>
@@ -40942,7 +40951,7 @@
         <x:v>2203</x:v>
       </x:c>
       <x:c r="H356" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="357" spans="1:8">
@@ -40953,10 +40962,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C357" s="1" t="s">
-        <x:v>1718</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="D357" s="1" t="s">
-        <x:v>1719</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="E357" s="1" t="s">
         <x:v>930</x:v>
@@ -40968,7 +40977,7 @@
         <x:v>2203</x:v>
       </x:c>
       <x:c r="H357" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="358" spans="1:8">
@@ -59737,7 +59746,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K194"/>
+  <x:dimension ref="A1:K195"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="12" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -60445,7 +60454,7 @@
         <x:v>2588</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>5731065</x:v>
+        <x:v>12894063</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
         <x:v>2610</x:v>
@@ -61751,10 +61760,10 @@
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
         <x:v>2671</x:v>
@@ -61775,7 +61784,7 @@
         <x:v>2673</x:v>
       </x:c>
       <x:c r="I58" s="1">
-        <x:v>910292</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="J58" s="1" t="s">
         <x:v>2579</x:v>
@@ -61786,10 +61795,10 @@
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="1" t="s">
-        <x:v>2598</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
         <x:v>2671</x:v>
@@ -61810,7 +61819,7 @@
         <x:v>2673</x:v>
       </x:c>
       <x:c r="I59" s="1">
-        <x:v>300000</x:v>
+        <x:v>910292</x:v>
       </x:c>
       <x:c r="J59" s="1" t="s">
         <x:v>2579</x:v>
@@ -62136,10 +62145,10 @@
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
         <x:v>2153</x:v>
@@ -62160,7 +62169,7 @@
         <x:v>2597</x:v>
       </x:c>
       <x:c r="I69" s="1">
-        <x:v>122688</x:v>
+        <x:v>120103</x:v>
       </x:c>
       <x:c r="J69" s="1" t="s">
         <x:v>2579</x:v>
@@ -62171,10 +62180,10 @@
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
         <x:v>2153</x:v>
@@ -62195,7 +62204,7 @@
         <x:v>2597</x:v>
       </x:c>
       <x:c r="I70" s="1">
-        <x:v>120103</x:v>
+        <x:v>122688</x:v>
       </x:c>
       <x:c r="J70" s="1" t="s">
         <x:v>2579</x:v>
@@ -62486,10 +62495,10 @@
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
         <x:v>2189</x:v>
@@ -62510,7 +62519,7 @@
         <x:v>2621</x:v>
       </x:c>
       <x:c r="I79" s="1">
-        <x:v>1019964</x:v>
+        <x:v>836118</x:v>
       </x:c>
       <x:c r="J79" s="1" t="s">
         <x:v>2579</x:v>
@@ -62521,10 +62530,10 @@
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
         <x:v>2189</x:v>
@@ -62545,7 +62554,7 @@
         <x:v>2621</x:v>
       </x:c>
       <x:c r="I80" s="1">
-        <x:v>836118</x:v>
+        <x:v>1019964</x:v>
       </x:c>
       <x:c r="J80" s="1" t="s">
         <x:v>2579</x:v>
@@ -62661,10 +62670,10 @@
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
         <x:v>2203</x:v>
@@ -62685,7 +62694,7 @@
         <x:v>2591</x:v>
       </x:c>
       <x:c r="I84" s="1">
-        <x:v>1019167</x:v>
+        <x:v>1023992</x:v>
       </x:c>
       <x:c r="J84" s="1" t="s">
         <x:v>2579</x:v>
@@ -62696,10 +62705,10 @@
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
         <x:v>2203</x:v>
@@ -62720,7 +62729,7 @@
         <x:v>2591</x:v>
       </x:c>
       <x:c r="I85" s="1">
-        <x:v>1023992</x:v>
+        <x:v>1019167</x:v>
       </x:c>
       <x:c r="J85" s="1" t="s">
         <x:v>2579</x:v>
@@ -62766,10 +62775,10 @@
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
         <x:v>2206</x:v>
@@ -62790,7 +62799,7 @@
         <x:v>2588</x:v>
       </x:c>
       <x:c r="I87" s="1">
-        <x:v>2475165</x:v>
+        <x:v>33778233</x:v>
       </x:c>
       <x:c r="J87" s="1" t="s">
         <x:v>2579</x:v>
@@ -62801,10 +62810,10 @@
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
         <x:v>2206</x:v>
@@ -62825,7 +62834,7 @@
         <x:v>2588</x:v>
       </x:c>
       <x:c r="I88" s="1">
-        <x:v>29079466</x:v>
+        <x:v>2475165</x:v>
       </x:c>
       <x:c r="J88" s="1" t="s">
         <x:v>2579</x:v>
@@ -64551,34 +64560,34 @@
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B138" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C138" s="1" t="s">
-        <x:v>2377</x:v>
+        <x:v>2746</x:v>
       </x:c>
       <x:c r="D138" s="1" t="s">
-        <x:v>1000</x:v>
+        <x:v>2747</x:v>
       </x:c>
       <x:c r="E138" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2748</x:v>
       </x:c>
       <x:c r="F138" s="1" t="s">
-        <x:v>2577</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="G138" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H138" s="1" t="s">
-        <x:v>2746</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="I138" s="1">
-        <x:v>74692</x:v>
+        <x:v>6723910</x:v>
       </x:c>
       <x:c r="J138" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2610</x:v>
       </x:c>
       <x:c r="K138" s="1">
         <x:v>2026</x:v>
@@ -64586,31 +64595,31 @@
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B139" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C139" s="1" t="s">
-        <x:v>2747</x:v>
+        <x:v>2377</x:v>
       </x:c>
       <x:c r="D139" s="1" t="s">
-        <x:v>2748</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="E139" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="F139" s="1" t="s">
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G139" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H139" s="1" t="s">
-        <x:v>2628</x:v>
+        <x:v>2749</x:v>
       </x:c>
       <x:c r="I139" s="1">
-        <x:v>558813</x:v>
+        <x:v>74692</x:v>
       </x:c>
       <x:c r="J139" s="1" t="s">
         <x:v>2579</x:v>
@@ -64621,31 +64630,31 @@
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="1" t="s">
-        <x:v>2598</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B140" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C140" s="1" t="s">
-        <x:v>2749</x:v>
+        <x:v>2750</x:v>
       </x:c>
       <x:c r="D140" s="1" t="s">
-        <x:v>2750</x:v>
+        <x:v>2751</x:v>
       </x:c>
       <x:c r="E140" s="1" t="s">
         <x:v>2586</x:v>
       </x:c>
       <x:c r="F140" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="G140" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H140" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2628</x:v>
       </x:c>
       <x:c r="I140" s="1">
-        <x:v>2750000</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="J140" s="1" t="s">
         <x:v>2579</x:v>
@@ -64656,34 +64665,34 @@
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="B141" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="C141" s="1" t="s">
-        <x:v>2751</x:v>
+        <x:v>2752</x:v>
       </x:c>
       <x:c r="D141" s="1" t="s">
-        <x:v>2752</x:v>
+        <x:v>2753</x:v>
       </x:c>
       <x:c r="E141" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="F141" s="1" t="s">
-        <x:v>2577</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="G141" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H141" s="1" t="s">
-        <x:v>2753</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="I141" s="1">
-        <x:v>20483</x:v>
+        <x:v>2750000</x:v>
       </x:c>
       <x:c r="J141" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2579</x:v>
       </x:c>
       <x:c r="K141" s="1">
         <x:v>2026</x:v>
@@ -64691,10 +64700,10 @@
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B142" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C142" s="1" t="s">
         <x:v>2754</x:v>
@@ -64709,19 +64718,19 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G142" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="H142" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2756</x:v>
       </x:c>
       <x:c r="I142" s="1">
-        <x:v>1927706</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="J142" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2610</x:v>
       </x:c>
       <x:c r="K142" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
@@ -64732,10 +64741,10 @@
         <x:v>2617</x:v>
       </x:c>
       <x:c r="C143" s="1" t="s">
-        <x:v>2756</x:v>
+        <x:v>2757</x:v>
       </x:c>
       <x:c r="D143" s="1" t="s">
-        <x:v>2757</x:v>
+        <x:v>2758</x:v>
       </x:c>
       <x:c r="E143" s="1" t="s">
         <x:v>2576</x:v>
@@ -64744,19 +64753,19 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G143" s="1" t="s">
-        <x:v>222</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H143" s="1" t="s">
-        <x:v>2621</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="I143" s="1">
-        <x:v>817066</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="J143" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2579</x:v>
       </x:c>
       <x:c r="K143" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
@@ -64767,10 +64776,10 @@
         <x:v>2617</x:v>
       </x:c>
       <x:c r="C144" s="1" t="s">
-        <x:v>2390</x:v>
+        <x:v>2759</x:v>
       </x:c>
       <x:c r="D144" s="1" t="s">
-        <x:v>269</x:v>
+        <x:v>2760</x:v>
       </x:c>
       <x:c r="E144" s="1" t="s">
         <x:v>2576</x:v>
@@ -64779,121 +64788,121 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G144" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="H144" s="1" t="s">
-        <x:v>2665</x:v>
+        <x:v>2621</x:v>
       </x:c>
       <x:c r="I144" s="1">
-        <x:v>88256</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="J144" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2610</x:v>
       </x:c>
       <x:c r="K144" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="B145" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="C145" s="1" t="s">
-        <x:v>2758</x:v>
+        <x:v>2390</x:v>
       </x:c>
       <x:c r="D145" s="1" t="s">
-        <x:v>2759</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="E145" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="F145" s="1" t="s">
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G145" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H145" s="1" t="s">
-        <x:v>2753</x:v>
+        <x:v>2665</x:v>
       </x:c>
       <x:c r="I145" s="1">
-        <x:v>75000</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="J145" s="1" t="s">
         <x:v>2579</x:v>
       </x:c>
       <x:c r="K145" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B146" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C146" s="1" t="s">
-        <x:v>2760</x:v>
+        <x:v>2761</x:v>
       </x:c>
       <x:c r="D146" s="1" t="s">
-        <x:v>1088</x:v>
+        <x:v>2762</x:v>
       </x:c>
       <x:c r="E146" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="F146" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="G146" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H146" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2756</x:v>
       </x:c>
       <x:c r="I146" s="1">
-        <x:v>10041119</x:v>
+        <x:v>75000</x:v>
       </x:c>
       <x:c r="J146" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2579</x:v>
       </x:c>
       <x:c r="K146" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="B147" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="C147" s="1" t="s">
-        <x:v>2761</x:v>
+        <x:v>2763</x:v>
       </x:c>
       <x:c r="D147" s="1" t="s">
-        <x:v>2762</x:v>
+        <x:v>1088</x:v>
       </x:c>
       <x:c r="E147" s="1" t="s">
         <x:v>2576</x:v>
       </x:c>
       <x:c r="F147" s="1" t="s">
-        <x:v>2577</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="G147" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H147" s="1" t="s">
-        <x:v>2602</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="I147" s="1">
-        <x:v>1491280</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="J147" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2610</x:v>
       </x:c>
       <x:c r="K147" s="1">
         <x:v>2024</x:v>
@@ -64901,66 +64910,66 @@
     </x:row>
     <x:row r="148" spans="1:11">
       <x:c r="A148" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B148" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C148" s="1" t="s">
-        <x:v>2406</x:v>
+        <x:v>2764</x:v>
       </x:c>
       <x:c r="D148" s="1" t="s">
-        <x:v>888</x:v>
+        <x:v>2765</x:v>
       </x:c>
       <x:c r="E148" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="F148" s="1" t="s">
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G148" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H148" s="1" t="s">
-        <x:v>2673</x:v>
+        <x:v>2602</x:v>
       </x:c>
       <x:c r="I148" s="1">
-        <x:v>75844</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="J148" s="1" t="s">
         <x:v>2579</x:v>
       </x:c>
       <x:c r="K148" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
       <x:c r="A149" s="1" t="s">
-        <x:v>2598</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B149" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C149" s="1" t="s">
-        <x:v>2410</x:v>
+        <x:v>2406</x:v>
       </x:c>
       <x:c r="D149" s="1" t="s">
-        <x:v>1477</x:v>
+        <x:v>888</x:v>
       </x:c>
       <x:c r="E149" s="1" t="s">
         <x:v>2586</x:v>
       </x:c>
       <x:c r="F149" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="G149" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="H149" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2673</x:v>
       </x:c>
       <x:c r="I149" s="1">
-        <x:v>700000</x:v>
+        <x:v>75844</x:v>
       </x:c>
       <x:c r="J149" s="1" t="s">
         <x:v>2579</x:v>
@@ -64971,16 +64980,16 @@
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="1" t="s">
-        <x:v>167</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="B150" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="C150" s="1" t="s">
-        <x:v>2763</x:v>
+        <x:v>2410</x:v>
       </x:c>
       <x:c r="D150" s="1" t="s">
-        <x:v>2764</x:v>
+        <x:v>1477</x:v>
       </x:c>
       <x:c r="E150" s="1" t="s">
         <x:v>2586</x:v>
@@ -64989,13 +64998,13 @@
         <x:v>2587</x:v>
       </x:c>
       <x:c r="G150" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H150" s="1" t="s">
         <x:v>2588</x:v>
       </x:c>
       <x:c r="I150" s="1">
-        <x:v>902547</x:v>
+        <x:v>700000</x:v>
       </x:c>
       <x:c r="J150" s="1" t="s">
         <x:v>2579</x:v>
@@ -65006,16 +65015,16 @@
     </x:row>
     <x:row r="151" spans="1:11">
       <x:c r="A151" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B151" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C151" s="1" t="s">
-        <x:v>2424</x:v>
+        <x:v>2766</x:v>
       </x:c>
       <x:c r="D151" s="1" t="s">
-        <x:v>1582</x:v>
+        <x:v>2767</x:v>
       </x:c>
       <x:c r="E151" s="1" t="s">
         <x:v>2586</x:v>
@@ -65024,13 +65033,13 @@
         <x:v>2587</x:v>
       </x:c>
       <x:c r="G151" s="1" t="s">
-        <x:v>733</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H151" s="1" t="s">
         <x:v>2588</x:v>
       </x:c>
       <x:c r="I151" s="1">
-        <x:v>823496</x:v>
+        <x:v>902547</x:v>
       </x:c>
       <x:c r="J151" s="1" t="s">
         <x:v>2579</x:v>
@@ -65047,25 +65056,25 @@
         <x:v>2593</x:v>
       </x:c>
       <x:c r="C152" s="1" t="s">
-        <x:v>2425</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="D152" s="1" t="s">
-        <x:v>493</x:v>
+        <x:v>1582</x:v>
       </x:c>
       <x:c r="E152" s="1" t="s">
         <x:v>2586</x:v>
       </x:c>
       <x:c r="F152" s="1" t="s">
-        <x:v>2577</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="G152" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>733</x:v>
       </x:c>
       <x:c r="H152" s="1" t="s">
-        <x:v>2665</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="I152" s="1">
-        <x:v>75320</x:v>
+        <x:v>823496</x:v>
       </x:c>
       <x:c r="J152" s="1" t="s">
         <x:v>2579</x:v>
@@ -65076,51 +65085,51 @@
     </x:row>
     <x:row r="153" spans="1:11">
       <x:c r="A153" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B153" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C153" s="1" t="s">
-        <x:v>2433</x:v>
+        <x:v>2425</x:v>
       </x:c>
       <x:c r="D153" s="1" t="s">
-        <x:v>1444</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="E153" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="F153" s="1" t="s">
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G153" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H153" s="1" t="s">
-        <x:v>2689</x:v>
+        <x:v>2665</x:v>
       </x:c>
       <x:c r="I153" s="1">
-        <x:v>1987660</x:v>
+        <x:v>75320</x:v>
       </x:c>
       <x:c r="J153" s="1" t="s">
         <x:v>2579</x:v>
       </x:c>
       <x:c r="K153" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:11">
       <x:c r="A154" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="B154" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="C154" s="1" t="s">
-        <x:v>2765</x:v>
+        <x:v>2433</x:v>
       </x:c>
       <x:c r="D154" s="1" t="s">
-        <x:v>2766</x:v>
+        <x:v>1444</x:v>
       </x:c>
       <x:c r="E154" s="1" t="s">
         <x:v>2576</x:v>
@@ -65129,19 +65138,19 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G154" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H154" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2689</x:v>
       </x:c>
       <x:c r="I154" s="1">
-        <x:v>74382</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="J154" s="1" t="s">
         <x:v>2579</x:v>
       </x:c>
       <x:c r="K154" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:11">
@@ -65152,10 +65161,10 @@
         <x:v>2575</x:v>
       </x:c>
       <x:c r="C155" s="1" t="s">
-        <x:v>2448</x:v>
+        <x:v>2768</x:v>
       </x:c>
       <x:c r="D155" s="1" t="s">
-        <x:v>591</x:v>
+        <x:v>2769</x:v>
       </x:c>
       <x:c r="E155" s="1" t="s">
         <x:v>2576</x:v>
@@ -65164,13 +65173,13 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G155" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H155" s="1" t="s">
-        <x:v>2605</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="I155" s="1">
-        <x:v>105040</x:v>
+        <x:v>74382</x:v>
       </x:c>
       <x:c r="J155" s="1" t="s">
         <x:v>2579</x:v>
@@ -65187,10 +65196,10 @@
         <x:v>2575</x:v>
       </x:c>
       <x:c r="C156" s="1" t="s">
-        <x:v>2451</x:v>
+        <x:v>2448</x:v>
       </x:c>
       <x:c r="D156" s="1" t="s">
-        <x:v>496</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="E156" s="1" t="s">
         <x:v>2576</x:v>
@@ -65199,16 +65208,16 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G156" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H156" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2605</x:v>
       </x:c>
       <x:c r="I156" s="1">
-        <x:v>56045</x:v>
+        <x:v>105040</x:v>
       </x:c>
       <x:c r="J156" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2579</x:v>
       </x:c>
       <x:c r="K156" s="1">
         <x:v>2026</x:v>
@@ -65216,19 +65225,19 @@
     </x:row>
     <x:row r="157" spans="1:11">
       <x:c r="A157" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B157" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C157" s="1" t="s">
-        <x:v>2452</x:v>
+        <x:v>2451</x:v>
       </x:c>
       <x:c r="D157" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="E157" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="F157" s="1" t="s">
         <x:v>2577</x:v>
@@ -65237,13 +65246,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="H157" s="1" t="s">
-        <x:v>2605</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="I157" s="1">
-        <x:v>75281</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="J157" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2610</x:v>
       </x:c>
       <x:c r="K157" s="1">
         <x:v>2026</x:v>
@@ -65257,10 +65266,10 @@
         <x:v>2593</x:v>
       </x:c>
       <x:c r="C158" s="1" t="s">
-        <x:v>2767</x:v>
+        <x:v>2452</x:v>
       </x:c>
       <x:c r="D158" s="1" t="s">
-        <x:v>2768</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="E158" s="1" t="s">
         <x:v>2586</x:v>
@@ -65269,13 +65278,13 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G158" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H158" s="1" t="s">
-        <x:v>2746</x:v>
+        <x:v>2605</x:v>
       </x:c>
       <x:c r="I158" s="1">
-        <x:v>852561</x:v>
+        <x:v>75281</x:v>
       </x:c>
       <x:c r="J158" s="1" t="s">
         <x:v>2579</x:v>
@@ -65286,31 +65295,31 @@
     </x:row>
     <x:row r="159" spans="1:11">
       <x:c r="A159" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B159" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C159" s="1" t="s">
-        <x:v>2458</x:v>
+        <x:v>2770</x:v>
       </x:c>
       <x:c r="D159" s="1" t="s">
-        <x:v>1737</x:v>
+        <x:v>2771</x:v>
       </x:c>
       <x:c r="E159" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="F159" s="1" t="s">
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G159" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H159" s="1" t="s">
-        <x:v>2665</x:v>
+        <x:v>2749</x:v>
       </x:c>
       <x:c r="I159" s="1">
-        <x:v>74852</x:v>
+        <x:v>852561</x:v>
       </x:c>
       <x:c r="J159" s="1" t="s">
         <x:v>2579</x:v>
@@ -65327,10 +65336,10 @@
         <x:v>2575</x:v>
       </x:c>
       <x:c r="C160" s="1" t="s">
-        <x:v>2769</x:v>
+        <x:v>2458</x:v>
       </x:c>
       <x:c r="D160" s="1" t="s">
-        <x:v>2770</x:v>
+        <x:v>1737</x:v>
       </x:c>
       <x:c r="E160" s="1" t="s">
         <x:v>2576</x:v>
@@ -65339,13 +65348,13 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G160" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H160" s="1" t="s">
-        <x:v>2683</x:v>
+        <x:v>2665</x:v>
       </x:c>
       <x:c r="I160" s="1">
-        <x:v>111599</x:v>
+        <x:v>74852</x:v>
       </x:c>
       <x:c r="J160" s="1" t="s">
         <x:v>2579</x:v>
@@ -65362,66 +65371,66 @@
         <x:v>2575</x:v>
       </x:c>
       <x:c r="C161" s="1" t="s">
-        <x:v>2771</x:v>
+        <x:v>2772</x:v>
       </x:c>
       <x:c r="D161" s="1" t="s">
-        <x:v>634</x:v>
+        <x:v>2773</x:v>
       </x:c>
       <x:c r="E161" s="1" t="s">
         <x:v>2576</x:v>
       </x:c>
       <x:c r="F161" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="G161" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H161" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2683</x:v>
       </x:c>
       <x:c r="I161" s="1">
-        <x:v>10046680</x:v>
+        <x:v>111599</x:v>
       </x:c>
       <x:c r="J161" s="1" t="s">
         <x:v>2579</x:v>
       </x:c>
       <x:c r="K161" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:11">
       <x:c r="A162" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B162" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C162" s="1" t="s">
-        <x:v>2470</x:v>
+        <x:v>2774</x:v>
       </x:c>
       <x:c r="D162" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="E162" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="F162" s="1" t="s">
-        <x:v>2577</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="G162" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H162" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="I162" s="1">
-        <x:v>565950</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="J162" s="1" t="s">
         <x:v>2579</x:v>
       </x:c>
       <x:c r="K162" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:11">
@@ -65432,10 +65441,10 @@
         <x:v>2593</x:v>
       </x:c>
       <x:c r="C163" s="1" t="s">
-        <x:v>2473</x:v>
+        <x:v>2470</x:v>
       </x:c>
       <x:c r="D163" s="1" t="s">
-        <x:v>966</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E163" s="1" t="s">
         <x:v>2586</x:v>
@@ -65444,13 +65453,13 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G163" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H163" s="1" t="s">
-        <x:v>2605</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="I163" s="1">
-        <x:v>75617</x:v>
+        <x:v>565950</x:v>
       </x:c>
       <x:c r="J163" s="1" t="s">
         <x:v>2579</x:v>
@@ -65461,31 +65470,31 @@
     </x:row>
     <x:row r="164" spans="1:11">
       <x:c r="A164" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B164" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C164" s="1" t="s">
-        <x:v>2772</x:v>
+        <x:v>2473</x:v>
       </x:c>
       <x:c r="D164" s="1" t="s">
-        <x:v>2773</x:v>
+        <x:v>966</x:v>
       </x:c>
       <x:c r="E164" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="F164" s="1" t="s">
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G164" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H164" s="1" t="s">
-        <x:v>2615</x:v>
+        <x:v>2605</x:v>
       </x:c>
       <x:c r="I164" s="1">
-        <x:v>380377</x:v>
+        <x:v>75617</x:v>
       </x:c>
       <x:c r="J164" s="1" t="s">
         <x:v>2579</x:v>
@@ -65496,16 +65505,16 @@
     </x:row>
     <x:row r="165" spans="1:11">
       <x:c r="A165" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B165" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C165" s="1" t="s">
-        <x:v>2476</x:v>
+        <x:v>2775</x:v>
       </x:c>
       <x:c r="D165" s="1" t="s">
-        <x:v>655</x:v>
+        <x:v>2776</x:v>
       </x:c>
       <x:c r="E165" s="1" t="s">
         <x:v>2576</x:v>
@@ -65514,51 +65523,51 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G165" s="1" t="s">
-        <x:v>222</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H165" s="1" t="s">
-        <x:v>2704</x:v>
+        <x:v>2615</x:v>
       </x:c>
       <x:c r="I165" s="1">
-        <x:v>817169</x:v>
+        <x:v>380377</x:v>
       </x:c>
       <x:c r="J165" s="1" t="s">
         <x:v>2579</x:v>
       </x:c>
       <x:c r="K165" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:11">
       <x:c r="A166" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="B166" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="C166" s="1" t="s">
-        <x:v>2774</x:v>
+        <x:v>2476</x:v>
       </x:c>
       <x:c r="D166" s="1" t="s">
-        <x:v>2775</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="E166" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="F166" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="G166" s="1" t="s">
-        <x:v>238</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="H166" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2704</x:v>
       </x:c>
       <x:c r="I166" s="1">
-        <x:v>1531015</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="J166" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2579</x:v>
       </x:c>
       <x:c r="K166" s="1">
         <x:v>2024</x:v>
@@ -65566,72 +65575,72 @@
     </x:row>
     <x:row r="167" spans="1:11">
       <x:c r="A167" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B167" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C167" s="1" t="s">
-        <x:v>2482</x:v>
+        <x:v>2777</x:v>
       </x:c>
       <x:c r="D167" s="1" t="s">
-        <x:v>1666</x:v>
+        <x:v>2778</x:v>
       </x:c>
       <x:c r="E167" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="F167" s="1" t="s">
-        <x:v>2577</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="G167" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="H167" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="I167" s="1">
-        <x:v>157560</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="J167" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2610</x:v>
       </x:c>
       <x:c r="K167" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:11">
       <x:c r="A168" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B168" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C168" s="1" t="s">
-        <x:v>2484</x:v>
+        <x:v>2482</x:v>
       </x:c>
       <x:c r="D168" s="1" t="s">
-        <x:v>1323</x:v>
+        <x:v>1666</x:v>
       </x:c>
       <x:c r="E168" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="F168" s="1" t="s">
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G168" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H168" s="1" t="s">
-        <x:v>2776</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I168" s="1">
-        <x:v>2791716</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="J168" s="1" t="s">
         <x:v>2579</x:v>
       </x:c>
       <x:c r="K168" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:11">
@@ -65642,10 +65651,10 @@
         <x:v>2617</x:v>
       </x:c>
       <x:c r="C169" s="1" t="s">
-        <x:v>2486</x:v>
+        <x:v>2484</x:v>
       </x:c>
       <x:c r="D169" s="1" t="s">
-        <x:v>1669</x:v>
+        <x:v>1323</x:v>
       </x:c>
       <x:c r="E169" s="1" t="s">
         <x:v>2586</x:v>
@@ -65654,19 +65663,19 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G169" s="1" t="s">
-        <x:v>601</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H169" s="1" t="s">
-        <x:v>2628</x:v>
+        <x:v>2779</x:v>
       </x:c>
       <x:c r="I169" s="1">
-        <x:v>1025785</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="J169" s="1" t="s">
         <x:v>2579</x:v>
       </x:c>
       <x:c r="K169" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:11">
@@ -65695,27 +65704,27 @@
         <x:v>2628</x:v>
       </x:c>
       <x:c r="I170" s="1">
-        <x:v>764206</x:v>
+        <x:v>1025785</x:v>
       </x:c>
       <x:c r="J170" s="1" t="s">
         <x:v>2579</x:v>
       </x:c>
       <x:c r="K170" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:11">
       <x:c r="A171" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="B171" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="C171" s="1" t="s">
-        <x:v>2777</x:v>
+        <x:v>2486</x:v>
       </x:c>
       <x:c r="D171" s="1" t="s">
-        <x:v>2778</x:v>
+        <x:v>1669</x:v>
       </x:c>
       <x:c r="E171" s="1" t="s">
         <x:v>2586</x:v>
@@ -65724,51 +65733,51 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G171" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="H171" s="1" t="s">
-        <x:v>2605</x:v>
+        <x:v>2628</x:v>
       </x:c>
       <x:c r="I171" s="1">
-        <x:v>1543316</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="J171" s="1" t="s">
         <x:v>2579</x:v>
       </x:c>
       <x:c r="K171" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:11">
       <x:c r="A172" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B172" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C172" s="1" t="s">
-        <x:v>2779</x:v>
+        <x:v>2780</x:v>
       </x:c>
       <x:c r="D172" s="1" t="s">
-        <x:v>2780</x:v>
+        <x:v>2781</x:v>
       </x:c>
       <x:c r="E172" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="F172" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="G172" s="1" t="s">
-        <x:v>222</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H172" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2605</x:v>
       </x:c>
       <x:c r="I172" s="1">
-        <x:v>10015605</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="J172" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2579</x:v>
       </x:c>
       <x:c r="K172" s="1">
         <x:v>2026</x:v>
@@ -65776,16 +65785,16 @@
     </x:row>
     <x:row r="173" spans="1:11">
       <x:c r="A173" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="B173" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="C173" s="1" t="s">
-        <x:v>2779</x:v>
+        <x:v>2782</x:v>
       </x:c>
       <x:c r="D173" s="1" t="s">
-        <x:v>2780</x:v>
+        <x:v>2783</x:v>
       </x:c>
       <x:c r="E173" s="1" t="s">
         <x:v>2576</x:v>
@@ -65800,7 +65809,7 @@
         <x:v>2588</x:v>
       </x:c>
       <x:c r="I173" s="1">
-        <x:v>119844</x:v>
+        <x:v>10015605</x:v>
       </x:c>
       <x:c r="J173" s="1" t="s">
         <x:v>2610</x:v>
@@ -65817,28 +65826,28 @@
         <x:v>2575</x:v>
       </x:c>
       <x:c r="C174" s="1" t="s">
-        <x:v>2781</x:v>
+        <x:v>2782</x:v>
       </x:c>
       <x:c r="D174" s="1" t="s">
-        <x:v>2782</x:v>
+        <x:v>2783</x:v>
       </x:c>
       <x:c r="E174" s="1" t="s">
         <x:v>2576</x:v>
       </x:c>
       <x:c r="F174" s="1" t="s">
-        <x:v>2577</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="G174" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="H174" s="1" t="s">
-        <x:v>2676</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="I174" s="1">
-        <x:v>103020</x:v>
+        <x:v>119844</x:v>
       </x:c>
       <x:c r="J174" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2610</x:v>
       </x:c>
       <x:c r="K174" s="1">
         <x:v>2026</x:v>
@@ -65852,10 +65861,10 @@
         <x:v>2575</x:v>
       </x:c>
       <x:c r="C175" s="1" t="s">
-        <x:v>2783</x:v>
+        <x:v>2784</x:v>
       </x:c>
       <x:c r="D175" s="1" t="s">
-        <x:v>2784</x:v>
+        <x:v>2785</x:v>
       </x:c>
       <x:c r="E175" s="1" t="s">
         <x:v>2576</x:v>
@@ -65864,13 +65873,13 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G175" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H175" s="1" t="s">
         <x:v>2676</x:v>
       </x:c>
       <x:c r="I175" s="1">
-        <x:v>75332</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="J175" s="1" t="s">
         <x:v>2579</x:v>
@@ -65887,10 +65896,10 @@
         <x:v>2575</x:v>
       </x:c>
       <x:c r="C176" s="1" t="s">
-        <x:v>2783</x:v>
+        <x:v>2786</x:v>
       </x:c>
       <x:c r="D176" s="1" t="s">
-        <x:v>2784</x:v>
+        <x:v>2787</x:v>
       </x:c>
       <x:c r="E176" s="1" t="s">
         <x:v>2576</x:v>
@@ -65905,27 +65914,27 @@
         <x:v>2676</x:v>
       </x:c>
       <x:c r="I176" s="1">
-        <x:v>106947</x:v>
+        <x:v>75332</x:v>
       </x:c>
       <x:c r="J176" s="1" t="s">
         <x:v>2579</x:v>
       </x:c>
       <x:c r="K176" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="177" spans="1:11">
       <x:c r="A177" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B177" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C177" s="1" t="s">
-        <x:v>2493</x:v>
+        <x:v>2786</x:v>
       </x:c>
       <x:c r="D177" s="1" t="s">
-        <x:v>1687</x:v>
+        <x:v>2787</x:v>
       </x:c>
       <x:c r="E177" s="1" t="s">
         <x:v>2576</x:v>
@@ -65934,13 +65943,13 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G177" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="H177" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2676</x:v>
       </x:c>
       <x:c r="I177" s="1">
-        <x:v>902176</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="J177" s="1" t="s">
         <x:v>2579</x:v>
@@ -65951,16 +65960,16 @@
     </x:row>
     <x:row r="178" spans="1:11">
       <x:c r="A178" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="B178" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="C178" s="1" t="s">
-        <x:v>2785</x:v>
+        <x:v>2493</x:v>
       </x:c>
       <x:c r="D178" s="1" t="s">
-        <x:v>2786</x:v>
+        <x:v>1687</x:v>
       </x:c>
       <x:c r="E178" s="1" t="s">
         <x:v>2576</x:v>
@@ -65969,19 +65978,19 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G178" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H178" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="I178" s="1">
-        <x:v>1761655</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="J178" s="1" t="s">
         <x:v>2579</x:v>
       </x:c>
       <x:c r="K178" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="179" spans="1:11">
@@ -65992,10 +66001,10 @@
         <x:v>2575</x:v>
       </x:c>
       <x:c r="C179" s="1" t="s">
-        <x:v>2785</x:v>
+        <x:v>2788</x:v>
       </x:c>
       <x:c r="D179" s="1" t="s">
-        <x:v>2786</x:v>
+        <x:v>2789</x:v>
       </x:c>
       <x:c r="E179" s="1" t="s">
         <x:v>2576</x:v>
@@ -66010,48 +66019,48 @@
         <x:v>2625</x:v>
       </x:c>
       <x:c r="I179" s="1">
-        <x:v>1010142</x:v>
+        <x:v>1761655</x:v>
       </x:c>
       <x:c r="J179" s="1" t="s">
         <x:v>2579</x:v>
       </x:c>
       <x:c r="K179" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="180" spans="1:11">
       <x:c r="A180" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B180" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C180" s="1" t="s">
-        <x:v>2500</x:v>
+        <x:v>2788</x:v>
       </x:c>
       <x:c r="D180" s="1" t="s">
-        <x:v>736</x:v>
+        <x:v>2789</x:v>
       </x:c>
       <x:c r="E180" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="F180" s="1" t="s">
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G180" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H180" s="1" t="s">
-        <x:v>2656</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="I180" s="1">
-        <x:v>73673</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="J180" s="1" t="s">
         <x:v>2579</x:v>
       </x:c>
       <x:c r="K180" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="181" spans="1:11">
@@ -66062,10 +66071,10 @@
         <x:v>2593</x:v>
       </x:c>
       <x:c r="C181" s="1" t="s">
-        <x:v>2506</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D181" s="1" t="s">
-        <x:v>1919</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="E181" s="1" t="s">
         <x:v>2586</x:v>
@@ -66074,13 +66083,13 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G181" s="1" t="s">
-        <x:v>746</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="H181" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2656</x:v>
       </x:c>
       <x:c r="I181" s="1">
-        <x:v>974633</x:v>
+        <x:v>73673</x:v>
       </x:c>
       <x:c r="J181" s="1" t="s">
         <x:v>2579</x:v>
@@ -66115,56 +66124,56 @@
         <x:v>2591</x:v>
       </x:c>
       <x:c r="I182" s="1">
-        <x:v>1860445</x:v>
+        <x:v>974633</x:v>
       </x:c>
       <x:c r="J182" s="1" t="s">
         <x:v>2579</x:v>
       </x:c>
       <x:c r="K182" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="183" spans="1:11">
       <x:c r="A183" s="1" t="s">
-        <x:v>2598</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B183" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C183" s="1" t="s">
-        <x:v>2514</x:v>
+        <x:v>2506</x:v>
       </x:c>
       <x:c r="D183" s="1" t="s">
-        <x:v>1807</x:v>
+        <x:v>1919</x:v>
       </x:c>
       <x:c r="E183" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="F183" s="1" t="s">
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G183" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="H183" s="1" t="s">
-        <x:v>2656</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I183" s="1">
-        <x:v>600000</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="J183" s="1" t="s">
         <x:v>2579</x:v>
       </x:c>
       <x:c r="K183" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="184" spans="1:11">
       <x:c r="A184" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="B184" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="C184" s="1" t="s">
         <x:v>2514</x:v>
@@ -66185,7 +66194,7 @@
         <x:v>2656</x:v>
       </x:c>
       <x:c r="I184" s="1">
-        <x:v>1419040</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="J184" s="1" t="s">
         <x:v>2579</x:v>
@@ -66220,21 +66229,21 @@
         <x:v>2656</x:v>
       </x:c>
       <x:c r="I185" s="1">
-        <x:v>110148</x:v>
+        <x:v>1419040</x:v>
       </x:c>
       <x:c r="J185" s="1" t="s">
         <x:v>2579</x:v>
       </x:c>
       <x:c r="K185" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="186" spans="1:11">
       <x:c r="A186" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B186" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C186" s="1" t="s">
         <x:v>2514</x:v>
@@ -66255,7 +66264,7 @@
         <x:v>2656</x:v>
       </x:c>
       <x:c r="I186" s="1">
-        <x:v>63084</x:v>
+        <x:v>110148</x:v>
       </x:c>
       <x:c r="J186" s="1" t="s">
         <x:v>2579</x:v>
@@ -66272,10 +66281,10 @@
         <x:v>2617</x:v>
       </x:c>
       <x:c r="C187" s="1" t="s">
-        <x:v>2516</x:v>
+        <x:v>2514</x:v>
       </x:c>
       <x:c r="D187" s="1" t="s">
-        <x:v>543</x:v>
+        <x:v>1807</x:v>
       </x:c>
       <x:c r="E187" s="1" t="s">
         <x:v>2576</x:v>
@@ -66284,153 +66293,153 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G187" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H187" s="1" t="s">
-        <x:v>2776</x:v>
+        <x:v>2656</x:v>
       </x:c>
       <x:c r="I187" s="1">
-        <x:v>1015758</x:v>
+        <x:v>63084</x:v>
       </x:c>
       <x:c r="J187" s="1" t="s">
         <x:v>2579</x:v>
       </x:c>
       <x:c r="K187" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="188" spans="1:11">
       <x:c r="A188" s="1" t="s">
-        <x:v>2642</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="B188" s="1" t="s">
-        <x:v>2643</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="C188" s="1" t="s">
-        <x:v>2787</x:v>
+        <x:v>2516</x:v>
       </x:c>
       <x:c r="D188" s="1" t="s">
-        <x:v>2788</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="E188" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="F188" s="1" t="s">
-        <x:v>2789</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="G188" s="1" t="s">
-        <x:v>2790</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H188" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2779</x:v>
       </x:c>
       <x:c r="I188" s="1">
-        <x:v>10000</x:v>
+        <x:v>1015758</x:v>
       </x:c>
       <x:c r="J188" s="1" t="s">
         <x:v>2579</x:v>
       </x:c>
       <x:c r="K188" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="189" spans="1:11">
       <x:c r="A189" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2642</x:v>
       </x:c>
       <x:c r="B189" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2643</x:v>
       </x:c>
       <x:c r="C189" s="1" t="s">
+        <x:v>2790</x:v>
+      </x:c>
+      <x:c r="D189" s="1" t="s">
         <x:v>2791</x:v>
       </x:c>
-      <x:c r="D189" s="1" t="s">
+      <x:c r="E189" s="1" t="s">
+        <x:v>2586</x:v>
+      </x:c>
+      <x:c r="F189" s="1" t="s">
         <x:v>2792</x:v>
       </x:c>
-      <x:c r="E189" s="1" t="s">
-        <x:v>2576</x:v>
-      </x:c>
-      <x:c r="F189" s="1" t="s">
-        <x:v>2587</x:v>
-      </x:c>
       <x:c r="G189" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>2793</x:v>
       </x:c>
       <x:c r="H189" s="1" t="s">
         <x:v>2588</x:v>
       </x:c>
       <x:c r="I189" s="1">
-        <x:v>424596</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="J189" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2579</x:v>
       </x:c>
       <x:c r="K189" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="190" spans="1:11">
       <x:c r="A190" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="B190" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="C190" s="1" t="s">
-        <x:v>2793</x:v>
+        <x:v>2794</x:v>
       </x:c>
       <x:c r="D190" s="1" t="s">
-        <x:v>2794</x:v>
+        <x:v>2795</x:v>
       </x:c>
       <x:c r="E190" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="F190" s="1" t="s">
-        <x:v>2577</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="G190" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="H190" s="1" t="s">
-        <x:v>2670</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="I190" s="1">
-        <x:v>1306863</x:v>
+        <x:v>424596</x:v>
       </x:c>
       <x:c r="J190" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2610</x:v>
       </x:c>
       <x:c r="K190" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="191" spans="1:11">
       <x:c r="A191" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="B191" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="C191" s="1" t="s">
-        <x:v>2531</x:v>
+        <x:v>2796</x:v>
       </x:c>
       <x:c r="D191" s="1" t="s">
-        <x:v>1858</x:v>
+        <x:v>2797</x:v>
       </x:c>
       <x:c r="E191" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="F191" s="1" t="s">
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G191" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H191" s="1" t="s">
-        <x:v>2665</x:v>
+        <x:v>2670</x:v>
       </x:c>
       <x:c r="I191" s="1">
-        <x:v>889852</x:v>
+        <x:v>1306863</x:v>
       </x:c>
       <x:c r="J191" s="1" t="s">
         <x:v>2579</x:v>
@@ -66447,10 +66456,10 @@
         <x:v>2575</x:v>
       </x:c>
       <x:c r="C192" s="1" t="s">
-        <x:v>2795</x:v>
+        <x:v>2531</x:v>
       </x:c>
       <x:c r="D192" s="1" t="s">
-        <x:v>2796</x:v>
+        <x:v>1858</x:v>
       </x:c>
       <x:c r="E192" s="1" t="s">
         <x:v>2576</x:v>
@@ -66462,45 +66471,45 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="H192" s="1" t="s">
-        <x:v>2753</x:v>
+        <x:v>2665</x:v>
       </x:c>
       <x:c r="I192" s="1">
-        <x:v>1012792</x:v>
+        <x:v>889852</x:v>
       </x:c>
       <x:c r="J192" s="1" t="s">
         <x:v>2579</x:v>
       </x:c>
       <x:c r="K192" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="193" spans="1:11">
       <x:c r="A193" s="1" t="s">
-        <x:v>2598</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B193" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C193" s="1" t="s">
-        <x:v>2539</x:v>
+        <x:v>2798</x:v>
       </x:c>
       <x:c r="D193" s="1" t="s">
-        <x:v>764</x:v>
+        <x:v>2799</x:v>
       </x:c>
       <x:c r="E193" s="1" t="s">
         <x:v>2576</x:v>
       </x:c>
       <x:c r="F193" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="G193" s="1" t="s">
         <x:v>185</x:v>
       </x:c>
       <x:c r="H193" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2756</x:v>
       </x:c>
       <x:c r="I193" s="1">
-        <x:v>300000</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="J193" s="1" t="s">
         <x:v>2579</x:v>
@@ -66511,36 +66520,71 @@
     </x:row>
     <x:row r="194" spans="1:11">
       <x:c r="A194" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="B194" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="C194" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2539</x:v>
       </x:c>
       <x:c r="D194" s="1" t="s">
-        <x:v>836</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="E194" s="1" t="s">
         <x:v>2576</x:v>
       </x:c>
       <x:c r="F194" s="1" t="s">
-        <x:v>2577</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="G194" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="H194" s="1" t="s">
-        <x:v>2678</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="I194" s="1">
-        <x:v>487174</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="J194" s="1" t="s">
         <x:v>2579</x:v>
       </x:c>
       <x:c r="K194" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" spans="1:11">
+      <x:c r="A195" s="1" t="s">
+        <x:v>2574</x:v>
+      </x:c>
+      <x:c r="B195" s="1" t="s">
+        <x:v>2575</x:v>
+      </x:c>
+      <x:c r="C195" s="1" t="s">
+        <x:v>2552</x:v>
+      </x:c>
+      <x:c r="D195" s="1" t="s">
+        <x:v>836</x:v>
+      </x:c>
+      <x:c r="E195" s="1" t="s">
+        <x:v>2576</x:v>
+      </x:c>
+      <x:c r="F195" s="1" t="s">
+        <x:v>2577</x:v>
+      </x:c>
+      <x:c r="G195" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H195" s="1" t="s">
+        <x:v>2678</x:v>
+      </x:c>
+      <x:c r="I195" s="1">
+        <x:v>487174</x:v>
+      </x:c>
+      <x:c r="J195" s="1" t="s">
+        <x:v>2579</x:v>
+      </x:c>
+      <x:c r="K195" s="1">
         <x:v>2026</x:v>
       </x:c>
     </x:row>
@@ -66560,7 +66604,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J180"/>
+  <x:dimension ref="A1:J181"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -67154,10 +67198,10 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>2624</x:v>
@@ -67178,7 +67222,7 @@
         <x:v>2588</x:v>
       </x:c>
       <x:c r="I19" s="1">
-        <x:v>5731065</x:v>
+        <x:v>3465231</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
         <x:v>2610</x:v>
@@ -67186,10 +67230,10 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>2624</x:v>
@@ -67210,7 +67254,7 @@
         <x:v>2588</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>3465231</x:v>
+        <x:v>12894063</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
         <x:v>2610</x:v>
@@ -67218,10 +67262,10 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>2003</x:v>
@@ -67242,7 +67286,7 @@
         <x:v>2625</x:v>
       </x:c>
       <x:c r="I21" s="1">
-        <x:v>83860</x:v>
+        <x:v>582374</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
         <x:v>2579</x:v>
@@ -67250,10 +67294,10 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>2003</x:v>
@@ -67274,7 +67318,7 @@
         <x:v>2625</x:v>
       </x:c>
       <x:c r="I22" s="1">
-        <x:v>582374</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
         <x:v>2579</x:v>
@@ -68050,10 +68094,10 @@
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
         <x:v>2104</x:v>
@@ -68074,7 +68118,7 @@
         <x:v>2602</x:v>
       </x:c>
       <x:c r="I47" s="1">
-        <x:v>76342</x:v>
+        <x:v>118034</x:v>
       </x:c>
       <x:c r="J47" s="1" t="s">
         <x:v>2579</x:v>
@@ -68082,10 +68126,10 @@
     </x:row>
     <x:row r="48" spans="1:10">
       <x:c r="A48" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
         <x:v>2104</x:v>
@@ -68106,7 +68150,7 @@
         <x:v>2602</x:v>
       </x:c>
       <x:c r="I48" s="1">
-        <x:v>118034</x:v>
+        <x:v>76342</x:v>
       </x:c>
       <x:c r="J48" s="1" t="s">
         <x:v>2579</x:v>
@@ -68914,10 +68958,10 @@
     </x:row>
     <x:row r="74" spans="1:10">
       <x:c r="A74" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
         <x:v>2696</x:v>
@@ -68938,7 +68982,7 @@
         <x:v>2588</x:v>
       </x:c>
       <x:c r="I74" s="1">
-        <x:v>1471226</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="J74" s="1" t="s">
         <x:v>2579</x:v>
@@ -68946,10 +68990,10 @@
     </x:row>
     <x:row r="75" spans="1:10">
       <x:c r="A75" s="1" t="s">
-        <x:v>2598</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
         <x:v>2696</x:v>
@@ -68970,7 +69014,7 @@
         <x:v>2588</x:v>
       </x:c>
       <x:c r="I75" s="1">
-        <x:v>600000</x:v>
+        <x:v>1471226</x:v>
       </x:c>
       <x:c r="J75" s="1" t="s">
         <x:v>2579</x:v>
@@ -68978,10 +69022,10 @@
     </x:row>
     <x:row r="76" spans="1:10">
       <x:c r="A76" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
         <x:v>2189</x:v>
@@ -69002,7 +69046,7 @@
         <x:v>2621</x:v>
       </x:c>
       <x:c r="I76" s="1">
-        <x:v>1019964</x:v>
+        <x:v>943006</x:v>
       </x:c>
       <x:c r="J76" s="1" t="s">
         <x:v>2579</x:v>
@@ -69010,10 +69054,10 @@
     </x:row>
     <x:row r="77" spans="1:10">
       <x:c r="A77" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
         <x:v>2189</x:v>
@@ -69034,7 +69078,7 @@
         <x:v>2621</x:v>
       </x:c>
       <x:c r="I77" s="1">
-        <x:v>943006</x:v>
+        <x:v>1019964</x:v>
       </x:c>
       <x:c r="J77" s="1" t="s">
         <x:v>2579</x:v>
@@ -69074,10 +69118,10 @@
     </x:row>
     <x:row r="79" spans="1:10">
       <x:c r="A79" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
         <x:v>2203</x:v>
@@ -69098,7 +69142,7 @@
         <x:v>2591</x:v>
       </x:c>
       <x:c r="I79" s="1">
-        <x:v>1131345</x:v>
+        <x:v>1019167</x:v>
       </x:c>
       <x:c r="J79" s="1" t="s">
         <x:v>2579</x:v>
@@ -69106,10 +69150,10 @@
     </x:row>
     <x:row r="80" spans="1:10">
       <x:c r="A80" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
         <x:v>2203</x:v>
@@ -69130,7 +69174,7 @@
         <x:v>2591</x:v>
       </x:c>
       <x:c r="I80" s="1">
-        <x:v>1019167</x:v>
+        <x:v>1131345</x:v>
       </x:c>
       <x:c r="J80" s="1" t="s">
         <x:v>2579</x:v>
@@ -69194,7 +69238,7 @@
         <x:v>2588</x:v>
       </x:c>
       <x:c r="I82" s="1">
-        <x:v>29079466</x:v>
+        <x:v>33778233</x:v>
       </x:c>
       <x:c r="J82" s="1" t="s">
         <x:v>2579</x:v>
@@ -70322,10 +70366,10 @@
     </x:row>
     <x:row r="118" spans="1:10">
       <x:c r="A118" s="1" t="s">
-        <x:v>2598</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B118" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C118" s="1" t="s">
         <x:v>2734</x:v>
@@ -70346,7 +70390,7 @@
         <x:v>2588</x:v>
       </x:c>
       <x:c r="I118" s="1">
-        <x:v>700000</x:v>
+        <x:v>24457627</x:v>
       </x:c>
       <x:c r="J118" s="1" t="s">
         <x:v>2579</x:v>
@@ -70354,10 +70398,10 @@
     </x:row>
     <x:row r="119" spans="1:10">
       <x:c r="A119" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="B119" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="C119" s="1" t="s">
         <x:v>2734</x:v>
@@ -70378,7 +70422,7 @@
         <x:v>2588</x:v>
       </x:c>
       <x:c r="I119" s="1">
-        <x:v>24457627</x:v>
+        <x:v>700000</x:v>
       </x:c>
       <x:c r="J119" s="1" t="s">
         <x:v>2579</x:v>
@@ -70674,63 +70718,63 @@
     </x:row>
     <x:row r="129" spans="1:10">
       <x:c r="A129" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B129" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C129" s="1" t="s">
-        <x:v>2377</x:v>
+        <x:v>2746</x:v>
       </x:c>
       <x:c r="D129" s="1" t="s">
-        <x:v>1000</x:v>
+        <x:v>2747</x:v>
       </x:c>
       <x:c r="E129" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2748</x:v>
       </x:c>
       <x:c r="F129" s="1" t="s">
-        <x:v>2577</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="G129" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H129" s="1" t="s">
-        <x:v>2746</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="I129" s="1">
-        <x:v>74692</x:v>
+        <x:v>6723910</x:v>
       </x:c>
       <x:c r="J129" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2610</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:10">
       <x:c r="A130" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B130" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C130" s="1" t="s">
-        <x:v>2747</x:v>
+        <x:v>2377</x:v>
       </x:c>
       <x:c r="D130" s="1" t="s">
-        <x:v>2748</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="E130" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="F130" s="1" t="s">
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G130" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H130" s="1" t="s">
-        <x:v>2628</x:v>
+        <x:v>2749</x:v>
       </x:c>
       <x:c r="I130" s="1">
-        <x:v>558813</x:v>
+        <x:v>74692</x:v>
       </x:c>
       <x:c r="J130" s="1" t="s">
         <x:v>2579</x:v>
@@ -70738,31 +70782,31 @@
     </x:row>
     <x:row r="131" spans="1:10">
       <x:c r="A131" s="1" t="s">
-        <x:v>2598</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B131" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C131" s="1" t="s">
-        <x:v>2749</x:v>
+        <x:v>2750</x:v>
       </x:c>
       <x:c r="D131" s="1" t="s">
-        <x:v>2750</x:v>
+        <x:v>2751</x:v>
       </x:c>
       <x:c r="E131" s="1" t="s">
         <x:v>2586</x:v>
       </x:c>
       <x:c r="F131" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="G131" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H131" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2628</x:v>
       </x:c>
       <x:c r="I131" s="1">
-        <x:v>2750000</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="J131" s="1" t="s">
         <x:v>2579</x:v>
@@ -70770,42 +70814,42 @@
     </x:row>
     <x:row r="132" spans="1:10">
       <x:c r="A132" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="B132" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="C132" s="1" t="s">
-        <x:v>2751</x:v>
+        <x:v>2752</x:v>
       </x:c>
       <x:c r="D132" s="1" t="s">
-        <x:v>2752</x:v>
+        <x:v>2753</x:v>
       </x:c>
       <x:c r="E132" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="F132" s="1" t="s">
-        <x:v>2577</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="G132" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H132" s="1" t="s">
-        <x:v>2753</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="I132" s="1">
-        <x:v>20483</x:v>
+        <x:v>2750000</x:v>
       </x:c>
       <x:c r="J132" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2579</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:10">
       <x:c r="A133" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B133" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C133" s="1" t="s">
         <x:v>2754</x:v>
@@ -70820,16 +70864,16 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G133" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="H133" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2756</x:v>
       </x:c>
       <x:c r="I133" s="1">
-        <x:v>1927706</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="J133" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2610</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:10">
@@ -70840,10 +70884,10 @@
         <x:v>2617</x:v>
       </x:c>
       <x:c r="C134" s="1" t="s">
-        <x:v>2756</x:v>
+        <x:v>2757</x:v>
       </x:c>
       <x:c r="D134" s="1" t="s">
-        <x:v>2757</x:v>
+        <x:v>2758</x:v>
       </x:c>
       <x:c r="E134" s="1" t="s">
         <x:v>2576</x:v>
@@ -70852,16 +70896,16 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G134" s="1" t="s">
-        <x:v>222</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H134" s="1" t="s">
-        <x:v>2621</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="I134" s="1">
-        <x:v>817066</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="J134" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2579</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:10">
@@ -70872,10 +70916,10 @@
         <x:v>2617</x:v>
       </x:c>
       <x:c r="C135" s="1" t="s">
-        <x:v>2390</x:v>
+        <x:v>2759</x:v>
       </x:c>
       <x:c r="D135" s="1" t="s">
-        <x:v>269</x:v>
+        <x:v>2760</x:v>
       </x:c>
       <x:c r="E135" s="1" t="s">
         <x:v>2576</x:v>
@@ -70884,45 +70928,45 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G135" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="H135" s="1" t="s">
-        <x:v>2665</x:v>
+        <x:v>2621</x:v>
       </x:c>
       <x:c r="I135" s="1">
-        <x:v>88256</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="J135" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2610</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:10">
       <x:c r="A136" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="B136" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="C136" s="1" t="s">
-        <x:v>2758</x:v>
+        <x:v>2390</x:v>
       </x:c>
       <x:c r="D136" s="1" t="s">
-        <x:v>2759</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="E136" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="F136" s="1" t="s">
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G136" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H136" s="1" t="s">
-        <x:v>2753</x:v>
+        <x:v>2665</x:v>
       </x:c>
       <x:c r="I136" s="1">
-        <x:v>75000</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="J136" s="1" t="s">
         <x:v>2579</x:v>
@@ -70930,95 +70974,95 @@
     </x:row>
     <x:row r="137" spans="1:10">
       <x:c r="A137" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B137" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C137" s="1" t="s">
-        <x:v>2760</x:v>
+        <x:v>2761</x:v>
       </x:c>
       <x:c r="D137" s="1" t="s">
-        <x:v>1088</x:v>
+        <x:v>2762</x:v>
       </x:c>
       <x:c r="E137" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="F137" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="G137" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H137" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2756</x:v>
       </x:c>
       <x:c r="I137" s="1">
-        <x:v>10041119</x:v>
+        <x:v>75000</x:v>
       </x:c>
       <x:c r="J137" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2579</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:10">
       <x:c r="A138" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="B138" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="C138" s="1" t="s">
-        <x:v>2761</x:v>
+        <x:v>2763</x:v>
       </x:c>
       <x:c r="D138" s="1" t="s">
-        <x:v>2762</x:v>
+        <x:v>1088</x:v>
       </x:c>
       <x:c r="E138" s="1" t="s">
         <x:v>2576</x:v>
       </x:c>
       <x:c r="F138" s="1" t="s">
-        <x:v>2577</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="G138" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H138" s="1" t="s">
-        <x:v>2602</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="I138" s="1">
-        <x:v>1491280</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="J138" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2610</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:10">
       <x:c r="A139" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B139" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C139" s="1" t="s">
-        <x:v>2406</x:v>
+        <x:v>2764</x:v>
       </x:c>
       <x:c r="D139" s="1" t="s">
-        <x:v>888</x:v>
+        <x:v>2765</x:v>
       </x:c>
       <x:c r="E139" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="F139" s="1" t="s">
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G139" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H139" s="1" t="s">
-        <x:v>2673</x:v>
+        <x:v>2602</x:v>
       </x:c>
       <x:c r="I139" s="1">
-        <x:v>75844</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="J139" s="1" t="s">
         <x:v>2579</x:v>
@@ -71026,31 +71070,31 @@
     </x:row>
     <x:row r="140" spans="1:10">
       <x:c r="A140" s="1" t="s">
-        <x:v>2598</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B140" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C140" s="1" t="s">
-        <x:v>2410</x:v>
+        <x:v>2406</x:v>
       </x:c>
       <x:c r="D140" s="1" t="s">
-        <x:v>1477</x:v>
+        <x:v>888</x:v>
       </x:c>
       <x:c r="E140" s="1" t="s">
         <x:v>2586</x:v>
       </x:c>
       <x:c r="F140" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="G140" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="H140" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2673</x:v>
       </x:c>
       <x:c r="I140" s="1">
-        <x:v>700000</x:v>
+        <x:v>75844</x:v>
       </x:c>
       <x:c r="J140" s="1" t="s">
         <x:v>2579</x:v>
@@ -71058,16 +71102,16 @@
     </x:row>
     <x:row r="141" spans="1:10">
       <x:c r="A141" s="1" t="s">
-        <x:v>167</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="B141" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="C141" s="1" t="s">
-        <x:v>2763</x:v>
+        <x:v>2410</x:v>
       </x:c>
       <x:c r="D141" s="1" t="s">
-        <x:v>2764</x:v>
+        <x:v>1477</x:v>
       </x:c>
       <x:c r="E141" s="1" t="s">
         <x:v>2586</x:v>
@@ -71076,13 +71120,13 @@
         <x:v>2587</x:v>
       </x:c>
       <x:c r="G141" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H141" s="1" t="s">
         <x:v>2588</x:v>
       </x:c>
       <x:c r="I141" s="1">
-        <x:v>902547</x:v>
+        <x:v>700000</x:v>
       </x:c>
       <x:c r="J141" s="1" t="s">
         <x:v>2579</x:v>
@@ -71090,16 +71134,16 @@
     </x:row>
     <x:row r="142" spans="1:10">
       <x:c r="A142" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B142" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C142" s="1" t="s">
-        <x:v>2424</x:v>
+        <x:v>2766</x:v>
       </x:c>
       <x:c r="D142" s="1" t="s">
-        <x:v>1582</x:v>
+        <x:v>2767</x:v>
       </x:c>
       <x:c r="E142" s="1" t="s">
         <x:v>2586</x:v>
@@ -71108,13 +71152,13 @@
         <x:v>2587</x:v>
       </x:c>
       <x:c r="G142" s="1" t="s">
-        <x:v>733</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H142" s="1" t="s">
         <x:v>2588</x:v>
       </x:c>
       <x:c r="I142" s="1">
-        <x:v>823496</x:v>
+        <x:v>902547</x:v>
       </x:c>
       <x:c r="J142" s="1" t="s">
         <x:v>2579</x:v>
@@ -71128,25 +71172,25 @@
         <x:v>2593</x:v>
       </x:c>
       <x:c r="C143" s="1" t="s">
-        <x:v>2425</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="D143" s="1" t="s">
-        <x:v>493</x:v>
+        <x:v>1582</x:v>
       </x:c>
       <x:c r="E143" s="1" t="s">
         <x:v>2586</x:v>
       </x:c>
       <x:c r="F143" s="1" t="s">
-        <x:v>2577</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="G143" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>733</x:v>
       </x:c>
       <x:c r="H143" s="1" t="s">
-        <x:v>2665</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="I143" s="1">
-        <x:v>75320</x:v>
+        <x:v>823496</x:v>
       </x:c>
       <x:c r="J143" s="1" t="s">
         <x:v>2579</x:v>
@@ -71154,31 +71198,31 @@
     </x:row>
     <x:row r="144" spans="1:10">
       <x:c r="A144" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B144" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C144" s="1" t="s">
-        <x:v>2433</x:v>
+        <x:v>2425</x:v>
       </x:c>
       <x:c r="D144" s="1" t="s">
-        <x:v>1444</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="E144" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="F144" s="1" t="s">
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G144" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H144" s="1" t="s">
-        <x:v>2689</x:v>
+        <x:v>2665</x:v>
       </x:c>
       <x:c r="I144" s="1">
-        <x:v>1987660</x:v>
+        <x:v>75320</x:v>
       </x:c>
       <x:c r="J144" s="1" t="s">
         <x:v>2579</x:v>
@@ -71186,16 +71230,16 @@
     </x:row>
     <x:row r="145" spans="1:10">
       <x:c r="A145" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="B145" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="C145" s="1" t="s">
-        <x:v>2765</x:v>
+        <x:v>2433</x:v>
       </x:c>
       <x:c r="D145" s="1" t="s">
-        <x:v>2766</x:v>
+        <x:v>1444</x:v>
       </x:c>
       <x:c r="E145" s="1" t="s">
         <x:v>2576</x:v>
@@ -71204,13 +71248,13 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G145" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H145" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2689</x:v>
       </x:c>
       <x:c r="I145" s="1">
-        <x:v>74382</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="J145" s="1" t="s">
         <x:v>2579</x:v>
@@ -71224,10 +71268,10 @@
         <x:v>2575</x:v>
       </x:c>
       <x:c r="C146" s="1" t="s">
-        <x:v>2448</x:v>
+        <x:v>2768</x:v>
       </x:c>
       <x:c r="D146" s="1" t="s">
-        <x:v>591</x:v>
+        <x:v>2769</x:v>
       </x:c>
       <x:c r="E146" s="1" t="s">
         <x:v>2576</x:v>
@@ -71236,13 +71280,13 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G146" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H146" s="1" t="s">
-        <x:v>2605</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="I146" s="1">
-        <x:v>105040</x:v>
+        <x:v>74382</x:v>
       </x:c>
       <x:c r="J146" s="1" t="s">
         <x:v>2579</x:v>
@@ -71256,10 +71300,10 @@
         <x:v>2575</x:v>
       </x:c>
       <x:c r="C147" s="1" t="s">
-        <x:v>2451</x:v>
+        <x:v>2448</x:v>
       </x:c>
       <x:c r="D147" s="1" t="s">
-        <x:v>496</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="E147" s="1" t="s">
         <x:v>2576</x:v>
@@ -71268,33 +71312,33 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G147" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H147" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2605</x:v>
       </x:c>
       <x:c r="I147" s="1">
-        <x:v>56045</x:v>
+        <x:v>105040</x:v>
       </x:c>
       <x:c r="J147" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2579</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:10">
       <x:c r="A148" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B148" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C148" s="1" t="s">
-        <x:v>2452</x:v>
+        <x:v>2451</x:v>
       </x:c>
       <x:c r="D148" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="E148" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="F148" s="1" t="s">
         <x:v>2577</x:v>
@@ -71303,13 +71347,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="H148" s="1" t="s">
-        <x:v>2605</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="I148" s="1">
-        <x:v>75281</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="J148" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2610</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:10">
@@ -71320,10 +71364,10 @@
         <x:v>2593</x:v>
       </x:c>
       <x:c r="C149" s="1" t="s">
-        <x:v>2767</x:v>
+        <x:v>2452</x:v>
       </x:c>
       <x:c r="D149" s="1" t="s">
-        <x:v>2768</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="E149" s="1" t="s">
         <x:v>2586</x:v>
@@ -71332,13 +71376,13 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G149" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H149" s="1" t="s">
-        <x:v>2746</x:v>
+        <x:v>2605</x:v>
       </x:c>
       <x:c r="I149" s="1">
-        <x:v>852561</x:v>
+        <x:v>75281</x:v>
       </x:c>
       <x:c r="J149" s="1" t="s">
         <x:v>2579</x:v>
@@ -71346,31 +71390,31 @@
     </x:row>
     <x:row r="150" spans="1:10">
       <x:c r="A150" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B150" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C150" s="1" t="s">
-        <x:v>2458</x:v>
+        <x:v>2770</x:v>
       </x:c>
       <x:c r="D150" s="1" t="s">
-        <x:v>1737</x:v>
+        <x:v>2771</x:v>
       </x:c>
       <x:c r="E150" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="F150" s="1" t="s">
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G150" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H150" s="1" t="s">
-        <x:v>2665</x:v>
+        <x:v>2749</x:v>
       </x:c>
       <x:c r="I150" s="1">
-        <x:v>74852</x:v>
+        <x:v>852561</x:v>
       </x:c>
       <x:c r="J150" s="1" t="s">
         <x:v>2579</x:v>
@@ -71384,10 +71428,10 @@
         <x:v>2575</x:v>
       </x:c>
       <x:c r="C151" s="1" t="s">
-        <x:v>2769</x:v>
+        <x:v>2458</x:v>
       </x:c>
       <x:c r="D151" s="1" t="s">
-        <x:v>2770</x:v>
+        <x:v>1737</x:v>
       </x:c>
       <x:c r="E151" s="1" t="s">
         <x:v>2576</x:v>
@@ -71396,13 +71440,13 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G151" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H151" s="1" t="s">
-        <x:v>2683</x:v>
+        <x:v>2665</x:v>
       </x:c>
       <x:c r="I151" s="1">
-        <x:v>111599</x:v>
+        <x:v>74852</x:v>
       </x:c>
       <x:c r="J151" s="1" t="s">
         <x:v>2579</x:v>
@@ -71416,25 +71460,25 @@
         <x:v>2575</x:v>
       </x:c>
       <x:c r="C152" s="1" t="s">
-        <x:v>2771</x:v>
+        <x:v>2772</x:v>
       </x:c>
       <x:c r="D152" s="1" t="s">
-        <x:v>634</x:v>
+        <x:v>2773</x:v>
       </x:c>
       <x:c r="E152" s="1" t="s">
         <x:v>2576</x:v>
       </x:c>
       <x:c r="F152" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="G152" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H152" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2683</x:v>
       </x:c>
       <x:c r="I152" s="1">
-        <x:v>10046680</x:v>
+        <x:v>111599</x:v>
       </x:c>
       <x:c r="J152" s="1" t="s">
         <x:v>2579</x:v>
@@ -71442,31 +71486,31 @@
     </x:row>
     <x:row r="153" spans="1:10">
       <x:c r="A153" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B153" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C153" s="1" t="s">
-        <x:v>2470</x:v>
+        <x:v>2774</x:v>
       </x:c>
       <x:c r="D153" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="E153" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="F153" s="1" t="s">
-        <x:v>2577</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="G153" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H153" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="I153" s="1">
-        <x:v>565950</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="J153" s="1" t="s">
         <x:v>2579</x:v>
@@ -71480,10 +71524,10 @@
         <x:v>2593</x:v>
       </x:c>
       <x:c r="C154" s="1" t="s">
-        <x:v>2473</x:v>
+        <x:v>2470</x:v>
       </x:c>
       <x:c r="D154" s="1" t="s">
-        <x:v>966</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E154" s="1" t="s">
         <x:v>2586</x:v>
@@ -71492,13 +71536,13 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G154" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H154" s="1" t="s">
-        <x:v>2605</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="I154" s="1">
-        <x:v>75617</x:v>
+        <x:v>565950</x:v>
       </x:c>
       <x:c r="J154" s="1" t="s">
         <x:v>2579</x:v>
@@ -71506,31 +71550,31 @@
     </x:row>
     <x:row r="155" spans="1:10">
       <x:c r="A155" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B155" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C155" s="1" t="s">
-        <x:v>2772</x:v>
+        <x:v>2473</x:v>
       </x:c>
       <x:c r="D155" s="1" t="s">
-        <x:v>2773</x:v>
+        <x:v>966</x:v>
       </x:c>
       <x:c r="E155" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="F155" s="1" t="s">
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G155" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H155" s="1" t="s">
-        <x:v>2615</x:v>
+        <x:v>2605</x:v>
       </x:c>
       <x:c r="I155" s="1">
-        <x:v>380377</x:v>
+        <x:v>75617</x:v>
       </x:c>
       <x:c r="J155" s="1" t="s">
         <x:v>2579</x:v>
@@ -71538,16 +71582,16 @@
     </x:row>
     <x:row r="156" spans="1:10">
       <x:c r="A156" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B156" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C156" s="1" t="s">
-        <x:v>2476</x:v>
+        <x:v>2775</x:v>
       </x:c>
       <x:c r="D156" s="1" t="s">
-        <x:v>655</x:v>
+        <x:v>2776</x:v>
       </x:c>
       <x:c r="E156" s="1" t="s">
         <x:v>2576</x:v>
@@ -71556,13 +71600,13 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G156" s="1" t="s">
-        <x:v>222</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H156" s="1" t="s">
-        <x:v>2704</x:v>
+        <x:v>2615</x:v>
       </x:c>
       <x:c r="I156" s="1">
-        <x:v>817169</x:v>
+        <x:v>380377</x:v>
       </x:c>
       <x:c r="J156" s="1" t="s">
         <x:v>2579</x:v>
@@ -71570,95 +71614,95 @@
     </x:row>
     <x:row r="157" spans="1:10">
       <x:c r="A157" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="B157" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="C157" s="1" t="s">
-        <x:v>2774</x:v>
+        <x:v>2476</x:v>
       </x:c>
       <x:c r="D157" s="1" t="s">
-        <x:v>2775</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="E157" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="F157" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="G157" s="1" t="s">
-        <x:v>238</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="H157" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2704</x:v>
       </x:c>
       <x:c r="I157" s="1">
-        <x:v>1531015</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="J157" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2579</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:10">
       <x:c r="A158" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B158" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C158" s="1" t="s">
-        <x:v>2482</x:v>
+        <x:v>2777</x:v>
       </x:c>
       <x:c r="D158" s="1" t="s">
-        <x:v>1666</x:v>
+        <x:v>2778</x:v>
       </x:c>
       <x:c r="E158" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="F158" s="1" t="s">
-        <x:v>2577</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="G158" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="H158" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="I158" s="1">
-        <x:v>157560</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="J158" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2610</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:10">
       <x:c r="A159" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B159" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C159" s="1" t="s">
-        <x:v>2484</x:v>
+        <x:v>2482</x:v>
       </x:c>
       <x:c r="D159" s="1" t="s">
-        <x:v>1323</x:v>
+        <x:v>1666</x:v>
       </x:c>
       <x:c r="E159" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="F159" s="1" t="s">
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G159" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H159" s="1" t="s">
-        <x:v>2776</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I159" s="1">
-        <x:v>2791716</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="J159" s="1" t="s">
         <x:v>2579</x:v>
@@ -71672,10 +71716,10 @@
         <x:v>2617</x:v>
       </x:c>
       <x:c r="C160" s="1" t="s">
-        <x:v>2486</x:v>
+        <x:v>2484</x:v>
       </x:c>
       <x:c r="D160" s="1" t="s">
-        <x:v>1669</x:v>
+        <x:v>1323</x:v>
       </x:c>
       <x:c r="E160" s="1" t="s">
         <x:v>2586</x:v>
@@ -71684,13 +71728,13 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G160" s="1" t="s">
-        <x:v>601</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H160" s="1" t="s">
-        <x:v>2628</x:v>
+        <x:v>2779</x:v>
       </x:c>
       <x:c r="I160" s="1">
-        <x:v>1789991</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="J160" s="1" t="s">
         <x:v>2579</x:v>
@@ -71698,16 +71742,16 @@
     </x:row>
     <x:row r="161" spans="1:10">
       <x:c r="A161" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="B161" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="C161" s="1" t="s">
-        <x:v>2777</x:v>
+        <x:v>2486</x:v>
       </x:c>
       <x:c r="D161" s="1" t="s">
-        <x:v>2778</x:v>
+        <x:v>1669</x:v>
       </x:c>
       <x:c r="E161" s="1" t="s">
         <x:v>2586</x:v>
@@ -71716,13 +71760,13 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G161" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="H161" s="1" t="s">
-        <x:v>2605</x:v>
+        <x:v>2628</x:v>
       </x:c>
       <x:c r="I161" s="1">
-        <x:v>1543316</x:v>
+        <x:v>1789991</x:v>
       </x:c>
       <x:c r="J161" s="1" t="s">
         <x:v>2579</x:v>
@@ -71730,34 +71774,34 @@
     </x:row>
     <x:row r="162" spans="1:10">
       <x:c r="A162" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B162" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C162" s="1" t="s">
-        <x:v>2779</x:v>
+        <x:v>2780</x:v>
       </x:c>
       <x:c r="D162" s="1" t="s">
-        <x:v>2780</x:v>
+        <x:v>2781</x:v>
       </x:c>
       <x:c r="E162" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="F162" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="G162" s="1" t="s">
-        <x:v>222</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H162" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2605</x:v>
       </x:c>
       <x:c r="I162" s="1">
-        <x:v>10015605</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="J162" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2579</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:10">
@@ -71768,10 +71812,10 @@
         <x:v>2575</x:v>
       </x:c>
       <x:c r="C163" s="1" t="s">
-        <x:v>2779</x:v>
+        <x:v>2782</x:v>
       </x:c>
       <x:c r="D163" s="1" t="s">
-        <x:v>2780</x:v>
+        <x:v>2783</x:v>
       </x:c>
       <x:c r="E163" s="1" t="s">
         <x:v>2576</x:v>
@@ -71794,34 +71838,34 @@
     </x:row>
     <x:row r="164" spans="1:10">
       <x:c r="A164" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="B164" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="C164" s="1" t="s">
-        <x:v>2781</x:v>
+        <x:v>2782</x:v>
       </x:c>
       <x:c r="D164" s="1" t="s">
-        <x:v>2782</x:v>
+        <x:v>2783</x:v>
       </x:c>
       <x:c r="E164" s="1" t="s">
         <x:v>2576</x:v>
       </x:c>
       <x:c r="F164" s="1" t="s">
-        <x:v>2577</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="G164" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="H164" s="1" t="s">
-        <x:v>2676</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="I164" s="1">
-        <x:v>103020</x:v>
+        <x:v>10015605</x:v>
       </x:c>
       <x:c r="J164" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2610</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:10">
@@ -71832,10 +71876,10 @@
         <x:v>2575</x:v>
       </x:c>
       <x:c r="C165" s="1" t="s">
-        <x:v>2783</x:v>
+        <x:v>2784</x:v>
       </x:c>
       <x:c r="D165" s="1" t="s">
-        <x:v>2784</x:v>
+        <x:v>2785</x:v>
       </x:c>
       <x:c r="E165" s="1" t="s">
         <x:v>2576</x:v>
@@ -71844,13 +71888,13 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G165" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H165" s="1" t="s">
         <x:v>2676</x:v>
       </x:c>
       <x:c r="I165" s="1">
-        <x:v>182279</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="J165" s="1" t="s">
         <x:v>2579</x:v>
@@ -71858,16 +71902,16 @@
     </x:row>
     <x:row r="166" spans="1:10">
       <x:c r="A166" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B166" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C166" s="1" t="s">
-        <x:v>2493</x:v>
+        <x:v>2786</x:v>
       </x:c>
       <x:c r="D166" s="1" t="s">
-        <x:v>1687</x:v>
+        <x:v>2787</x:v>
       </x:c>
       <x:c r="E166" s="1" t="s">
         <x:v>2576</x:v>
@@ -71876,13 +71920,13 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G166" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="H166" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2676</x:v>
       </x:c>
       <x:c r="I166" s="1">
-        <x:v>902176</x:v>
+        <x:v>182279</x:v>
       </x:c>
       <x:c r="J166" s="1" t="s">
         <x:v>2579</x:v>
@@ -71890,16 +71934,16 @@
     </x:row>
     <x:row r="167" spans="1:10">
       <x:c r="A167" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="B167" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="C167" s="1" t="s">
-        <x:v>2785</x:v>
+        <x:v>2493</x:v>
       </x:c>
       <x:c r="D167" s="1" t="s">
-        <x:v>2786</x:v>
+        <x:v>1687</x:v>
       </x:c>
       <x:c r="E167" s="1" t="s">
         <x:v>2576</x:v>
@@ -71908,13 +71952,13 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G167" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H167" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="I167" s="1">
-        <x:v>2771797</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="J167" s="1" t="s">
         <x:v>2579</x:v>
@@ -71922,31 +71966,31 @@
     </x:row>
     <x:row r="168" spans="1:10">
       <x:c r="A168" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B168" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C168" s="1" t="s">
-        <x:v>2500</x:v>
+        <x:v>2788</x:v>
       </x:c>
       <x:c r="D168" s="1" t="s">
-        <x:v>736</x:v>
+        <x:v>2789</x:v>
       </x:c>
       <x:c r="E168" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="F168" s="1" t="s">
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G168" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H168" s="1" t="s">
-        <x:v>2656</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="I168" s="1">
-        <x:v>73673</x:v>
+        <x:v>2771797</x:v>
       </x:c>
       <x:c r="J168" s="1" t="s">
         <x:v>2579</x:v>
@@ -71960,10 +72004,10 @@
         <x:v>2593</x:v>
       </x:c>
       <x:c r="C169" s="1" t="s">
-        <x:v>2506</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D169" s="1" t="s">
-        <x:v>1919</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="E169" s="1" t="s">
         <x:v>2586</x:v>
@@ -71972,13 +72016,13 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G169" s="1" t="s">
-        <x:v>746</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="H169" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2656</x:v>
       </x:c>
       <x:c r="I169" s="1">
-        <x:v>2835078</x:v>
+        <x:v>73673</x:v>
       </x:c>
       <x:c r="J169" s="1" t="s">
         <x:v>2579</x:v>
@@ -71986,31 +72030,31 @@
     </x:row>
     <x:row r="170" spans="1:10">
       <x:c r="A170" s="1" t="s">
-        <x:v>2598</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B170" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C170" s="1" t="s">
-        <x:v>2514</x:v>
+        <x:v>2506</x:v>
       </x:c>
       <x:c r="D170" s="1" t="s">
-        <x:v>1807</x:v>
+        <x:v>1919</x:v>
       </x:c>
       <x:c r="E170" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="F170" s="1" t="s">
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G170" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="H170" s="1" t="s">
-        <x:v>2656</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I170" s="1">
-        <x:v>600000</x:v>
+        <x:v>2835078</x:v>
       </x:c>
       <x:c r="J170" s="1" t="s">
         <x:v>2579</x:v>
@@ -72018,10 +72062,10 @@
     </x:row>
     <x:row r="171" spans="1:10">
       <x:c r="A171" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="B171" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="C171" s="1" t="s">
         <x:v>2514</x:v>
@@ -72042,7 +72086,7 @@
         <x:v>2656</x:v>
       </x:c>
       <x:c r="I171" s="1">
-        <x:v>1529188</x:v>
+        <x:v>63084</x:v>
       </x:c>
       <x:c r="J171" s="1" t="s">
         <x:v>2579</x:v>
@@ -72050,10 +72094,10 @@
     </x:row>
     <x:row r="172" spans="1:10">
       <x:c r="A172" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="B172" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="C172" s="1" t="s">
         <x:v>2514</x:v>
@@ -72074,7 +72118,7 @@
         <x:v>2656</x:v>
       </x:c>
       <x:c r="I172" s="1">
-        <x:v>63084</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="J172" s="1" t="s">
         <x:v>2579</x:v>
@@ -72082,16 +72126,16 @@
     </x:row>
     <x:row r="173" spans="1:10">
       <x:c r="A173" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B173" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C173" s="1" t="s">
-        <x:v>2516</x:v>
+        <x:v>2514</x:v>
       </x:c>
       <x:c r="D173" s="1" t="s">
-        <x:v>543</x:v>
+        <x:v>1807</x:v>
       </x:c>
       <x:c r="E173" s="1" t="s">
         <x:v>2576</x:v>
@@ -72100,13 +72144,13 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G173" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H173" s="1" t="s">
-        <x:v>2776</x:v>
+        <x:v>2656</x:v>
       </x:c>
       <x:c r="I173" s="1">
-        <x:v>1015758</x:v>
+        <x:v>1529188</x:v>
       </x:c>
       <x:c r="J173" s="1" t="s">
         <x:v>2579</x:v>
@@ -72114,31 +72158,31 @@
     </x:row>
     <x:row r="174" spans="1:10">
       <x:c r="A174" s="1" t="s">
-        <x:v>2642</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="B174" s="1" t="s">
-        <x:v>2643</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="C174" s="1" t="s">
-        <x:v>2787</x:v>
+        <x:v>2516</x:v>
       </x:c>
       <x:c r="D174" s="1" t="s">
-        <x:v>2788</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="E174" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="F174" s="1" t="s">
-        <x:v>2789</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="G174" s="1" t="s">
-        <x:v>2790</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H174" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2779</x:v>
       </x:c>
       <x:c r="I174" s="1">
-        <x:v>10000</x:v>
+        <x:v>1015758</x:v>
       </x:c>
       <x:c r="J174" s="1" t="s">
         <x:v>2579</x:v>
@@ -72146,95 +72190,95 @@
     </x:row>
     <x:row r="175" spans="1:10">
       <x:c r="A175" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2642</x:v>
       </x:c>
       <x:c r="B175" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2643</x:v>
       </x:c>
       <x:c r="C175" s="1" t="s">
+        <x:v>2790</x:v>
+      </x:c>
+      <x:c r="D175" s="1" t="s">
         <x:v>2791</x:v>
       </x:c>
-      <x:c r="D175" s="1" t="s">
+      <x:c r="E175" s="1" t="s">
+        <x:v>2586</x:v>
+      </x:c>
+      <x:c r="F175" s="1" t="s">
         <x:v>2792</x:v>
       </x:c>
-      <x:c r="E175" s="1" t="s">
-        <x:v>2576</x:v>
-      </x:c>
-      <x:c r="F175" s="1" t="s">
-        <x:v>2587</x:v>
-      </x:c>
       <x:c r="G175" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>2793</x:v>
       </x:c>
       <x:c r="H175" s="1" t="s">
         <x:v>2588</x:v>
       </x:c>
       <x:c r="I175" s="1">
-        <x:v>424596</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="J175" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2579</x:v>
       </x:c>
     </x:row>
     <x:row r="176" spans="1:10">
       <x:c r="A176" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="B176" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="C176" s="1" t="s">
-        <x:v>2793</x:v>
+        <x:v>2794</x:v>
       </x:c>
       <x:c r="D176" s="1" t="s">
-        <x:v>2794</x:v>
+        <x:v>2795</x:v>
       </x:c>
       <x:c r="E176" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="F176" s="1" t="s">
-        <x:v>2577</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="G176" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="H176" s="1" t="s">
-        <x:v>2670</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="I176" s="1">
-        <x:v>1306863</x:v>
+        <x:v>424596</x:v>
       </x:c>
       <x:c r="J176" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2610</x:v>
       </x:c>
     </x:row>
     <x:row r="177" spans="1:10">
       <x:c r="A177" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="B177" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="C177" s="1" t="s">
-        <x:v>2531</x:v>
+        <x:v>2796</x:v>
       </x:c>
       <x:c r="D177" s="1" t="s">
-        <x:v>1858</x:v>
+        <x:v>2797</x:v>
       </x:c>
       <x:c r="E177" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="F177" s="1" t="s">
         <x:v>2577</x:v>
       </x:c>
       <x:c r="G177" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H177" s="1" t="s">
-        <x:v>2665</x:v>
+        <x:v>2670</x:v>
       </x:c>
       <x:c r="I177" s="1">
-        <x:v>889852</x:v>
+        <x:v>1306863</x:v>
       </x:c>
       <x:c r="J177" s="1" t="s">
         <x:v>2579</x:v>
@@ -72248,10 +72292,10 @@
         <x:v>2575</x:v>
       </x:c>
       <x:c r="C178" s="1" t="s">
-        <x:v>2795</x:v>
+        <x:v>2531</x:v>
       </x:c>
       <x:c r="D178" s="1" t="s">
-        <x:v>2796</x:v>
+        <x:v>1858</x:v>
       </x:c>
       <x:c r="E178" s="1" t="s">
         <x:v>2576</x:v>
@@ -72263,10 +72307,10 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="H178" s="1" t="s">
-        <x:v>2753</x:v>
+        <x:v>2665</x:v>
       </x:c>
       <x:c r="I178" s="1">
-        <x:v>1012792</x:v>
+        <x:v>889852</x:v>
       </x:c>
       <x:c r="J178" s="1" t="s">
         <x:v>2579</x:v>
@@ -72274,31 +72318,31 @@
     </x:row>
     <x:row r="179" spans="1:10">
       <x:c r="A179" s="1" t="s">
-        <x:v>2598</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B179" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C179" s="1" t="s">
-        <x:v>2539</x:v>
+        <x:v>2798</x:v>
       </x:c>
       <x:c r="D179" s="1" t="s">
-        <x:v>764</x:v>
+        <x:v>2799</x:v>
       </x:c>
       <x:c r="E179" s="1" t="s">
         <x:v>2576</x:v>
       </x:c>
       <x:c r="F179" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="G179" s="1" t="s">
         <x:v>185</x:v>
       </x:c>
       <x:c r="H179" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2756</x:v>
       </x:c>
       <x:c r="I179" s="1">
-        <x:v>300000</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="J179" s="1" t="s">
         <x:v>2579</x:v>
@@ -72306,33 +72350,65 @@
     </x:row>
     <x:row r="180" spans="1:10">
       <x:c r="A180" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="B180" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="C180" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2539</x:v>
       </x:c>
       <x:c r="D180" s="1" t="s">
-        <x:v>836</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="E180" s="1" t="s">
         <x:v>2576</x:v>
       </x:c>
       <x:c r="F180" s="1" t="s">
+        <x:v>2587</x:v>
+      </x:c>
+      <x:c r="G180" s="1" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="H180" s="1" t="s">
+        <x:v>2588</x:v>
+      </x:c>
+      <x:c r="I180" s="1">
+        <x:v>300000</x:v>
+      </x:c>
+      <x:c r="J180" s="1" t="s">
+        <x:v>2579</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" spans="1:10">
+      <x:c r="A181" s="1" t="s">
+        <x:v>2574</x:v>
+      </x:c>
+      <x:c r="B181" s="1" t="s">
+        <x:v>2575</x:v>
+      </x:c>
+      <x:c r="C181" s="1" t="s">
+        <x:v>2552</x:v>
+      </x:c>
+      <x:c r="D181" s="1" t="s">
+        <x:v>836</x:v>
+      </x:c>
+      <x:c r="E181" s="1" t="s">
+        <x:v>2576</x:v>
+      </x:c>
+      <x:c r="F181" s="1" t="s">
         <x:v>2577</x:v>
       </x:c>
-      <x:c r="G180" s="1" t="s">
+      <x:c r="G181" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H180" s="1" t="s">
+      <x:c r="H181" s="1" t="s">
         <x:v>2678</x:v>
       </x:c>
-      <x:c r="I180" s="1">
+      <x:c r="I181" s="1">
         <x:v>487174</x:v>
       </x:c>
-      <x:c r="J180" s="1" t="s">
+      <x:c r="J181" s="1" t="s">
         <x:v>2579</x:v>
       </x:c>
     </x:row>
@@ -72352,7 +72428,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C165"/>
+  <x:dimension ref="A1:C166"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -72553,7 +72629,7 @@
         <x:v>555</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>9196296</x:v>
+        <x:v>16359294</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>2610</x:v>
@@ -73147,7 +73223,7 @@
         <x:v>936</x:v>
       </x:c>
       <x:c r="B72" s="1">
-        <x:v>31554631</x:v>
+        <x:v>36253398</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
         <x:v>2579</x:v>
@@ -73639,21 +73715,21 @@
     </x:row>
     <x:row r="117" spans="1:3">
       <x:c r="A117" s="1" t="s">
-        <x:v>1000</x:v>
+        <x:v>2747</x:v>
       </x:c>
       <x:c r="B117" s="1">
-        <x:v>74692</x:v>
+        <x:v>6723910</x:v>
       </x:c>
       <x:c r="C117" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2610</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:3">
       <x:c r="A118" s="1" t="s">
-        <x:v>2748</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="B118" s="1">
-        <x:v>558813</x:v>
+        <x:v>74692</x:v>
       </x:c>
       <x:c r="C118" s="1" t="s">
         <x:v>2579</x:v>
@@ -73661,10 +73737,10 @@
     </x:row>
     <x:row r="119" spans="1:3">
       <x:c r="A119" s="1" t="s">
-        <x:v>2750</x:v>
+        <x:v>2751</x:v>
       </x:c>
       <x:c r="B119" s="1">
-        <x:v>2750000</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="C119" s="1" t="s">
         <x:v>2579</x:v>
@@ -73672,13 +73748,13 @@
     </x:row>
     <x:row r="120" spans="1:3">
       <x:c r="A120" s="1" t="s">
-        <x:v>2752</x:v>
+        <x:v>2753</x:v>
       </x:c>
       <x:c r="B120" s="1">
-        <x:v>20483</x:v>
+        <x:v>2750000</x:v>
       </x:c>
       <x:c r="C120" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2579</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:3">
@@ -73686,40 +73762,40 @@
         <x:v>2755</x:v>
       </x:c>
       <x:c r="B121" s="1">
-        <x:v>1927706</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="C121" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2610</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:3">
       <x:c r="A122" s="1" t="s">
-        <x:v>2757</x:v>
+        <x:v>2758</x:v>
       </x:c>
       <x:c r="B122" s="1">
-        <x:v>817066</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="C122" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2579</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:3">
       <x:c r="A123" s="1" t="s">
-        <x:v>269</x:v>
+        <x:v>2760</x:v>
       </x:c>
       <x:c r="B123" s="1">
-        <x:v>88256</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="C123" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2610</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:3">
       <x:c r="A124" s="1" t="s">
-        <x:v>2759</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B124" s="1">
-        <x:v>75000</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="C124" s="1" t="s">
         <x:v>2579</x:v>
@@ -73727,32 +73803,32 @@
     </x:row>
     <x:row r="125" spans="1:3">
       <x:c r="A125" s="1" t="s">
-        <x:v>1088</x:v>
+        <x:v>2762</x:v>
       </x:c>
       <x:c r="B125" s="1">
-        <x:v>10041119</x:v>
+        <x:v>75000</x:v>
       </x:c>
       <x:c r="C125" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2579</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:3">
       <x:c r="A126" s="1" t="s">
-        <x:v>2762</x:v>
+        <x:v>1088</x:v>
       </x:c>
       <x:c r="B126" s="1">
-        <x:v>1491280</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="C126" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2610</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:3">
       <x:c r="A127" s="1" t="s">
-        <x:v>888</x:v>
+        <x:v>2765</x:v>
       </x:c>
       <x:c r="B127" s="1">
-        <x:v>75844</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="C127" s="1" t="s">
         <x:v>2579</x:v>
@@ -73760,10 +73836,10 @@
     </x:row>
     <x:row r="128" spans="1:3">
       <x:c r="A128" s="1" t="s">
-        <x:v>1477</x:v>
+        <x:v>888</x:v>
       </x:c>
       <x:c r="B128" s="1">
-        <x:v>700000</x:v>
+        <x:v>75844</x:v>
       </x:c>
       <x:c r="C128" s="1" t="s">
         <x:v>2579</x:v>
@@ -73771,10 +73847,10 @@
     </x:row>
     <x:row r="129" spans="1:3">
       <x:c r="A129" s="1" t="s">
-        <x:v>2764</x:v>
+        <x:v>1477</x:v>
       </x:c>
       <x:c r="B129" s="1">
-        <x:v>902547</x:v>
+        <x:v>700000</x:v>
       </x:c>
       <x:c r="C129" s="1" t="s">
         <x:v>2579</x:v>
@@ -73782,10 +73858,10 @@
     </x:row>
     <x:row r="130" spans="1:3">
       <x:c r="A130" s="1" t="s">
-        <x:v>1582</x:v>
+        <x:v>2767</x:v>
       </x:c>
       <x:c r="B130" s="1">
-        <x:v>823496</x:v>
+        <x:v>902547</x:v>
       </x:c>
       <x:c r="C130" s="1" t="s">
         <x:v>2579</x:v>
@@ -73793,10 +73869,10 @@
     </x:row>
     <x:row r="131" spans="1:3">
       <x:c r="A131" s="1" t="s">
-        <x:v>493</x:v>
+        <x:v>1582</x:v>
       </x:c>
       <x:c r="B131" s="1">
-        <x:v>75320</x:v>
+        <x:v>823496</x:v>
       </x:c>
       <x:c r="C131" s="1" t="s">
         <x:v>2579</x:v>
@@ -73804,10 +73880,10 @@
     </x:row>
     <x:row r="132" spans="1:3">
       <x:c r="A132" s="1" t="s">
-        <x:v>1444</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="B132" s="1">
-        <x:v>1987660</x:v>
+        <x:v>75320</x:v>
       </x:c>
       <x:c r="C132" s="1" t="s">
         <x:v>2579</x:v>
@@ -73815,10 +73891,10 @@
     </x:row>
     <x:row r="133" spans="1:3">
       <x:c r="A133" s="1" t="s">
-        <x:v>2766</x:v>
+        <x:v>1444</x:v>
       </x:c>
       <x:c r="B133" s="1">
-        <x:v>74382</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="C133" s="1" t="s">
         <x:v>2579</x:v>
@@ -73826,10 +73902,10 @@
     </x:row>
     <x:row r="134" spans="1:3">
       <x:c r="A134" s="1" t="s">
-        <x:v>591</x:v>
+        <x:v>2769</x:v>
       </x:c>
       <x:c r="B134" s="1">
-        <x:v>105040</x:v>
+        <x:v>74382</x:v>
       </x:c>
       <x:c r="C134" s="1" t="s">
         <x:v>2579</x:v>
@@ -73837,32 +73913,32 @@
     </x:row>
     <x:row r="135" spans="1:3">
       <x:c r="A135" s="1" t="s">
-        <x:v>496</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="B135" s="1">
-        <x:v>56045</x:v>
+        <x:v>105040</x:v>
       </x:c>
       <x:c r="C135" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2579</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:3">
       <x:c r="A136" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="B136" s="1">
-        <x:v>75281</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="C136" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2610</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:3">
       <x:c r="A137" s="1" t="s">
-        <x:v>2768</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B137" s="1">
-        <x:v>852561</x:v>
+        <x:v>75281</x:v>
       </x:c>
       <x:c r="C137" s="1" t="s">
         <x:v>2579</x:v>
@@ -73870,10 +73946,10 @@
     </x:row>
     <x:row r="138" spans="1:3">
       <x:c r="A138" s="1" t="s">
-        <x:v>1737</x:v>
+        <x:v>2771</x:v>
       </x:c>
       <x:c r="B138" s="1">
-        <x:v>74852</x:v>
+        <x:v>852561</x:v>
       </x:c>
       <x:c r="C138" s="1" t="s">
         <x:v>2579</x:v>
@@ -73881,10 +73957,10 @@
     </x:row>
     <x:row r="139" spans="1:3">
       <x:c r="A139" s="1" t="s">
-        <x:v>2770</x:v>
+        <x:v>1737</x:v>
       </x:c>
       <x:c r="B139" s="1">
-        <x:v>111599</x:v>
+        <x:v>74852</x:v>
       </x:c>
       <x:c r="C139" s="1" t="s">
         <x:v>2579</x:v>
@@ -73892,10 +73968,10 @@
     </x:row>
     <x:row r="140" spans="1:3">
       <x:c r="A140" s="1" t="s">
-        <x:v>634</x:v>
+        <x:v>2773</x:v>
       </x:c>
       <x:c r="B140" s="1">
-        <x:v>10046680</x:v>
+        <x:v>111599</x:v>
       </x:c>
       <x:c r="C140" s="1" t="s">
         <x:v>2579</x:v>
@@ -73903,10 +73979,10 @@
     </x:row>
     <x:row r="141" spans="1:3">
       <x:c r="A141" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="B141" s="1">
-        <x:v>565950</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="C141" s="1" t="s">
         <x:v>2579</x:v>
@@ -73914,10 +73990,10 @@
     </x:row>
     <x:row r="142" spans="1:3">
       <x:c r="A142" s="1" t="s">
-        <x:v>966</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B142" s="1">
-        <x:v>75617</x:v>
+        <x:v>565950</x:v>
       </x:c>
       <x:c r="C142" s="1" t="s">
         <x:v>2579</x:v>
@@ -73925,10 +74001,10 @@
     </x:row>
     <x:row r="143" spans="1:3">
       <x:c r="A143" s="1" t="s">
-        <x:v>2773</x:v>
+        <x:v>966</x:v>
       </x:c>
       <x:c r="B143" s="1">
-        <x:v>380377</x:v>
+        <x:v>75617</x:v>
       </x:c>
       <x:c r="C143" s="1" t="s">
         <x:v>2579</x:v>
@@ -73936,10 +74012,10 @@
     </x:row>
     <x:row r="144" spans="1:3">
       <x:c r="A144" s="1" t="s">
-        <x:v>655</x:v>
+        <x:v>2776</x:v>
       </x:c>
       <x:c r="B144" s="1">
-        <x:v>817169</x:v>
+        <x:v>380377</x:v>
       </x:c>
       <x:c r="C144" s="1" t="s">
         <x:v>2579</x:v>
@@ -73947,32 +74023,32 @@
     </x:row>
     <x:row r="145" spans="1:3">
       <x:c r="A145" s="1" t="s">
-        <x:v>2775</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="B145" s="1">
-        <x:v>1531015</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="C145" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2579</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:3">
       <x:c r="A146" s="1" t="s">
-        <x:v>1666</x:v>
+        <x:v>2778</x:v>
       </x:c>
       <x:c r="B146" s="1">
-        <x:v>157560</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="C146" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2610</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:3">
       <x:c r="A147" s="1" t="s">
-        <x:v>1323</x:v>
+        <x:v>1666</x:v>
       </x:c>
       <x:c r="B147" s="1">
-        <x:v>2791716</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="C147" s="1" t="s">
         <x:v>2579</x:v>
@@ -73980,10 +74056,10 @@
     </x:row>
     <x:row r="148" spans="1:3">
       <x:c r="A148" s="1" t="s">
-        <x:v>1669</x:v>
+        <x:v>1323</x:v>
       </x:c>
       <x:c r="B148" s="1">
-        <x:v>1789991</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="C148" s="1" t="s">
         <x:v>2579</x:v>
@@ -73991,10 +74067,10 @@
     </x:row>
     <x:row r="149" spans="1:3">
       <x:c r="A149" s="1" t="s">
-        <x:v>2778</x:v>
+        <x:v>1669</x:v>
       </x:c>
       <x:c r="B149" s="1">
-        <x:v>1543316</x:v>
+        <x:v>1789991</x:v>
       </x:c>
       <x:c r="C149" s="1" t="s">
         <x:v>2579</x:v>
@@ -74002,32 +74078,32 @@
     </x:row>
     <x:row r="150" spans="1:3">
       <x:c r="A150" s="1" t="s">
-        <x:v>2780</x:v>
+        <x:v>2781</x:v>
       </x:c>
       <x:c r="B150" s="1">
-        <x:v>10135449</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="C150" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2579</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:3">
       <x:c r="A151" s="1" t="s">
-        <x:v>2782</x:v>
+        <x:v>2783</x:v>
       </x:c>
       <x:c r="B151" s="1">
-        <x:v>103020</x:v>
+        <x:v>10135449</x:v>
       </x:c>
       <x:c r="C151" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2610</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:3">
       <x:c r="A152" s="1" t="s">
-        <x:v>2784</x:v>
+        <x:v>2785</x:v>
       </x:c>
       <x:c r="B152" s="1">
-        <x:v>182279</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="C152" s="1" t="s">
         <x:v>2579</x:v>
@@ -74035,10 +74111,10 @@
     </x:row>
     <x:row r="153" spans="1:3">
       <x:c r="A153" s="1" t="s">
-        <x:v>1687</x:v>
+        <x:v>2787</x:v>
       </x:c>
       <x:c r="B153" s="1">
-        <x:v>902176</x:v>
+        <x:v>182279</x:v>
       </x:c>
       <x:c r="C153" s="1" t="s">
         <x:v>2579</x:v>
@@ -74046,10 +74122,10 @@
     </x:row>
     <x:row r="154" spans="1:3">
       <x:c r="A154" s="1" t="s">
-        <x:v>2786</x:v>
+        <x:v>1687</x:v>
       </x:c>
       <x:c r="B154" s="1">
-        <x:v>2771797</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="C154" s="1" t="s">
         <x:v>2579</x:v>
@@ -74057,10 +74133,10 @@
     </x:row>
     <x:row r="155" spans="1:3">
       <x:c r="A155" s="1" t="s">
-        <x:v>736</x:v>
+        <x:v>2789</x:v>
       </x:c>
       <x:c r="B155" s="1">
-        <x:v>73673</x:v>
+        <x:v>2771797</x:v>
       </x:c>
       <x:c r="C155" s="1" t="s">
         <x:v>2579</x:v>
@@ -74068,10 +74144,10 @@
     </x:row>
     <x:row r="156" spans="1:3">
       <x:c r="A156" s="1" t="s">
-        <x:v>1919</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="B156" s="1">
-        <x:v>2835078</x:v>
+        <x:v>73673</x:v>
       </x:c>
       <x:c r="C156" s="1" t="s">
         <x:v>2579</x:v>
@@ -74079,10 +74155,10 @@
     </x:row>
     <x:row r="157" spans="1:3">
       <x:c r="A157" s="1" t="s">
-        <x:v>1807</x:v>
+        <x:v>1919</x:v>
       </x:c>
       <x:c r="B157" s="1">
-        <x:v>2192272</x:v>
+        <x:v>2835078</x:v>
       </x:c>
       <x:c r="C157" s="1" t="s">
         <x:v>2579</x:v>
@@ -74090,10 +74166,10 @@
     </x:row>
     <x:row r="158" spans="1:3">
       <x:c r="A158" s="1" t="s">
-        <x:v>543</x:v>
+        <x:v>1807</x:v>
       </x:c>
       <x:c r="B158" s="1">
-        <x:v>1015758</x:v>
+        <x:v>2192272</x:v>
       </x:c>
       <x:c r="C158" s="1" t="s">
         <x:v>2579</x:v>
@@ -74101,10 +74177,10 @@
     </x:row>
     <x:row r="159" spans="1:3">
       <x:c r="A159" s="1" t="s">
-        <x:v>2788</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="B159" s="1">
-        <x:v>10000</x:v>
+        <x:v>1015758</x:v>
       </x:c>
       <x:c r="C159" s="1" t="s">
         <x:v>2579</x:v>
@@ -74112,32 +74188,32 @@
     </x:row>
     <x:row r="160" spans="1:3">
       <x:c r="A160" s="1" t="s">
-        <x:v>2792</x:v>
+        <x:v>2791</x:v>
       </x:c>
       <x:c r="B160" s="1">
-        <x:v>424596</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="C160" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2579</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:3">
       <x:c r="A161" s="1" t="s">
-        <x:v>2794</x:v>
+        <x:v>2795</x:v>
       </x:c>
       <x:c r="B161" s="1">
-        <x:v>1306863</x:v>
+        <x:v>424596</x:v>
       </x:c>
       <x:c r="C161" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2610</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:3">
       <x:c r="A162" s="1" t="s">
-        <x:v>1858</x:v>
+        <x:v>2797</x:v>
       </x:c>
       <x:c r="B162" s="1">
-        <x:v>889852</x:v>
+        <x:v>1306863</x:v>
       </x:c>
       <x:c r="C162" s="1" t="s">
         <x:v>2579</x:v>
@@ -74145,10 +74221,10 @@
     </x:row>
     <x:row r="163" spans="1:3">
       <x:c r="A163" s="1" t="s">
-        <x:v>2796</x:v>
+        <x:v>1858</x:v>
       </x:c>
       <x:c r="B163" s="1">
-        <x:v>1012792</x:v>
+        <x:v>889852</x:v>
       </x:c>
       <x:c r="C163" s="1" t="s">
         <x:v>2579</x:v>
@@ -74156,10 +74232,10 @@
     </x:row>
     <x:row r="164" spans="1:3">
       <x:c r="A164" s="1" t="s">
-        <x:v>764</x:v>
+        <x:v>2799</x:v>
       </x:c>
       <x:c r="B164" s="1">
-        <x:v>300000</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="C164" s="1" t="s">
         <x:v>2579</x:v>
@@ -74167,12 +74243,23 @@
     </x:row>
     <x:row r="165" spans="1:3">
       <x:c r="A165" s="1" t="s">
+        <x:v>764</x:v>
+      </x:c>
+      <x:c r="B165" s="1">
+        <x:v>300000</x:v>
+      </x:c>
+      <x:c r="C165" s="1" t="s">
+        <x:v>2579</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" spans="1:3">
+      <x:c r="A166" s="1" t="s">
         <x:v>836</x:v>
       </x:c>
-      <x:c r="B165" s="1">
+      <x:c r="B166" s="1">
         <x:v>487174</x:v>
       </x:c>
-      <x:c r="C165" s="1" t="s">
+      <x:c r="C166" s="1" t="s">
         <x:v>2579</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -40936,10 +40936,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C356" s="1" t="s">
-        <x:v>1718</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="D356" s="1" t="s">
-        <x:v>1719</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="E356" s="1" t="s">
         <x:v>930</x:v>
@@ -40951,7 +40951,7 @@
         <x:v>2203</x:v>
       </x:c>
       <x:c r="H356" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="357" spans="1:8">
@@ -40962,10 +40962,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C357" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>1718</x:v>
       </x:c>
       <x:c r="D357" s="1" t="s">
-        <x:v>929</x:v>
+        <x:v>1719</x:v>
       </x:c>
       <x:c r="E357" s="1" t="s">
         <x:v>930</x:v>
@@ -40977,7 +40977,7 @@
         <x:v>2203</x:v>
       </x:c>
       <x:c r="H357" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="358" spans="1:8">

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -37244,10 +37244,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="C214" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="D214" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="E214" s="1" t="s">
         <x:v>640</x:v>
@@ -37259,7 +37259,7 @@
         <x:v>2104</x:v>
       </x:c>
       <x:c r="H214" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="215" spans="1:8">
@@ -37270,10 +37270,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="C215" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="D215" s="1" t="s">
-        <x:v>642</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="E215" s="1" t="s">
         <x:v>640</x:v>
@@ -37285,7 +37285,7 @@
         <x:v>2104</x:v>
       </x:c>
       <x:c r="H215" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="216" spans="1:8">

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -41376,10 +41376,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C361" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>1724</x:v>
       </x:c>
       <x:c r="D361" s="1" t="s">
-        <x:v>929</x:v>
+        <x:v>1725</x:v>
       </x:c>
       <x:c r="E361" s="1" t="s">
         <x:v>930</x:v>
@@ -41391,7 +41391,7 @@
         <x:v>2209</x:v>
       </x:c>
       <x:c r="H361" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="362" spans="1:8">
@@ -41402,10 +41402,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C362" s="1" t="s">
-        <x:v>1724</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="D362" s="1" t="s">
-        <x:v>1725</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="E362" s="1" t="s">
         <x:v>930</x:v>
@@ -41417,7 +41417,7 @@
         <x:v>2209</x:v>
       </x:c>
       <x:c r="H362" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="363" spans="1:8">

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -8401,6 +8401,12 @@
   </x:si>
   <x:si>
     <x:t>SUBRAMANYAM, SUHAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6TX00479</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TALARICO, JAMES</x:t>
   </x:si>
   <x:si>
     <x:t>H2MI13204</x:t>
@@ -8564,8 +8570,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K196" totalsRowShown="0">
-  <x:autoFilter ref="A1:K196"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K198" totalsRowShown="0">
+  <x:autoFilter ref="A1:K198"/>
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -8584,8 +8590,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J182" totalsRowShown="0">
-  <x:autoFilter ref="A1:J182"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J184" totalsRowShown="0">
+  <x:autoFilter ref="A1:J184"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -8603,8 +8609,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C167" totalsRowShown="0">
-  <x:autoFilter ref="A1:C167"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C168" totalsRowShown="0">
+  <x:autoFilter ref="A1:C168"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -41376,10 +41382,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C361" s="1" t="s">
-        <x:v>1724</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="D361" s="1" t="s">
-        <x:v>1725</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="E361" s="1" t="s">
         <x:v>930</x:v>
@@ -41391,7 +41397,7 @@
         <x:v>2209</x:v>
       </x:c>
       <x:c r="H361" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="362" spans="1:8">
@@ -41402,10 +41408,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C362" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>1724</x:v>
       </x:c>
       <x:c r="D362" s="1" t="s">
-        <x:v>929</x:v>
+        <x:v>1725</x:v>
       </x:c>
       <x:c r="E362" s="1" t="s">
         <x:v>930</x:v>
@@ -41417,7 +41423,7 @@
         <x:v>2209</x:v>
       </x:c>
       <x:c r="H362" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="363" spans="1:8">
@@ -60338,7 +60344,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K196"/>
+  <x:dimension ref="A1:K198"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="12" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -60486,7 +60492,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I4" s="1">
-        <x:v>145696</x:v>
+        <x:v>145958</x:v>
       </x:c>
       <x:c r="J4" s="1" t="s">
         <x:v>2587</x:v>
@@ -61046,7 +61052,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>3465231</x:v>
+        <x:v>3507184</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
         <x:v>2618</x:v>
@@ -63367,10 +63373,10 @@
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
         <x:v>2212</x:v>
@@ -63391,7 +63397,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I87" s="1">
-        <x:v>2475165</x:v>
+        <x:v>33778233</x:v>
       </x:c>
       <x:c r="J87" s="1" t="s">
         <x:v>2587</x:v>
@@ -63402,10 +63408,10 @@
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
         <x:v>2212</x:v>
@@ -63426,7 +63432,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I88" s="1">
-        <x:v>33778233</x:v>
+        <x:v>2477373</x:v>
       </x:c>
       <x:c r="J88" s="1" t="s">
         <x:v>2587</x:v>
@@ -65292,34 +65298,34 @@
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="B142" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="C142" s="1" t="s">
-        <x:v>2760</x:v>
+        <x:v>2758</x:v>
       </x:c>
       <x:c r="D142" s="1" t="s">
-        <x:v>2761</x:v>
+        <x:v>2759</x:v>
       </x:c>
       <x:c r="E142" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="F142" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="G142" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H142" s="1" t="s">
-        <x:v>2762</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="I142" s="1">
-        <x:v>20483</x:v>
+        <x:v>4075</x:v>
       </x:c>
       <x:c r="J142" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="K142" s="1">
         <x:v>2026</x:v>
@@ -65327,16 +65333,16 @@
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B143" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C143" s="1" t="s">
-        <x:v>2763</x:v>
+        <x:v>2760</x:v>
       </x:c>
       <x:c r="D143" s="1" t="s">
-        <x:v>2764</x:v>
+        <x:v>2761</x:v>
       </x:c>
       <x:c r="E143" s="1" t="s">
         <x:v>2584</x:v>
@@ -65345,19 +65351,19 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G143" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="H143" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2762</x:v>
       </x:c>
       <x:c r="I143" s="1">
-        <x:v>1927706</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="J143" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="K143" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
@@ -65368,10 +65374,10 @@
         <x:v>2625</x:v>
       </x:c>
       <x:c r="C144" s="1" t="s">
-        <x:v>2765</x:v>
+        <x:v>2763</x:v>
       </x:c>
       <x:c r="D144" s="1" t="s">
-        <x:v>2766</x:v>
+        <x:v>2764</x:v>
       </x:c>
       <x:c r="E144" s="1" t="s">
         <x:v>2584</x:v>
@@ -65380,19 +65386,19 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G144" s="1" t="s">
-        <x:v>222</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H144" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="I144" s="1">
-        <x:v>817066</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="J144" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="K144" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
@@ -65403,10 +65409,10 @@
         <x:v>2625</x:v>
       </x:c>
       <x:c r="C145" s="1" t="s">
-        <x:v>2398</x:v>
+        <x:v>2765</x:v>
       </x:c>
       <x:c r="D145" s="1" t="s">
-        <x:v>269</x:v>
+        <x:v>2766</x:v>
       </x:c>
       <x:c r="E145" s="1" t="s">
         <x:v>2584</x:v>
@@ -65415,121 +65421,121 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G145" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="H145" s="1" t="s">
-        <x:v>2673</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="I145" s="1">
-        <x:v>88256</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="J145" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="K145" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="B146" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="C146" s="1" t="s">
-        <x:v>2767</x:v>
+        <x:v>2398</x:v>
       </x:c>
       <x:c r="D146" s="1" t="s">
-        <x:v>2768</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="E146" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="F146" s="1" t="s">
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G146" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H146" s="1" t="s">
-        <x:v>2762</x:v>
+        <x:v>2673</x:v>
       </x:c>
       <x:c r="I146" s="1">
-        <x:v>75000</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="J146" s="1" t="s">
         <x:v>2587</x:v>
       </x:c>
       <x:c r="K146" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="B147" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="C147" s="1" t="s">
-        <x:v>2769</x:v>
+        <x:v>2767</x:v>
       </x:c>
       <x:c r="D147" s="1" t="s">
-        <x:v>1088</x:v>
+        <x:v>2768</x:v>
       </x:c>
       <x:c r="E147" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="F147" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="G147" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H147" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2762</x:v>
       </x:c>
       <x:c r="I147" s="1">
-        <x:v>10041119</x:v>
+        <x:v>75000</x:v>
       </x:c>
       <x:c r="J147" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="K147" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
       <x:c r="A148" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="B148" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="C148" s="1" t="s">
-        <x:v>2770</x:v>
+        <x:v>2769</x:v>
       </x:c>
       <x:c r="D148" s="1" t="s">
-        <x:v>2771</x:v>
+        <x:v>1088</x:v>
       </x:c>
       <x:c r="E148" s="1" t="s">
         <x:v>2584</x:v>
       </x:c>
       <x:c r="F148" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="G148" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H148" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="I148" s="1">
-        <x:v>1491280</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="J148" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="K148" s="1">
         <x:v>2024</x:v>
@@ -65537,66 +65543,66 @@
     </x:row>
     <x:row r="149" spans="1:11">
       <x:c r="A149" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B149" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C149" s="1" t="s">
-        <x:v>2414</x:v>
+        <x:v>2770</x:v>
       </x:c>
       <x:c r="D149" s="1" t="s">
-        <x:v>888</x:v>
+        <x:v>2771</x:v>
       </x:c>
       <x:c r="E149" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="F149" s="1" t="s">
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G149" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H149" s="1" t="s">
-        <x:v>2681</x:v>
+        <x:v>2607</x:v>
       </x:c>
       <x:c r="I149" s="1">
-        <x:v>75844</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="J149" s="1" t="s">
         <x:v>2587</x:v>
       </x:c>
       <x:c r="K149" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="1" t="s">
-        <x:v>2608</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="B150" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="C150" s="1" t="s">
-        <x:v>2418</x:v>
+        <x:v>2414</x:v>
       </x:c>
       <x:c r="D150" s="1" t="s">
-        <x:v>1483</x:v>
+        <x:v>888</x:v>
       </x:c>
       <x:c r="E150" s="1" t="s">
         <x:v>2594</x:v>
       </x:c>
       <x:c r="F150" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="G150" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="H150" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2681</x:v>
       </x:c>
       <x:c r="I150" s="1">
-        <x:v>700000</x:v>
+        <x:v>75844</x:v>
       </x:c>
       <x:c r="J150" s="1" t="s">
         <x:v>2587</x:v>
@@ -65607,16 +65613,16 @@
     </x:row>
     <x:row r="151" spans="1:11">
       <x:c r="A151" s="1" t="s">
-        <x:v>167</x:v>
+        <x:v>2608</x:v>
       </x:c>
       <x:c r="B151" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>2609</x:v>
       </x:c>
       <x:c r="C151" s="1" t="s">
-        <x:v>2772</x:v>
+        <x:v>2418</x:v>
       </x:c>
       <x:c r="D151" s="1" t="s">
-        <x:v>2773</x:v>
+        <x:v>1483</x:v>
       </x:c>
       <x:c r="E151" s="1" t="s">
         <x:v>2594</x:v>
@@ -65625,13 +65631,13 @@
         <x:v>2595</x:v>
       </x:c>
       <x:c r="G151" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H151" s="1" t="s">
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I151" s="1">
-        <x:v>902547</x:v>
+        <x:v>700000</x:v>
       </x:c>
       <x:c r="J151" s="1" t="s">
         <x:v>2587</x:v>
@@ -65642,16 +65648,16 @@
     </x:row>
     <x:row r="152" spans="1:11">
       <x:c r="A152" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B152" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C152" s="1" t="s">
-        <x:v>2432</x:v>
+        <x:v>2772</x:v>
       </x:c>
       <x:c r="D152" s="1" t="s">
-        <x:v>1588</x:v>
+        <x:v>2773</x:v>
       </x:c>
       <x:c r="E152" s="1" t="s">
         <x:v>2594</x:v>
@@ -65660,13 +65666,13 @@
         <x:v>2595</x:v>
       </x:c>
       <x:c r="G152" s="1" t="s">
-        <x:v>733</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H152" s="1" t="s">
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I152" s="1">
-        <x:v>823496</x:v>
+        <x:v>902547</x:v>
       </x:c>
       <x:c r="J152" s="1" t="s">
         <x:v>2587</x:v>
@@ -65683,25 +65689,25 @@
         <x:v>2601</x:v>
       </x:c>
       <x:c r="C153" s="1" t="s">
-        <x:v>2433</x:v>
+        <x:v>2432</x:v>
       </x:c>
       <x:c r="D153" s="1" t="s">
-        <x:v>493</x:v>
+        <x:v>1588</x:v>
       </x:c>
       <x:c r="E153" s="1" t="s">
         <x:v>2594</x:v>
       </x:c>
       <x:c r="F153" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="G153" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>733</x:v>
       </x:c>
       <x:c r="H153" s="1" t="s">
-        <x:v>2673</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="I153" s="1">
-        <x:v>75320</x:v>
+        <x:v>823496</x:v>
       </x:c>
       <x:c r="J153" s="1" t="s">
         <x:v>2587</x:v>
@@ -65712,51 +65718,51 @@
     </x:row>
     <x:row r="154" spans="1:11">
       <x:c r="A154" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="B154" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="C154" s="1" t="s">
-        <x:v>2441</x:v>
+        <x:v>2433</x:v>
       </x:c>
       <x:c r="D154" s="1" t="s">
-        <x:v>1450</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="E154" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="F154" s="1" t="s">
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G154" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H154" s="1" t="s">
-        <x:v>2697</x:v>
+        <x:v>2673</x:v>
       </x:c>
       <x:c r="I154" s="1">
-        <x:v>1987660</x:v>
+        <x:v>75320</x:v>
       </x:c>
       <x:c r="J154" s="1" t="s">
         <x:v>2587</x:v>
       </x:c>
       <x:c r="K154" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:11">
       <x:c r="A155" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="B155" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="C155" s="1" t="s">
-        <x:v>2774</x:v>
+        <x:v>2441</x:v>
       </x:c>
       <x:c r="D155" s="1" t="s">
-        <x:v>2775</x:v>
+        <x:v>1450</x:v>
       </x:c>
       <x:c r="E155" s="1" t="s">
         <x:v>2584</x:v>
@@ -65765,19 +65771,19 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G155" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H155" s="1" t="s">
-        <x:v>2590</x:v>
+        <x:v>2697</x:v>
       </x:c>
       <x:c r="I155" s="1">
-        <x:v>74382</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="J155" s="1" t="s">
         <x:v>2587</x:v>
       </x:c>
       <x:c r="K155" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:11">
@@ -65788,10 +65794,10 @@
         <x:v>2583</x:v>
       </x:c>
       <x:c r="C156" s="1" t="s">
-        <x:v>2456</x:v>
+        <x:v>2774</x:v>
       </x:c>
       <x:c r="D156" s="1" t="s">
-        <x:v>591</x:v>
+        <x:v>2775</x:v>
       </x:c>
       <x:c r="E156" s="1" t="s">
         <x:v>2584</x:v>
@@ -65800,13 +65806,13 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G156" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H156" s="1" t="s">
-        <x:v>2613</x:v>
+        <x:v>2590</x:v>
       </x:c>
       <x:c r="I156" s="1">
-        <x:v>105040</x:v>
+        <x:v>74382</x:v>
       </x:c>
       <x:c r="J156" s="1" t="s">
         <x:v>2587</x:v>
@@ -65823,10 +65829,10 @@
         <x:v>2583</x:v>
       </x:c>
       <x:c r="C157" s="1" t="s">
-        <x:v>2459</x:v>
+        <x:v>2456</x:v>
       </x:c>
       <x:c r="D157" s="1" t="s">
-        <x:v>496</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="E157" s="1" t="s">
         <x:v>2584</x:v>
@@ -65835,16 +65841,16 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G157" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H157" s="1" t="s">
-        <x:v>2633</x:v>
+        <x:v>2613</x:v>
       </x:c>
       <x:c r="I157" s="1">
-        <x:v>56045</x:v>
+        <x:v>105040</x:v>
       </x:c>
       <x:c r="J157" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="K157" s="1">
         <x:v>2026</x:v>
@@ -65852,19 +65858,19 @@
     </x:row>
     <x:row r="158" spans="1:11">
       <x:c r="A158" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B158" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C158" s="1" t="s">
-        <x:v>2460</x:v>
+        <x:v>2459</x:v>
       </x:c>
       <x:c r="D158" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="E158" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="F158" s="1" t="s">
         <x:v>2585</x:v>
@@ -65873,13 +65879,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="H158" s="1" t="s">
-        <x:v>2613</x:v>
+        <x:v>2633</x:v>
       </x:c>
       <x:c r="I158" s="1">
-        <x:v>75281</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="J158" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="K158" s="1">
         <x:v>2026</x:v>
@@ -65893,10 +65899,10 @@
         <x:v>2601</x:v>
       </x:c>
       <x:c r="C159" s="1" t="s">
-        <x:v>2776</x:v>
+        <x:v>2460</x:v>
       </x:c>
       <x:c r="D159" s="1" t="s">
-        <x:v>2777</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="E159" s="1" t="s">
         <x:v>2594</x:v>
@@ -65905,13 +65911,13 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G159" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H159" s="1" t="s">
-        <x:v>2755</x:v>
+        <x:v>2613</x:v>
       </x:c>
       <x:c r="I159" s="1">
-        <x:v>852561</x:v>
+        <x:v>75281</x:v>
       </x:c>
       <x:c r="J159" s="1" t="s">
         <x:v>2587</x:v>
@@ -65922,31 +65928,31 @@
     </x:row>
     <x:row r="160" spans="1:11">
       <x:c r="A160" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="B160" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="C160" s="1" t="s">
-        <x:v>2466</x:v>
+        <x:v>2776</x:v>
       </x:c>
       <x:c r="D160" s="1" t="s">
-        <x:v>1743</x:v>
+        <x:v>2777</x:v>
       </x:c>
       <x:c r="E160" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="F160" s="1" t="s">
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G160" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H160" s="1" t="s">
-        <x:v>2673</x:v>
+        <x:v>2755</x:v>
       </x:c>
       <x:c r="I160" s="1">
-        <x:v>74852</x:v>
+        <x:v>852561</x:v>
       </x:c>
       <x:c r="J160" s="1" t="s">
         <x:v>2587</x:v>
@@ -65963,10 +65969,10 @@
         <x:v>2583</x:v>
       </x:c>
       <x:c r="C161" s="1" t="s">
-        <x:v>2778</x:v>
+        <x:v>2466</x:v>
       </x:c>
       <x:c r="D161" s="1" t="s">
-        <x:v>2779</x:v>
+        <x:v>1743</x:v>
       </x:c>
       <x:c r="E161" s="1" t="s">
         <x:v>2584</x:v>
@@ -65975,13 +65981,13 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G161" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H161" s="1" t="s">
-        <x:v>2691</x:v>
+        <x:v>2673</x:v>
       </x:c>
       <x:c r="I161" s="1">
-        <x:v>111599</x:v>
+        <x:v>74852</x:v>
       </x:c>
       <x:c r="J161" s="1" t="s">
         <x:v>2587</x:v>
@@ -65998,66 +66004,66 @@
         <x:v>2583</x:v>
       </x:c>
       <x:c r="C162" s="1" t="s">
-        <x:v>2780</x:v>
+        <x:v>2778</x:v>
       </x:c>
       <x:c r="D162" s="1" t="s">
-        <x:v>634</x:v>
+        <x:v>2779</x:v>
       </x:c>
       <x:c r="E162" s="1" t="s">
         <x:v>2584</x:v>
       </x:c>
       <x:c r="F162" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="G162" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H162" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2691</x:v>
       </x:c>
       <x:c r="I162" s="1">
-        <x:v>10046680</x:v>
+        <x:v>111599</x:v>
       </x:c>
       <x:c r="J162" s="1" t="s">
         <x:v>2587</x:v>
       </x:c>
       <x:c r="K162" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:11">
       <x:c r="A163" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B163" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C163" s="1" t="s">
-        <x:v>2478</x:v>
+        <x:v>2780</x:v>
       </x:c>
       <x:c r="D163" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="E163" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="F163" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="G163" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H163" s="1" t="s">
-        <x:v>2590</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="I163" s="1">
-        <x:v>565950</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="J163" s="1" t="s">
         <x:v>2587</x:v>
       </x:c>
       <x:c r="K163" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:11">
@@ -66068,10 +66074,10 @@
         <x:v>2601</x:v>
       </x:c>
       <x:c r="C164" s="1" t="s">
-        <x:v>2481</x:v>
+        <x:v>2478</x:v>
       </x:c>
       <x:c r="D164" s="1" t="s">
-        <x:v>966</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E164" s="1" t="s">
         <x:v>2594</x:v>
@@ -66080,13 +66086,13 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G164" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H164" s="1" t="s">
-        <x:v>2613</x:v>
+        <x:v>2590</x:v>
       </x:c>
       <x:c r="I164" s="1">
-        <x:v>75617</x:v>
+        <x:v>565950</x:v>
       </x:c>
       <x:c r="J164" s="1" t="s">
         <x:v>2587</x:v>
@@ -66097,31 +66103,31 @@
     </x:row>
     <x:row r="165" spans="1:11">
       <x:c r="A165" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="B165" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="C165" s="1" t="s">
-        <x:v>2781</x:v>
+        <x:v>2481</x:v>
       </x:c>
       <x:c r="D165" s="1" t="s">
-        <x:v>2782</x:v>
+        <x:v>966</x:v>
       </x:c>
       <x:c r="E165" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="F165" s="1" t="s">
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G165" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H165" s="1" t="s">
-        <x:v>2623</x:v>
+        <x:v>2613</x:v>
       </x:c>
       <x:c r="I165" s="1">
-        <x:v>380377</x:v>
+        <x:v>75617</x:v>
       </x:c>
       <x:c r="J165" s="1" t="s">
         <x:v>2587</x:v>
@@ -66132,16 +66138,16 @@
     </x:row>
     <x:row r="166" spans="1:11">
       <x:c r="A166" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B166" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C166" s="1" t="s">
-        <x:v>2484</x:v>
+        <x:v>2781</x:v>
       </x:c>
       <x:c r="D166" s="1" t="s">
-        <x:v>655</x:v>
+        <x:v>2782</x:v>
       </x:c>
       <x:c r="E166" s="1" t="s">
         <x:v>2584</x:v>
@@ -66150,51 +66156,51 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G166" s="1" t="s">
-        <x:v>222</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H166" s="1" t="s">
-        <x:v>2712</x:v>
+        <x:v>2623</x:v>
       </x:c>
       <x:c r="I166" s="1">
-        <x:v>817169</x:v>
+        <x:v>380377</x:v>
       </x:c>
       <x:c r="J166" s="1" t="s">
         <x:v>2587</x:v>
       </x:c>
       <x:c r="K166" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:11">
       <x:c r="A167" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="B167" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="C167" s="1" t="s">
-        <x:v>2783</x:v>
+        <x:v>2484</x:v>
       </x:c>
       <x:c r="D167" s="1" t="s">
-        <x:v>2784</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="E167" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="F167" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="G167" s="1" t="s">
-        <x:v>238</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="H167" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2712</x:v>
       </x:c>
       <x:c r="I167" s="1">
-        <x:v>1531015</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="J167" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="K167" s="1">
         <x:v>2024</x:v>
@@ -66202,72 +66208,72 @@
     </x:row>
     <x:row r="168" spans="1:11">
       <x:c r="A168" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="B168" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="C168" s="1" t="s">
-        <x:v>2490</x:v>
+        <x:v>2783</x:v>
       </x:c>
       <x:c r="D168" s="1" t="s">
-        <x:v>1672</x:v>
+        <x:v>2784</x:v>
       </x:c>
       <x:c r="E168" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="F168" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="G168" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="H168" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="I168" s="1">
-        <x:v>157560</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="J168" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="K168" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:11">
       <x:c r="A169" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B169" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C169" s="1" t="s">
-        <x:v>2492</x:v>
+        <x:v>2490</x:v>
       </x:c>
       <x:c r="D169" s="1" t="s">
-        <x:v>1329</x:v>
+        <x:v>1672</x:v>
       </x:c>
       <x:c r="E169" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="F169" s="1" t="s">
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G169" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H169" s="1" t="s">
-        <x:v>2785</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="I169" s="1">
-        <x:v>2791716</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="J169" s="1" t="s">
         <x:v>2587</x:v>
       </x:c>
       <x:c r="K169" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:11">
@@ -66278,10 +66284,10 @@
         <x:v>2625</x:v>
       </x:c>
       <x:c r="C170" s="1" t="s">
-        <x:v>2494</x:v>
+        <x:v>2492</x:v>
       </x:c>
       <x:c r="D170" s="1" t="s">
-        <x:v>1675</x:v>
+        <x:v>1329</x:v>
       </x:c>
       <x:c r="E170" s="1" t="s">
         <x:v>2594</x:v>
@@ -66290,19 +66296,19 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G170" s="1" t="s">
-        <x:v>601</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H170" s="1" t="s">
-        <x:v>2636</x:v>
+        <x:v>2785</x:v>
       </x:c>
       <x:c r="I170" s="1">
-        <x:v>1025785</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="J170" s="1" t="s">
         <x:v>2587</x:v>
       </x:c>
       <x:c r="K170" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:11">
@@ -66331,27 +66337,27 @@
         <x:v>2636</x:v>
       </x:c>
       <x:c r="I171" s="1">
-        <x:v>764206</x:v>
+        <x:v>1025785</x:v>
       </x:c>
       <x:c r="J171" s="1" t="s">
         <x:v>2587</x:v>
       </x:c>
       <x:c r="K171" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:11">
       <x:c r="A172" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="B172" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="C172" s="1" t="s">
-        <x:v>2786</x:v>
+        <x:v>2494</x:v>
       </x:c>
       <x:c r="D172" s="1" t="s">
-        <x:v>2787</x:v>
+        <x:v>1675</x:v>
       </x:c>
       <x:c r="E172" s="1" t="s">
         <x:v>2594</x:v>
@@ -66360,51 +66366,51 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G172" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="H172" s="1" t="s">
-        <x:v>2613</x:v>
+        <x:v>2636</x:v>
       </x:c>
       <x:c r="I172" s="1">
-        <x:v>1543316</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="J172" s="1" t="s">
         <x:v>2587</x:v>
       </x:c>
       <x:c r="K172" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:11">
       <x:c r="A173" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="B173" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="C173" s="1" t="s">
-        <x:v>2788</x:v>
+        <x:v>2786</x:v>
       </x:c>
       <x:c r="D173" s="1" t="s">
-        <x:v>2789</x:v>
+        <x:v>2787</x:v>
       </x:c>
       <x:c r="E173" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="F173" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="G173" s="1" t="s">
-        <x:v>222</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H173" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2613</x:v>
       </x:c>
       <x:c r="I173" s="1">
-        <x:v>10015605</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="J173" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="K173" s="1">
         <x:v>2026</x:v>
@@ -66447,34 +66453,34 @@
     </x:row>
     <x:row r="175" spans="1:11">
       <x:c r="A175" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="B175" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="C175" s="1" t="s">
-        <x:v>2790</x:v>
+        <x:v>2788</x:v>
       </x:c>
       <x:c r="D175" s="1" t="s">
-        <x:v>2791</x:v>
+        <x:v>2789</x:v>
       </x:c>
       <x:c r="E175" s="1" t="s">
         <x:v>2584</x:v>
       </x:c>
       <x:c r="F175" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="G175" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="H175" s="1" t="s">
-        <x:v>2684</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="I175" s="1">
-        <x:v>103020</x:v>
+        <x:v>10015605</x:v>
       </x:c>
       <x:c r="J175" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="K175" s="1">
         <x:v>2026</x:v>
@@ -66488,10 +66494,10 @@
         <x:v>2583</x:v>
       </x:c>
       <x:c r="C176" s="1" t="s">
-        <x:v>2792</x:v>
+        <x:v>2790</x:v>
       </x:c>
       <x:c r="D176" s="1" t="s">
-        <x:v>2793</x:v>
+        <x:v>2791</x:v>
       </x:c>
       <x:c r="E176" s="1" t="s">
         <x:v>2584</x:v>
@@ -66500,13 +66506,13 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G176" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H176" s="1" t="s">
         <x:v>2684</x:v>
       </x:c>
       <x:c r="I176" s="1">
-        <x:v>75332</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="J176" s="1" t="s">
         <x:v>2587</x:v>
@@ -66541,27 +66547,27 @@
         <x:v>2684</x:v>
       </x:c>
       <x:c r="I177" s="1">
-        <x:v>106947</x:v>
+        <x:v>75332</x:v>
       </x:c>
       <x:c r="J177" s="1" t="s">
         <x:v>2587</x:v>
       </x:c>
       <x:c r="K177" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="178" spans="1:11">
       <x:c r="A178" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B178" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C178" s="1" t="s">
-        <x:v>2501</x:v>
+        <x:v>2792</x:v>
       </x:c>
       <x:c r="D178" s="1" t="s">
-        <x:v>1693</x:v>
+        <x:v>2793</x:v>
       </x:c>
       <x:c r="E178" s="1" t="s">
         <x:v>2584</x:v>
@@ -66570,13 +66576,13 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G178" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="H178" s="1" t="s">
-        <x:v>2590</x:v>
+        <x:v>2684</x:v>
       </x:c>
       <x:c r="I178" s="1">
-        <x:v>902176</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="J178" s="1" t="s">
         <x:v>2587</x:v>
@@ -66587,16 +66593,16 @@
     </x:row>
     <x:row r="179" spans="1:11">
       <x:c r="A179" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="B179" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="C179" s="1" t="s">
-        <x:v>2794</x:v>
+        <x:v>2501</x:v>
       </x:c>
       <x:c r="D179" s="1" t="s">
-        <x:v>2795</x:v>
+        <x:v>1693</x:v>
       </x:c>
       <x:c r="E179" s="1" t="s">
         <x:v>2584</x:v>
@@ -66605,27 +66611,27 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G179" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H179" s="1" t="s">
-        <x:v>2633</x:v>
+        <x:v>2590</x:v>
       </x:c>
       <x:c r="I179" s="1">
-        <x:v>1761655</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="J179" s="1" t="s">
         <x:v>2587</x:v>
       </x:c>
       <x:c r="K179" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="180" spans="1:11">
       <x:c r="A180" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="B180" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="C180" s="1" t="s">
         <x:v>2794</x:v>
@@ -66637,51 +66643,51 @@
         <x:v>2584</x:v>
       </x:c>
       <x:c r="F180" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="G180" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H180" s="1" t="s">
-        <x:v>2633</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="I180" s="1">
-        <x:v>1010142</x:v>
+        <x:v>77424</x:v>
       </x:c>
       <x:c r="J180" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="K180" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="181" spans="1:11">
       <x:c r="A181" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B181" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C181" s="1" t="s">
-        <x:v>2508</x:v>
+        <x:v>2796</x:v>
       </x:c>
       <x:c r="D181" s="1" t="s">
-        <x:v>736</x:v>
+        <x:v>2797</x:v>
       </x:c>
       <x:c r="E181" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="F181" s="1" t="s">
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G181" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H181" s="1" t="s">
-        <x:v>2664</x:v>
+        <x:v>2633</x:v>
       </x:c>
       <x:c r="I181" s="1">
-        <x:v>73673</x:v>
+        <x:v>1761655</x:v>
       </x:c>
       <x:c r="J181" s="1" t="s">
         <x:v>2587</x:v>
@@ -66692,37 +66698,37 @@
     </x:row>
     <x:row r="182" spans="1:11">
       <x:c r="A182" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B182" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C182" s="1" t="s">
-        <x:v>2514</x:v>
+        <x:v>2796</x:v>
       </x:c>
       <x:c r="D182" s="1" t="s">
-        <x:v>1925</x:v>
+        <x:v>2797</x:v>
       </x:c>
       <x:c r="E182" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="F182" s="1" t="s">
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G182" s="1" t="s">
-        <x:v>746</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H182" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2633</x:v>
       </x:c>
       <x:c r="I182" s="1">
-        <x:v>974633</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="J182" s="1" t="s">
         <x:v>2587</x:v>
       </x:c>
       <x:c r="K182" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="183" spans="1:11">
@@ -66733,10 +66739,10 @@
         <x:v>2601</x:v>
       </x:c>
       <x:c r="C183" s="1" t="s">
-        <x:v>2514</x:v>
+        <x:v>2508</x:v>
       </x:c>
       <x:c r="D183" s="1" t="s">
-        <x:v>1925</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="E183" s="1" t="s">
         <x:v>2594</x:v>
@@ -66745,48 +66751,48 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G183" s="1" t="s">
-        <x:v>746</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="H183" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2664</x:v>
       </x:c>
       <x:c r="I183" s="1">
-        <x:v>1860445</x:v>
+        <x:v>73673</x:v>
       </x:c>
       <x:c r="J183" s="1" t="s">
         <x:v>2587</x:v>
       </x:c>
       <x:c r="K183" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="184" spans="1:11">
       <x:c r="A184" s="1" t="s">
-        <x:v>2608</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="B184" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="C184" s="1" t="s">
-        <x:v>2522</x:v>
+        <x:v>2514</x:v>
       </x:c>
       <x:c r="D184" s="1" t="s">
-        <x:v>1813</x:v>
+        <x:v>1925</x:v>
       </x:c>
       <x:c r="E184" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="F184" s="1" t="s">
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G184" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="H184" s="1" t="s">
-        <x:v>2664</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="I184" s="1">
-        <x:v>600000</x:v>
+        <x:v>974633</x:v>
       </x:c>
       <x:c r="J184" s="1" t="s">
         <x:v>2587</x:v>
@@ -66797,45 +66803,45 @@
     </x:row>
     <x:row r="185" spans="1:11">
       <x:c r="A185" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="B185" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="C185" s="1" t="s">
-        <x:v>2522</x:v>
+        <x:v>2514</x:v>
       </x:c>
       <x:c r="D185" s="1" t="s">
-        <x:v>1813</x:v>
+        <x:v>1925</x:v>
       </x:c>
       <x:c r="E185" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="F185" s="1" t="s">
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G185" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="H185" s="1" t="s">
-        <x:v>2664</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="I185" s="1">
-        <x:v>1419040</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="J185" s="1" t="s">
         <x:v>2587</x:v>
       </x:c>
       <x:c r="K185" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="186" spans="1:11">
       <x:c r="A186" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2608</x:v>
       </x:c>
       <x:c r="B186" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2609</x:v>
       </x:c>
       <x:c r="C186" s="1" t="s">
         <x:v>2522</x:v>
@@ -66856,21 +66862,21 @@
         <x:v>2664</x:v>
       </x:c>
       <x:c r="I186" s="1">
-        <x:v>110148</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="J186" s="1" t="s">
         <x:v>2587</x:v>
       </x:c>
       <x:c r="K186" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="187" spans="1:11">
       <x:c r="A187" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B187" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C187" s="1" t="s">
         <x:v>2522</x:v>
@@ -66891,27 +66897,27 @@
         <x:v>2664</x:v>
       </x:c>
       <x:c r="I187" s="1">
-        <x:v>63084</x:v>
+        <x:v>1419040</x:v>
       </x:c>
       <x:c r="J187" s="1" t="s">
         <x:v>2587</x:v>
       </x:c>
       <x:c r="K187" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="188" spans="1:11">
       <x:c r="A188" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B188" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C188" s="1" t="s">
-        <x:v>2524</x:v>
+        <x:v>2522</x:v>
       </x:c>
       <x:c r="D188" s="1" t="s">
-        <x:v>543</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="E188" s="1" t="s">
         <x:v>2584</x:v>
@@ -66920,48 +66926,48 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G188" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H188" s="1" t="s">
-        <x:v>2785</x:v>
+        <x:v>2664</x:v>
       </x:c>
       <x:c r="I188" s="1">
-        <x:v>1015758</x:v>
+        <x:v>110148</x:v>
       </x:c>
       <x:c r="J188" s="1" t="s">
         <x:v>2587</x:v>
       </x:c>
       <x:c r="K188" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="189" spans="1:11">
       <x:c r="A189" s="1" t="s">
-        <x:v>2650</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="B189" s="1" t="s">
-        <x:v>2651</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="C189" s="1" t="s">
-        <x:v>2796</x:v>
+        <x:v>2522</x:v>
       </x:c>
       <x:c r="D189" s="1" t="s">
-        <x:v>2797</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="E189" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="F189" s="1" t="s">
-        <x:v>2798</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="G189" s="1" t="s">
-        <x:v>2799</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H189" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2664</x:v>
       </x:c>
       <x:c r="I189" s="1">
-        <x:v>10000</x:v>
+        <x:v>63084</x:v>
       </x:c>
       <x:c r="J189" s="1" t="s">
         <x:v>2587</x:v>
@@ -66972,34 +66978,34 @@
     </x:row>
     <x:row r="190" spans="1:11">
       <x:c r="A190" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="B190" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="C190" s="1" t="s">
-        <x:v>2800</x:v>
+        <x:v>2524</x:v>
       </x:c>
       <x:c r="D190" s="1" t="s">
-        <x:v>2801</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="E190" s="1" t="s">
         <x:v>2584</x:v>
       </x:c>
       <x:c r="F190" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="G190" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H190" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2785</x:v>
       </x:c>
       <x:c r="I190" s="1">
-        <x:v>424596</x:v>
+        <x:v>1015758</x:v>
       </x:c>
       <x:c r="J190" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="K190" s="1">
         <x:v>2026</x:v>
@@ -67007,31 +67013,31 @@
     </x:row>
     <x:row r="191" spans="1:11">
       <x:c r="A191" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2650</x:v>
       </x:c>
       <x:c r="B191" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="C191" s="1" t="s">
-        <x:v>2802</x:v>
+        <x:v>2798</x:v>
       </x:c>
       <x:c r="D191" s="1" t="s">
-        <x:v>2803</x:v>
+        <x:v>2799</x:v>
       </x:c>
       <x:c r="E191" s="1" t="s">
         <x:v>2594</x:v>
       </x:c>
       <x:c r="F191" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G191" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>2801</x:v>
       </x:c>
       <x:c r="H191" s="1" t="s">
-        <x:v>2678</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="I191" s="1">
-        <x:v>1306863</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="J191" s="1" t="s">
         <x:v>2587</x:v>
@@ -67042,45 +67048,45 @@
     </x:row>
     <x:row r="192" spans="1:11">
       <x:c r="A192" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="B192" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="C192" s="1" t="s">
-        <x:v>2539</x:v>
+        <x:v>2802</x:v>
       </x:c>
       <x:c r="D192" s="1" t="s">
-        <x:v>1864</x:v>
+        <x:v>2803</x:v>
       </x:c>
       <x:c r="E192" s="1" t="s">
         <x:v>2584</x:v>
       </x:c>
       <x:c r="F192" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="G192" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="H192" s="1" t="s">
-        <x:v>2673</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="I192" s="1">
-        <x:v>889852</x:v>
+        <x:v>429577</x:v>
       </x:c>
       <x:c r="J192" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="K192" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="193" spans="1:11">
       <x:c r="A193" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="B193" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="C193" s="1" t="s">
         <x:v>2804</x:v>
@@ -67089,7 +67095,7 @@
         <x:v>2805</x:v>
       </x:c>
       <x:c r="E193" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="F193" s="1" t="s">
         <x:v>2585</x:v>
@@ -67098,16 +67104,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H193" s="1" t="s">
-        <x:v>2664</x:v>
+        <x:v>2678</x:v>
       </x:c>
       <x:c r="I193" s="1">
-        <x:v>362000</x:v>
+        <x:v>1306863</x:v>
       </x:c>
       <x:c r="J193" s="1" t="s">
         <x:v>2587</x:v>
       </x:c>
       <x:c r="K193" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="194" spans="1:11">
@@ -67118,10 +67124,10 @@
         <x:v>2583</x:v>
       </x:c>
       <x:c r="C194" s="1" t="s">
-        <x:v>2806</x:v>
+        <x:v>2539</x:v>
       </x:c>
       <x:c r="D194" s="1" t="s">
-        <x:v>2807</x:v>
+        <x:v>1864</x:v>
       </x:c>
       <x:c r="E194" s="1" t="s">
         <x:v>2584</x:v>
@@ -67133,45 +67139,45 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="H194" s="1" t="s">
-        <x:v>2762</x:v>
+        <x:v>2673</x:v>
       </x:c>
       <x:c r="I194" s="1">
-        <x:v>1012792</x:v>
+        <x:v>889852</x:v>
       </x:c>
       <x:c r="J194" s="1" t="s">
         <x:v>2587</x:v>
       </x:c>
       <x:c r="K194" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="195" spans="1:11">
       <x:c r="A195" s="1" t="s">
-        <x:v>2608</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B195" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C195" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2806</x:v>
       </x:c>
       <x:c r="D195" s="1" t="s">
-        <x:v>764</x:v>
+        <x:v>2807</x:v>
       </x:c>
       <x:c r="E195" s="1" t="s">
         <x:v>2584</x:v>
       </x:c>
       <x:c r="F195" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="G195" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H195" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2664</x:v>
       </x:c>
       <x:c r="I195" s="1">
-        <x:v>300000</x:v>
+        <x:v>381352</x:v>
       </x:c>
       <x:c r="J195" s="1" t="s">
         <x:v>2587</x:v>
@@ -67188,10 +67194,10 @@
         <x:v>2583</x:v>
       </x:c>
       <x:c r="C196" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2808</x:v>
       </x:c>
       <x:c r="D196" s="1" t="s">
-        <x:v>836</x:v>
+        <x:v>2809</x:v>
       </x:c>
       <x:c r="E196" s="1" t="s">
         <x:v>2584</x:v>
@@ -67200,18 +67206,88 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G196" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="H196" s="1" t="s">
-        <x:v>2686</x:v>
+        <x:v>2762</x:v>
       </x:c>
       <x:c r="I196" s="1">
-        <x:v>487174</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="J196" s="1" t="s">
         <x:v>2587</x:v>
       </x:c>
       <x:c r="K196" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" spans="1:11">
+      <x:c r="A197" s="1" t="s">
+        <x:v>2608</x:v>
+      </x:c>
+      <x:c r="B197" s="1" t="s">
+        <x:v>2609</x:v>
+      </x:c>
+      <x:c r="C197" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="D197" s="1" t="s">
+        <x:v>764</x:v>
+      </x:c>
+      <x:c r="E197" s="1" t="s">
+        <x:v>2584</x:v>
+      </x:c>
+      <x:c r="F197" s="1" t="s">
+        <x:v>2595</x:v>
+      </x:c>
+      <x:c r="G197" s="1" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="H197" s="1" t="s">
+        <x:v>2596</x:v>
+      </x:c>
+      <x:c r="I197" s="1">
+        <x:v>300000</x:v>
+      </x:c>
+      <x:c r="J197" s="1" t="s">
+        <x:v>2587</x:v>
+      </x:c>
+      <x:c r="K197" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" spans="1:11">
+      <x:c r="A198" s="1" t="s">
+        <x:v>2582</x:v>
+      </x:c>
+      <x:c r="B198" s="1" t="s">
+        <x:v>2583</x:v>
+      </x:c>
+      <x:c r="C198" s="1" t="s">
+        <x:v>2560</x:v>
+      </x:c>
+      <x:c r="D198" s="1" t="s">
+        <x:v>836</x:v>
+      </x:c>
+      <x:c r="E198" s="1" t="s">
+        <x:v>2584</x:v>
+      </x:c>
+      <x:c r="F198" s="1" t="s">
+        <x:v>2585</x:v>
+      </x:c>
+      <x:c r="G198" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H198" s="1" t="s">
+        <x:v>2686</x:v>
+      </x:c>
+      <x:c r="I198" s="1">
+        <x:v>487174</x:v>
+      </x:c>
+      <x:c r="J198" s="1" t="s">
+        <x:v>2587</x:v>
+      </x:c>
+      <x:c r="K198" s="1">
         <x:v>2026</x:v>
       </x:c>
     </x:row>
@@ -67231,7 +67307,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J182"/>
+  <x:dimension ref="A1:J184"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -67369,7 +67445,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I4" s="1">
-        <x:v>145696</x:v>
+        <x:v>145958</x:v>
       </x:c>
       <x:c r="J4" s="1" t="s">
         <x:v>2587</x:v>
@@ -67825,10 +67901,10 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>2632</x:v>
@@ -67849,7 +67925,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I19" s="1">
-        <x:v>12894063</x:v>
+        <x:v>3507184</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
         <x:v>2618</x:v>
@@ -67857,10 +67933,10 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>2632</x:v>
@@ -67881,7 +67957,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>3465231</x:v>
+        <x:v>12894063</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
         <x:v>2618</x:v>
@@ -67889,10 +67965,10 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>2009</x:v>
@@ -67913,7 +67989,7 @@
         <x:v>2633</x:v>
       </x:c>
       <x:c r="I21" s="1">
-        <x:v>83860</x:v>
+        <x:v>582374</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
         <x:v>2587</x:v>
@@ -67921,10 +67997,10 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>2009</x:v>
@@ -67945,7 +68021,7 @@
         <x:v>2633</x:v>
       </x:c>
       <x:c r="I22" s="1">
-        <x:v>582374</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
         <x:v>2587</x:v>
@@ -69585,10 +69661,10 @@
     </x:row>
     <x:row r="74" spans="1:10">
       <x:c r="A74" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2608</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>2609</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
         <x:v>2704</x:v>
@@ -69609,7 +69685,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I74" s="1">
-        <x:v>1471226</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="J74" s="1" t="s">
         <x:v>2587</x:v>
@@ -69617,10 +69693,10 @@
     </x:row>
     <x:row r="75" spans="1:10">
       <x:c r="A75" s="1" t="s">
-        <x:v>2608</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
         <x:v>2704</x:v>
@@ -69641,7 +69717,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I75" s="1">
-        <x:v>600000</x:v>
+        <x:v>1471226</x:v>
       </x:c>
       <x:c r="J75" s="1" t="s">
         <x:v>2587</x:v>
@@ -69649,10 +69725,10 @@
     </x:row>
     <x:row r="76" spans="1:10">
       <x:c r="A76" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
         <x:v>2195</x:v>
@@ -69673,7 +69749,7 @@
         <x:v>2629</x:v>
       </x:c>
       <x:c r="I76" s="1">
-        <x:v>1019964</x:v>
+        <x:v>943006</x:v>
       </x:c>
       <x:c r="J76" s="1" t="s">
         <x:v>2587</x:v>
@@ -69681,10 +69757,10 @@
     </x:row>
     <x:row r="77" spans="1:10">
       <x:c r="A77" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
         <x:v>2195</x:v>
@@ -69705,7 +69781,7 @@
         <x:v>2629</x:v>
       </x:c>
       <x:c r="I77" s="1">
-        <x:v>943006</x:v>
+        <x:v>1019964</x:v>
       </x:c>
       <x:c r="J77" s="1" t="s">
         <x:v>2587</x:v>
@@ -69745,10 +69821,10 @@
     </x:row>
     <x:row r="79" spans="1:10">
       <x:c r="A79" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
         <x:v>2209</x:v>
@@ -69769,7 +69845,7 @@
         <x:v>2599</x:v>
       </x:c>
       <x:c r="I79" s="1">
-        <x:v>1131345</x:v>
+        <x:v>1019167</x:v>
       </x:c>
       <x:c r="J79" s="1" t="s">
         <x:v>2587</x:v>
@@ -69777,10 +69853,10 @@
     </x:row>
     <x:row r="80" spans="1:10">
       <x:c r="A80" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
         <x:v>2209</x:v>
@@ -69801,7 +69877,7 @@
         <x:v>2599</x:v>
       </x:c>
       <x:c r="I80" s="1">
-        <x:v>1019167</x:v>
+        <x:v>1131345</x:v>
       </x:c>
       <x:c r="J80" s="1" t="s">
         <x:v>2587</x:v>
@@ -69833,7 +69909,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I81" s="1">
-        <x:v>2475165</x:v>
+        <x:v>2477373</x:v>
       </x:c>
       <x:c r="J81" s="1" t="s">
         <x:v>2587</x:v>
@@ -71473,48 +71549,48 @@
     </x:row>
     <x:row r="133" spans="1:10">
       <x:c r="A133" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="B133" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="C133" s="1" t="s">
-        <x:v>2760</x:v>
+        <x:v>2758</x:v>
       </x:c>
       <x:c r="D133" s="1" t="s">
-        <x:v>2761</x:v>
+        <x:v>2759</x:v>
       </x:c>
       <x:c r="E133" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="F133" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="G133" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H133" s="1" t="s">
-        <x:v>2762</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="I133" s="1">
-        <x:v>20483</x:v>
+        <x:v>4075</x:v>
       </x:c>
       <x:c r="J133" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2587</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:10">
       <x:c r="A134" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B134" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C134" s="1" t="s">
-        <x:v>2763</x:v>
+        <x:v>2760</x:v>
       </x:c>
       <x:c r="D134" s="1" t="s">
-        <x:v>2764</x:v>
+        <x:v>2761</x:v>
       </x:c>
       <x:c r="E134" s="1" t="s">
         <x:v>2584</x:v>
@@ -71523,16 +71599,16 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G134" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="H134" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2762</x:v>
       </x:c>
       <x:c r="I134" s="1">
-        <x:v>1927706</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="J134" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2618</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:10">
@@ -71543,10 +71619,10 @@
         <x:v>2625</x:v>
       </x:c>
       <x:c r="C135" s="1" t="s">
-        <x:v>2765</x:v>
+        <x:v>2763</x:v>
       </x:c>
       <x:c r="D135" s="1" t="s">
-        <x:v>2766</x:v>
+        <x:v>2764</x:v>
       </x:c>
       <x:c r="E135" s="1" t="s">
         <x:v>2584</x:v>
@@ -71555,16 +71631,16 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G135" s="1" t="s">
-        <x:v>222</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H135" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="I135" s="1">
-        <x:v>817066</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="J135" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2587</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:10">
@@ -71575,10 +71651,10 @@
         <x:v>2625</x:v>
       </x:c>
       <x:c r="C136" s="1" t="s">
-        <x:v>2398</x:v>
+        <x:v>2765</x:v>
       </x:c>
       <x:c r="D136" s="1" t="s">
-        <x:v>269</x:v>
+        <x:v>2766</x:v>
       </x:c>
       <x:c r="E136" s="1" t="s">
         <x:v>2584</x:v>
@@ -71587,45 +71663,45 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G136" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="H136" s="1" t="s">
-        <x:v>2673</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="I136" s="1">
-        <x:v>88256</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="J136" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2618</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:10">
       <x:c r="A137" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="B137" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="C137" s="1" t="s">
-        <x:v>2767</x:v>
+        <x:v>2398</x:v>
       </x:c>
       <x:c r="D137" s="1" t="s">
-        <x:v>2768</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="E137" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="F137" s="1" t="s">
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G137" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H137" s="1" t="s">
-        <x:v>2762</x:v>
+        <x:v>2673</x:v>
       </x:c>
       <x:c r="I137" s="1">
-        <x:v>75000</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="J137" s="1" t="s">
         <x:v>2587</x:v>
@@ -71633,95 +71709,95 @@
     </x:row>
     <x:row r="138" spans="1:10">
       <x:c r="A138" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="B138" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="C138" s="1" t="s">
-        <x:v>2769</x:v>
+        <x:v>2767</x:v>
       </x:c>
       <x:c r="D138" s="1" t="s">
-        <x:v>1088</x:v>
+        <x:v>2768</x:v>
       </x:c>
       <x:c r="E138" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="F138" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="G138" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H138" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2762</x:v>
       </x:c>
       <x:c r="I138" s="1">
-        <x:v>10041119</x:v>
+        <x:v>75000</x:v>
       </x:c>
       <x:c r="J138" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2587</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:10">
       <x:c r="A139" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="B139" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="C139" s="1" t="s">
-        <x:v>2770</x:v>
+        <x:v>2769</x:v>
       </x:c>
       <x:c r="D139" s="1" t="s">
-        <x:v>2771</x:v>
+        <x:v>1088</x:v>
       </x:c>
       <x:c r="E139" s="1" t="s">
         <x:v>2584</x:v>
       </x:c>
       <x:c r="F139" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="G139" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H139" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="I139" s="1">
-        <x:v>1491280</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="J139" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2618</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:10">
       <x:c r="A140" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B140" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C140" s="1" t="s">
-        <x:v>2414</x:v>
+        <x:v>2770</x:v>
       </x:c>
       <x:c r="D140" s="1" t="s">
-        <x:v>888</x:v>
+        <x:v>2771</x:v>
       </x:c>
       <x:c r="E140" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="F140" s="1" t="s">
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G140" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H140" s="1" t="s">
-        <x:v>2681</x:v>
+        <x:v>2607</x:v>
       </x:c>
       <x:c r="I140" s="1">
-        <x:v>75844</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="J140" s="1" t="s">
         <x:v>2587</x:v>
@@ -71729,31 +71805,31 @@
     </x:row>
     <x:row r="141" spans="1:10">
       <x:c r="A141" s="1" t="s">
-        <x:v>2608</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="B141" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="C141" s="1" t="s">
-        <x:v>2418</x:v>
+        <x:v>2414</x:v>
       </x:c>
       <x:c r="D141" s="1" t="s">
-        <x:v>1483</x:v>
+        <x:v>888</x:v>
       </x:c>
       <x:c r="E141" s="1" t="s">
         <x:v>2594</x:v>
       </x:c>
       <x:c r="F141" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="G141" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="H141" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2681</x:v>
       </x:c>
       <x:c r="I141" s="1">
-        <x:v>700000</x:v>
+        <x:v>75844</x:v>
       </x:c>
       <x:c r="J141" s="1" t="s">
         <x:v>2587</x:v>
@@ -71761,16 +71837,16 @@
     </x:row>
     <x:row r="142" spans="1:10">
       <x:c r="A142" s="1" t="s">
-        <x:v>167</x:v>
+        <x:v>2608</x:v>
       </x:c>
       <x:c r="B142" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>2609</x:v>
       </x:c>
       <x:c r="C142" s="1" t="s">
-        <x:v>2772</x:v>
+        <x:v>2418</x:v>
       </x:c>
       <x:c r="D142" s="1" t="s">
-        <x:v>2773</x:v>
+        <x:v>1483</x:v>
       </x:c>
       <x:c r="E142" s="1" t="s">
         <x:v>2594</x:v>
@@ -71779,13 +71855,13 @@
         <x:v>2595</x:v>
       </x:c>
       <x:c r="G142" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H142" s="1" t="s">
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I142" s="1">
-        <x:v>902547</x:v>
+        <x:v>700000</x:v>
       </x:c>
       <x:c r="J142" s="1" t="s">
         <x:v>2587</x:v>
@@ -71793,16 +71869,16 @@
     </x:row>
     <x:row r="143" spans="1:10">
       <x:c r="A143" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B143" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C143" s="1" t="s">
-        <x:v>2432</x:v>
+        <x:v>2772</x:v>
       </x:c>
       <x:c r="D143" s="1" t="s">
-        <x:v>1588</x:v>
+        <x:v>2773</x:v>
       </x:c>
       <x:c r="E143" s="1" t="s">
         <x:v>2594</x:v>
@@ -71811,13 +71887,13 @@
         <x:v>2595</x:v>
       </x:c>
       <x:c r="G143" s="1" t="s">
-        <x:v>733</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H143" s="1" t="s">
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I143" s="1">
-        <x:v>823496</x:v>
+        <x:v>902547</x:v>
       </x:c>
       <x:c r="J143" s="1" t="s">
         <x:v>2587</x:v>
@@ -71831,25 +71907,25 @@
         <x:v>2601</x:v>
       </x:c>
       <x:c r="C144" s="1" t="s">
-        <x:v>2433</x:v>
+        <x:v>2432</x:v>
       </x:c>
       <x:c r="D144" s="1" t="s">
-        <x:v>493</x:v>
+        <x:v>1588</x:v>
       </x:c>
       <x:c r="E144" s="1" t="s">
         <x:v>2594</x:v>
       </x:c>
       <x:c r="F144" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="G144" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>733</x:v>
       </x:c>
       <x:c r="H144" s="1" t="s">
-        <x:v>2673</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="I144" s="1">
-        <x:v>75320</x:v>
+        <x:v>823496</x:v>
       </x:c>
       <x:c r="J144" s="1" t="s">
         <x:v>2587</x:v>
@@ -71857,31 +71933,31 @@
     </x:row>
     <x:row r="145" spans="1:10">
       <x:c r="A145" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="B145" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="C145" s="1" t="s">
-        <x:v>2441</x:v>
+        <x:v>2433</x:v>
       </x:c>
       <x:c r="D145" s="1" t="s">
-        <x:v>1450</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="E145" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="F145" s="1" t="s">
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G145" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H145" s="1" t="s">
-        <x:v>2697</x:v>
+        <x:v>2673</x:v>
       </x:c>
       <x:c r="I145" s="1">
-        <x:v>1987660</x:v>
+        <x:v>75320</x:v>
       </x:c>
       <x:c r="J145" s="1" t="s">
         <x:v>2587</x:v>
@@ -71889,16 +71965,16 @@
     </x:row>
     <x:row r="146" spans="1:10">
       <x:c r="A146" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="B146" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="C146" s="1" t="s">
-        <x:v>2774</x:v>
+        <x:v>2441</x:v>
       </x:c>
       <x:c r="D146" s="1" t="s">
-        <x:v>2775</x:v>
+        <x:v>1450</x:v>
       </x:c>
       <x:c r="E146" s="1" t="s">
         <x:v>2584</x:v>
@@ -71907,13 +71983,13 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G146" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H146" s="1" t="s">
-        <x:v>2590</x:v>
+        <x:v>2697</x:v>
       </x:c>
       <x:c r="I146" s="1">
-        <x:v>74382</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="J146" s="1" t="s">
         <x:v>2587</x:v>
@@ -71927,10 +72003,10 @@
         <x:v>2583</x:v>
       </x:c>
       <x:c r="C147" s="1" t="s">
-        <x:v>2456</x:v>
+        <x:v>2774</x:v>
       </x:c>
       <x:c r="D147" s="1" t="s">
-        <x:v>591</x:v>
+        <x:v>2775</x:v>
       </x:c>
       <x:c r="E147" s="1" t="s">
         <x:v>2584</x:v>
@@ -71939,13 +72015,13 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G147" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H147" s="1" t="s">
-        <x:v>2613</x:v>
+        <x:v>2590</x:v>
       </x:c>
       <x:c r="I147" s="1">
-        <x:v>105040</x:v>
+        <x:v>74382</x:v>
       </x:c>
       <x:c r="J147" s="1" t="s">
         <x:v>2587</x:v>
@@ -71959,10 +72035,10 @@
         <x:v>2583</x:v>
       </x:c>
       <x:c r="C148" s="1" t="s">
-        <x:v>2459</x:v>
+        <x:v>2456</x:v>
       </x:c>
       <x:c r="D148" s="1" t="s">
-        <x:v>496</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="E148" s="1" t="s">
         <x:v>2584</x:v>
@@ -71971,33 +72047,33 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G148" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H148" s="1" t="s">
-        <x:v>2633</x:v>
+        <x:v>2613</x:v>
       </x:c>
       <x:c r="I148" s="1">
-        <x:v>56045</x:v>
+        <x:v>105040</x:v>
       </x:c>
       <x:c r="J148" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2587</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:10">
       <x:c r="A149" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B149" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C149" s="1" t="s">
-        <x:v>2460</x:v>
+        <x:v>2459</x:v>
       </x:c>
       <x:c r="D149" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="E149" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="F149" s="1" t="s">
         <x:v>2585</x:v>
@@ -72006,13 +72082,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="H149" s="1" t="s">
-        <x:v>2613</x:v>
+        <x:v>2633</x:v>
       </x:c>
       <x:c r="I149" s="1">
-        <x:v>75281</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="J149" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2618</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:10">
@@ -72023,10 +72099,10 @@
         <x:v>2601</x:v>
       </x:c>
       <x:c r="C150" s="1" t="s">
-        <x:v>2776</x:v>
+        <x:v>2460</x:v>
       </x:c>
       <x:c r="D150" s="1" t="s">
-        <x:v>2777</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="E150" s="1" t="s">
         <x:v>2594</x:v>
@@ -72035,13 +72111,13 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G150" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H150" s="1" t="s">
-        <x:v>2755</x:v>
+        <x:v>2613</x:v>
       </x:c>
       <x:c r="I150" s="1">
-        <x:v>852561</x:v>
+        <x:v>75281</x:v>
       </x:c>
       <x:c r="J150" s="1" t="s">
         <x:v>2587</x:v>
@@ -72049,31 +72125,31 @@
     </x:row>
     <x:row r="151" spans="1:10">
       <x:c r="A151" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="B151" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="C151" s="1" t="s">
-        <x:v>2466</x:v>
+        <x:v>2776</x:v>
       </x:c>
       <x:c r="D151" s="1" t="s">
-        <x:v>1743</x:v>
+        <x:v>2777</x:v>
       </x:c>
       <x:c r="E151" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="F151" s="1" t="s">
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G151" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H151" s="1" t="s">
-        <x:v>2673</x:v>
+        <x:v>2755</x:v>
       </x:c>
       <x:c r="I151" s="1">
-        <x:v>74852</x:v>
+        <x:v>852561</x:v>
       </x:c>
       <x:c r="J151" s="1" t="s">
         <x:v>2587</x:v>
@@ -72087,10 +72163,10 @@
         <x:v>2583</x:v>
       </x:c>
       <x:c r="C152" s="1" t="s">
-        <x:v>2778</x:v>
+        <x:v>2466</x:v>
       </x:c>
       <x:c r="D152" s="1" t="s">
-        <x:v>2779</x:v>
+        <x:v>1743</x:v>
       </x:c>
       <x:c r="E152" s="1" t="s">
         <x:v>2584</x:v>
@@ -72099,13 +72175,13 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G152" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H152" s="1" t="s">
-        <x:v>2691</x:v>
+        <x:v>2673</x:v>
       </x:c>
       <x:c r="I152" s="1">
-        <x:v>111599</x:v>
+        <x:v>74852</x:v>
       </x:c>
       <x:c r="J152" s="1" t="s">
         <x:v>2587</x:v>
@@ -72119,25 +72195,25 @@
         <x:v>2583</x:v>
       </x:c>
       <x:c r="C153" s="1" t="s">
-        <x:v>2780</x:v>
+        <x:v>2778</x:v>
       </x:c>
       <x:c r="D153" s="1" t="s">
-        <x:v>634</x:v>
+        <x:v>2779</x:v>
       </x:c>
       <x:c r="E153" s="1" t="s">
         <x:v>2584</x:v>
       </x:c>
       <x:c r="F153" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="G153" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H153" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2691</x:v>
       </x:c>
       <x:c r="I153" s="1">
-        <x:v>10046680</x:v>
+        <x:v>111599</x:v>
       </x:c>
       <x:c r="J153" s="1" t="s">
         <x:v>2587</x:v>
@@ -72145,31 +72221,31 @@
     </x:row>
     <x:row r="154" spans="1:10">
       <x:c r="A154" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B154" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C154" s="1" t="s">
-        <x:v>2478</x:v>
+        <x:v>2780</x:v>
       </x:c>
       <x:c r="D154" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="E154" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="F154" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="G154" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H154" s="1" t="s">
-        <x:v>2590</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="I154" s="1">
-        <x:v>565950</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="J154" s="1" t="s">
         <x:v>2587</x:v>
@@ -72183,10 +72259,10 @@
         <x:v>2601</x:v>
       </x:c>
       <x:c r="C155" s="1" t="s">
-        <x:v>2481</x:v>
+        <x:v>2478</x:v>
       </x:c>
       <x:c r="D155" s="1" t="s">
-        <x:v>966</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E155" s="1" t="s">
         <x:v>2594</x:v>
@@ -72195,13 +72271,13 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G155" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H155" s="1" t="s">
-        <x:v>2613</x:v>
+        <x:v>2590</x:v>
       </x:c>
       <x:c r="I155" s="1">
-        <x:v>75617</x:v>
+        <x:v>565950</x:v>
       </x:c>
       <x:c r="J155" s="1" t="s">
         <x:v>2587</x:v>
@@ -72209,31 +72285,31 @@
     </x:row>
     <x:row r="156" spans="1:10">
       <x:c r="A156" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="B156" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="C156" s="1" t="s">
-        <x:v>2781</x:v>
+        <x:v>2481</x:v>
       </x:c>
       <x:c r="D156" s="1" t="s">
-        <x:v>2782</x:v>
+        <x:v>966</x:v>
       </x:c>
       <x:c r="E156" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="F156" s="1" t="s">
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G156" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H156" s="1" t="s">
-        <x:v>2623</x:v>
+        <x:v>2613</x:v>
       </x:c>
       <x:c r="I156" s="1">
-        <x:v>380377</x:v>
+        <x:v>75617</x:v>
       </x:c>
       <x:c r="J156" s="1" t="s">
         <x:v>2587</x:v>
@@ -72241,16 +72317,16 @@
     </x:row>
     <x:row r="157" spans="1:10">
       <x:c r="A157" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B157" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C157" s="1" t="s">
-        <x:v>2484</x:v>
+        <x:v>2781</x:v>
       </x:c>
       <x:c r="D157" s="1" t="s">
-        <x:v>655</x:v>
+        <x:v>2782</x:v>
       </x:c>
       <x:c r="E157" s="1" t="s">
         <x:v>2584</x:v>
@@ -72259,13 +72335,13 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G157" s="1" t="s">
-        <x:v>222</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H157" s="1" t="s">
-        <x:v>2712</x:v>
+        <x:v>2623</x:v>
       </x:c>
       <x:c r="I157" s="1">
-        <x:v>817169</x:v>
+        <x:v>380377</x:v>
       </x:c>
       <x:c r="J157" s="1" t="s">
         <x:v>2587</x:v>
@@ -72273,95 +72349,95 @@
     </x:row>
     <x:row r="158" spans="1:10">
       <x:c r="A158" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="B158" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="C158" s="1" t="s">
-        <x:v>2783</x:v>
+        <x:v>2484</x:v>
       </x:c>
       <x:c r="D158" s="1" t="s">
-        <x:v>2784</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="E158" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="F158" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="G158" s="1" t="s">
-        <x:v>238</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="H158" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2712</x:v>
       </x:c>
       <x:c r="I158" s="1">
-        <x:v>1531015</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="J158" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2587</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:10">
       <x:c r="A159" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="B159" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="C159" s="1" t="s">
-        <x:v>2490</x:v>
+        <x:v>2783</x:v>
       </x:c>
       <x:c r="D159" s="1" t="s">
-        <x:v>1672</x:v>
+        <x:v>2784</x:v>
       </x:c>
       <x:c r="E159" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="F159" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="G159" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="H159" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="I159" s="1">
-        <x:v>157560</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="J159" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2618</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:10">
       <x:c r="A160" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B160" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C160" s="1" t="s">
-        <x:v>2492</x:v>
+        <x:v>2490</x:v>
       </x:c>
       <x:c r="D160" s="1" t="s">
-        <x:v>1329</x:v>
+        <x:v>1672</x:v>
       </x:c>
       <x:c r="E160" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="F160" s="1" t="s">
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G160" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H160" s="1" t="s">
-        <x:v>2785</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="I160" s="1">
-        <x:v>2791716</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="J160" s="1" t="s">
         <x:v>2587</x:v>
@@ -72375,10 +72451,10 @@
         <x:v>2625</x:v>
       </x:c>
       <x:c r="C161" s="1" t="s">
-        <x:v>2494</x:v>
+        <x:v>2492</x:v>
       </x:c>
       <x:c r="D161" s="1" t="s">
-        <x:v>1675</x:v>
+        <x:v>1329</x:v>
       </x:c>
       <x:c r="E161" s="1" t="s">
         <x:v>2594</x:v>
@@ -72387,13 +72463,13 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G161" s="1" t="s">
-        <x:v>601</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H161" s="1" t="s">
-        <x:v>2636</x:v>
+        <x:v>2785</x:v>
       </x:c>
       <x:c r="I161" s="1">
-        <x:v>1789991</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="J161" s="1" t="s">
         <x:v>2587</x:v>
@@ -72401,16 +72477,16 @@
     </x:row>
     <x:row r="162" spans="1:10">
       <x:c r="A162" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="B162" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="C162" s="1" t="s">
-        <x:v>2786</x:v>
+        <x:v>2494</x:v>
       </x:c>
       <x:c r="D162" s="1" t="s">
-        <x:v>2787</x:v>
+        <x:v>1675</x:v>
       </x:c>
       <x:c r="E162" s="1" t="s">
         <x:v>2594</x:v>
@@ -72419,13 +72495,13 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G162" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="H162" s="1" t="s">
-        <x:v>2613</x:v>
+        <x:v>2636</x:v>
       </x:c>
       <x:c r="I162" s="1">
-        <x:v>1543316</x:v>
+        <x:v>1789991</x:v>
       </x:c>
       <x:c r="J162" s="1" t="s">
         <x:v>2587</x:v>
@@ -72433,42 +72509,42 @@
     </x:row>
     <x:row r="163" spans="1:10">
       <x:c r="A163" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="B163" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="C163" s="1" t="s">
-        <x:v>2788</x:v>
+        <x:v>2786</x:v>
       </x:c>
       <x:c r="D163" s="1" t="s">
-        <x:v>2789</x:v>
+        <x:v>2787</x:v>
       </x:c>
       <x:c r="E163" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="F163" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="G163" s="1" t="s">
-        <x:v>222</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H163" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2613</x:v>
       </x:c>
       <x:c r="I163" s="1">
-        <x:v>119844</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="J163" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2587</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:10">
       <x:c r="A164" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B164" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C164" s="1" t="s">
         <x:v>2788</x:v>
@@ -72489,7 +72565,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I164" s="1">
-        <x:v>10015605</x:v>
+        <x:v>119844</x:v>
       </x:c>
       <x:c r="J164" s="1" t="s">
         <x:v>2618</x:v>
@@ -72497,34 +72573,34 @@
     </x:row>
     <x:row r="165" spans="1:10">
       <x:c r="A165" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="B165" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="C165" s="1" t="s">
-        <x:v>2790</x:v>
+        <x:v>2788</x:v>
       </x:c>
       <x:c r="D165" s="1" t="s">
-        <x:v>2791</x:v>
+        <x:v>2789</x:v>
       </x:c>
       <x:c r="E165" s="1" t="s">
         <x:v>2584</x:v>
       </x:c>
       <x:c r="F165" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="G165" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="H165" s="1" t="s">
-        <x:v>2684</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="I165" s="1">
-        <x:v>103020</x:v>
+        <x:v>10015605</x:v>
       </x:c>
       <x:c r="J165" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2618</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:10">
@@ -72535,10 +72611,10 @@
         <x:v>2583</x:v>
       </x:c>
       <x:c r="C166" s="1" t="s">
-        <x:v>2792</x:v>
+        <x:v>2790</x:v>
       </x:c>
       <x:c r="D166" s="1" t="s">
-        <x:v>2793</x:v>
+        <x:v>2791</x:v>
       </x:c>
       <x:c r="E166" s="1" t="s">
         <x:v>2584</x:v>
@@ -72547,13 +72623,13 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G166" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H166" s="1" t="s">
         <x:v>2684</x:v>
       </x:c>
       <x:c r="I166" s="1">
-        <x:v>182279</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="J166" s="1" t="s">
         <x:v>2587</x:v>
@@ -72561,16 +72637,16 @@
     </x:row>
     <x:row r="167" spans="1:10">
       <x:c r="A167" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B167" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C167" s="1" t="s">
-        <x:v>2501</x:v>
+        <x:v>2792</x:v>
       </x:c>
       <x:c r="D167" s="1" t="s">
-        <x:v>1693</x:v>
+        <x:v>2793</x:v>
       </x:c>
       <x:c r="E167" s="1" t="s">
         <x:v>2584</x:v>
@@ -72579,13 +72655,13 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G167" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="H167" s="1" t="s">
-        <x:v>2590</x:v>
+        <x:v>2684</x:v>
       </x:c>
       <x:c r="I167" s="1">
-        <x:v>902176</x:v>
+        <x:v>182279</x:v>
       </x:c>
       <x:c r="J167" s="1" t="s">
         <x:v>2587</x:v>
@@ -72593,16 +72669,16 @@
     </x:row>
     <x:row r="168" spans="1:10">
       <x:c r="A168" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="B168" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="C168" s="1" t="s">
-        <x:v>2794</x:v>
+        <x:v>2501</x:v>
       </x:c>
       <x:c r="D168" s="1" t="s">
-        <x:v>2795</x:v>
+        <x:v>1693</x:v>
       </x:c>
       <x:c r="E168" s="1" t="s">
         <x:v>2584</x:v>
@@ -72611,13 +72687,13 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G168" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H168" s="1" t="s">
-        <x:v>2633</x:v>
+        <x:v>2590</x:v>
       </x:c>
       <x:c r="I168" s="1">
-        <x:v>2771797</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="J168" s="1" t="s">
         <x:v>2587</x:v>
@@ -72625,63 +72701,63 @@
     </x:row>
     <x:row r="169" spans="1:10">
       <x:c r="A169" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="B169" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="C169" s="1" t="s">
-        <x:v>2508</x:v>
+        <x:v>2794</x:v>
       </x:c>
       <x:c r="D169" s="1" t="s">
-        <x:v>736</x:v>
+        <x:v>2795</x:v>
       </x:c>
       <x:c r="E169" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="F169" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="G169" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H169" s="1" t="s">
-        <x:v>2664</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="I169" s="1">
-        <x:v>73673</x:v>
+        <x:v>77424</x:v>
       </x:c>
       <x:c r="J169" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2618</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:10">
       <x:c r="A170" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B170" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C170" s="1" t="s">
-        <x:v>2514</x:v>
+        <x:v>2796</x:v>
       </x:c>
       <x:c r="D170" s="1" t="s">
-        <x:v>1925</x:v>
+        <x:v>2797</x:v>
       </x:c>
       <x:c r="E170" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="F170" s="1" t="s">
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G170" s="1" t="s">
-        <x:v>746</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H170" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2633</x:v>
       </x:c>
       <x:c r="I170" s="1">
-        <x:v>2835078</x:v>
+        <x:v>2771797</x:v>
       </x:c>
       <x:c r="J170" s="1" t="s">
         <x:v>2587</x:v>
@@ -72689,31 +72765,31 @@
     </x:row>
     <x:row r="171" spans="1:10">
       <x:c r="A171" s="1" t="s">
-        <x:v>2608</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="B171" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="C171" s="1" t="s">
-        <x:v>2522</x:v>
+        <x:v>2508</x:v>
       </x:c>
       <x:c r="D171" s="1" t="s">
-        <x:v>1813</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="E171" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="F171" s="1" t="s">
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G171" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="H171" s="1" t="s">
         <x:v>2664</x:v>
       </x:c>
       <x:c r="I171" s="1">
-        <x:v>600000</x:v>
+        <x:v>73673</x:v>
       </x:c>
       <x:c r="J171" s="1" t="s">
         <x:v>2587</x:v>
@@ -72721,31 +72797,31 @@
     </x:row>
     <x:row r="172" spans="1:10">
       <x:c r="A172" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="B172" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="C172" s="1" t="s">
-        <x:v>2522</x:v>
+        <x:v>2514</x:v>
       </x:c>
       <x:c r="D172" s="1" t="s">
-        <x:v>1813</x:v>
+        <x:v>1925</x:v>
       </x:c>
       <x:c r="E172" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="F172" s="1" t="s">
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G172" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="H172" s="1" t="s">
-        <x:v>2664</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="I172" s="1">
-        <x:v>63084</x:v>
+        <x:v>2835078</x:v>
       </x:c>
       <x:c r="J172" s="1" t="s">
         <x:v>2587</x:v>
@@ -72753,10 +72829,10 @@
     </x:row>
     <x:row r="173" spans="1:10">
       <x:c r="A173" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="B173" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="C173" s="1" t="s">
         <x:v>2522</x:v>
@@ -72777,7 +72853,7 @@
         <x:v>2664</x:v>
       </x:c>
       <x:c r="I173" s="1">
-        <x:v>1529188</x:v>
+        <x:v>63084</x:v>
       </x:c>
       <x:c r="J173" s="1" t="s">
         <x:v>2587</x:v>
@@ -72785,16 +72861,16 @@
     </x:row>
     <x:row r="174" spans="1:10">
       <x:c r="A174" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2608</x:v>
       </x:c>
       <x:c r="B174" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2609</x:v>
       </x:c>
       <x:c r="C174" s="1" t="s">
-        <x:v>2524</x:v>
+        <x:v>2522</x:v>
       </x:c>
       <x:c r="D174" s="1" t="s">
-        <x:v>543</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="E174" s="1" t="s">
         <x:v>2584</x:v>
@@ -72803,13 +72879,13 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G174" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H174" s="1" t="s">
-        <x:v>2785</x:v>
+        <x:v>2664</x:v>
       </x:c>
       <x:c r="I174" s="1">
-        <x:v>1015758</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="J174" s="1" t="s">
         <x:v>2587</x:v>
@@ -72817,31 +72893,31 @@
     </x:row>
     <x:row r="175" spans="1:10">
       <x:c r="A175" s="1" t="s">
-        <x:v>2650</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B175" s="1" t="s">
-        <x:v>2651</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C175" s="1" t="s">
-        <x:v>2796</x:v>
+        <x:v>2522</x:v>
       </x:c>
       <x:c r="D175" s="1" t="s">
-        <x:v>2797</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="E175" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="F175" s="1" t="s">
-        <x:v>2798</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="G175" s="1" t="s">
-        <x:v>2799</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H175" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2664</x:v>
       </x:c>
       <x:c r="I175" s="1">
-        <x:v>10000</x:v>
+        <x:v>1529188</x:v>
       </x:c>
       <x:c r="J175" s="1" t="s">
         <x:v>2587</x:v>
@@ -72849,63 +72925,63 @@
     </x:row>
     <x:row r="176" spans="1:10">
       <x:c r="A176" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="B176" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="C176" s="1" t="s">
-        <x:v>2800</x:v>
+        <x:v>2524</x:v>
       </x:c>
       <x:c r="D176" s="1" t="s">
-        <x:v>2801</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="E176" s="1" t="s">
         <x:v>2584</x:v>
       </x:c>
       <x:c r="F176" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="G176" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H176" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2785</x:v>
       </x:c>
       <x:c r="I176" s="1">
-        <x:v>424596</x:v>
+        <x:v>1015758</x:v>
       </x:c>
       <x:c r="J176" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2587</x:v>
       </x:c>
     </x:row>
     <x:row r="177" spans="1:10">
       <x:c r="A177" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2650</x:v>
       </x:c>
       <x:c r="B177" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="C177" s="1" t="s">
-        <x:v>2802</x:v>
+        <x:v>2798</x:v>
       </x:c>
       <x:c r="D177" s="1" t="s">
-        <x:v>2803</x:v>
+        <x:v>2799</x:v>
       </x:c>
       <x:c r="E177" s="1" t="s">
         <x:v>2594</x:v>
       </x:c>
       <x:c r="F177" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G177" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>2801</x:v>
       </x:c>
       <x:c r="H177" s="1" t="s">
-        <x:v>2678</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="I177" s="1">
-        <x:v>1306863</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="J177" s="1" t="s">
         <x:v>2587</x:v>
@@ -72913,42 +72989,42 @@
     </x:row>
     <x:row r="178" spans="1:10">
       <x:c r="A178" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="B178" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="C178" s="1" t="s">
-        <x:v>2539</x:v>
+        <x:v>2802</x:v>
       </x:c>
       <x:c r="D178" s="1" t="s">
-        <x:v>1864</x:v>
+        <x:v>2803</x:v>
       </x:c>
       <x:c r="E178" s="1" t="s">
         <x:v>2584</x:v>
       </x:c>
       <x:c r="F178" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="G178" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="H178" s="1" t="s">
-        <x:v>2673</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="I178" s="1">
-        <x:v>889852</x:v>
+        <x:v>429577</x:v>
       </x:c>
       <x:c r="J178" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2618</x:v>
       </x:c>
     </x:row>
     <x:row r="179" spans="1:10">
       <x:c r="A179" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="B179" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="C179" s="1" t="s">
         <x:v>2804</x:v>
@@ -72957,7 +73033,7 @@
         <x:v>2805</x:v>
       </x:c>
       <x:c r="E179" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="F179" s="1" t="s">
         <x:v>2585</x:v>
@@ -72966,10 +73042,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H179" s="1" t="s">
-        <x:v>2664</x:v>
+        <x:v>2678</x:v>
       </x:c>
       <x:c r="I179" s="1">
-        <x:v>362000</x:v>
+        <x:v>1306863</x:v>
       </x:c>
       <x:c r="J179" s="1" t="s">
         <x:v>2587</x:v>
@@ -72983,10 +73059,10 @@
         <x:v>2583</x:v>
       </x:c>
       <x:c r="C180" s="1" t="s">
-        <x:v>2806</x:v>
+        <x:v>2539</x:v>
       </x:c>
       <x:c r="D180" s="1" t="s">
-        <x:v>2807</x:v>
+        <x:v>1864</x:v>
       </x:c>
       <x:c r="E180" s="1" t="s">
         <x:v>2584</x:v>
@@ -72998,10 +73074,10 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="H180" s="1" t="s">
-        <x:v>2762</x:v>
+        <x:v>2673</x:v>
       </x:c>
       <x:c r="I180" s="1">
-        <x:v>1012792</x:v>
+        <x:v>889852</x:v>
       </x:c>
       <x:c r="J180" s="1" t="s">
         <x:v>2587</x:v>
@@ -73009,31 +73085,31 @@
     </x:row>
     <x:row r="181" spans="1:10">
       <x:c r="A181" s="1" t="s">
-        <x:v>2608</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B181" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C181" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2806</x:v>
       </x:c>
       <x:c r="D181" s="1" t="s">
-        <x:v>764</x:v>
+        <x:v>2807</x:v>
       </x:c>
       <x:c r="E181" s="1" t="s">
         <x:v>2584</x:v>
       </x:c>
       <x:c r="F181" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="G181" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H181" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2664</x:v>
       </x:c>
       <x:c r="I181" s="1">
-        <x:v>300000</x:v>
+        <x:v>381352</x:v>
       </x:c>
       <x:c r="J181" s="1" t="s">
         <x:v>2587</x:v>
@@ -73047,10 +73123,10 @@
         <x:v>2583</x:v>
       </x:c>
       <x:c r="C182" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2808</x:v>
       </x:c>
       <x:c r="D182" s="1" t="s">
-        <x:v>836</x:v>
+        <x:v>2809</x:v>
       </x:c>
       <x:c r="E182" s="1" t="s">
         <x:v>2584</x:v>
@@ -73059,15 +73135,79 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="G182" s="1" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="H182" s="1" t="s">
+        <x:v>2762</x:v>
+      </x:c>
+      <x:c r="I182" s="1">
+        <x:v>1012792</x:v>
+      </x:c>
+      <x:c r="J182" s="1" t="s">
+        <x:v>2587</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" spans="1:10">
+      <x:c r="A183" s="1" t="s">
+        <x:v>2608</x:v>
+      </x:c>
+      <x:c r="B183" s="1" t="s">
+        <x:v>2609</x:v>
+      </x:c>
+      <x:c r="C183" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="D183" s="1" t="s">
+        <x:v>764</x:v>
+      </x:c>
+      <x:c r="E183" s="1" t="s">
+        <x:v>2584</x:v>
+      </x:c>
+      <x:c r="F183" s="1" t="s">
+        <x:v>2595</x:v>
+      </x:c>
+      <x:c r="G183" s="1" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="H183" s="1" t="s">
+        <x:v>2596</x:v>
+      </x:c>
+      <x:c r="I183" s="1">
+        <x:v>300000</x:v>
+      </x:c>
+      <x:c r="J183" s="1" t="s">
+        <x:v>2587</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" spans="1:10">
+      <x:c r="A184" s="1" t="s">
+        <x:v>2582</x:v>
+      </x:c>
+      <x:c r="B184" s="1" t="s">
+        <x:v>2583</x:v>
+      </x:c>
+      <x:c r="C184" s="1" t="s">
+        <x:v>2560</x:v>
+      </x:c>
+      <x:c r="D184" s="1" t="s">
+        <x:v>836</x:v>
+      </x:c>
+      <x:c r="E184" s="1" t="s">
+        <x:v>2584</x:v>
+      </x:c>
+      <x:c r="F184" s="1" t="s">
+        <x:v>2585</x:v>
+      </x:c>
+      <x:c r="G184" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H182" s="1" t="s">
+      <x:c r="H184" s="1" t="s">
         <x:v>2686</x:v>
       </x:c>
-      <x:c r="I182" s="1">
+      <x:c r="I184" s="1">
         <x:v>487174</x:v>
       </x:c>
-      <x:c r="J182" s="1" t="s">
+      <x:c r="J184" s="1" t="s">
         <x:v>2587</x:v>
       </x:c>
     </x:row>
@@ -73087,7 +73227,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C167"/>
+  <x:dimension ref="A1:C168"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -73134,7 +73274,7 @@
         <x:v>148</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>145696</x:v>
+        <x:v>145958</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>2587</x:v>
@@ -73288,7 +73428,7 @@
         <x:v>555</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>16359294</x:v>
+        <x:v>16401247</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>2618</x:v>
@@ -73882,7 +74022,7 @@
         <x:v>936</x:v>
       </x:c>
       <x:c r="B72" s="1">
-        <x:v>36253398</x:v>
+        <x:v>36255606</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
         <x:v>2587</x:v>
@@ -74410,7 +74550,7 @@
         <x:v>2759</x:v>
       </x:c>
       <x:c r="B120" s="1">
-        <x:v>2750000</x:v>
+        <x:v>2754075</x:v>
       </x:c>
       <x:c r="C120" s="1" t="s">
         <x:v>2587</x:v>
@@ -74795,18 +74935,18 @@
         <x:v>2795</x:v>
       </x:c>
       <x:c r="B155" s="1">
-        <x:v>2771797</x:v>
+        <x:v>77424</x:v>
       </x:c>
       <x:c r="C155" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2618</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:3">
       <x:c r="A156" s="1" t="s">
-        <x:v>736</x:v>
+        <x:v>2797</x:v>
       </x:c>
       <x:c r="B156" s="1">
-        <x:v>73673</x:v>
+        <x:v>2771797</x:v>
       </x:c>
       <x:c r="C156" s="1" t="s">
         <x:v>2587</x:v>
@@ -74814,10 +74954,10 @@
     </x:row>
     <x:row r="157" spans="1:3">
       <x:c r="A157" s="1" t="s">
-        <x:v>1925</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="B157" s="1">
-        <x:v>2835078</x:v>
+        <x:v>73673</x:v>
       </x:c>
       <x:c r="C157" s="1" t="s">
         <x:v>2587</x:v>
@@ -74825,10 +74965,10 @@
     </x:row>
     <x:row r="158" spans="1:3">
       <x:c r="A158" s="1" t="s">
-        <x:v>1813</x:v>
+        <x:v>1925</x:v>
       </x:c>
       <x:c r="B158" s="1">
-        <x:v>2192272</x:v>
+        <x:v>2835078</x:v>
       </x:c>
       <x:c r="C158" s="1" t="s">
         <x:v>2587</x:v>
@@ -74836,10 +74976,10 @@
     </x:row>
     <x:row r="159" spans="1:3">
       <x:c r="A159" s="1" t="s">
-        <x:v>543</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="B159" s="1">
-        <x:v>1015758</x:v>
+        <x:v>2192272</x:v>
       </x:c>
       <x:c r="C159" s="1" t="s">
         <x:v>2587</x:v>
@@ -74847,10 +74987,10 @@
     </x:row>
     <x:row r="160" spans="1:3">
       <x:c r="A160" s="1" t="s">
-        <x:v>2797</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="B160" s="1">
-        <x:v>10000</x:v>
+        <x:v>1015758</x:v>
       </x:c>
       <x:c r="C160" s="1" t="s">
         <x:v>2587</x:v>
@@ -74858,13 +74998,13 @@
     </x:row>
     <x:row r="161" spans="1:3">
       <x:c r="A161" s="1" t="s">
-        <x:v>2801</x:v>
+        <x:v>2799</x:v>
       </x:c>
       <x:c r="B161" s="1">
-        <x:v>424596</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="C161" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2587</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:3">
@@ -74872,18 +75012,18 @@
         <x:v>2803</x:v>
       </x:c>
       <x:c r="B162" s="1">
-        <x:v>1306863</x:v>
+        <x:v>429577</x:v>
       </x:c>
       <x:c r="C162" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2618</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:3">
       <x:c r="A163" s="1" t="s">
-        <x:v>1864</x:v>
+        <x:v>2805</x:v>
       </x:c>
       <x:c r="B163" s="1">
-        <x:v>889852</x:v>
+        <x:v>1306863</x:v>
       </x:c>
       <x:c r="C163" s="1" t="s">
         <x:v>2587</x:v>
@@ -74891,10 +75031,10 @@
     </x:row>
     <x:row r="164" spans="1:3">
       <x:c r="A164" s="1" t="s">
-        <x:v>2805</x:v>
+        <x:v>1864</x:v>
       </x:c>
       <x:c r="B164" s="1">
-        <x:v>362000</x:v>
+        <x:v>889852</x:v>
       </x:c>
       <x:c r="C164" s="1" t="s">
         <x:v>2587</x:v>
@@ -74905,7 +75045,7 @@
         <x:v>2807</x:v>
       </x:c>
       <x:c r="B165" s="1">
-        <x:v>1012792</x:v>
+        <x:v>381352</x:v>
       </x:c>
       <x:c r="C165" s="1" t="s">
         <x:v>2587</x:v>
@@ -74913,10 +75053,10 @@
     </x:row>
     <x:row r="166" spans="1:3">
       <x:c r="A166" s="1" t="s">
-        <x:v>764</x:v>
+        <x:v>2809</x:v>
       </x:c>
       <x:c r="B166" s="1">
-        <x:v>300000</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="C166" s="1" t="s">
         <x:v>2587</x:v>
@@ -74924,12 +75064,23 @@
     </x:row>
     <x:row r="167" spans="1:3">
       <x:c r="A167" s="1" t="s">
+        <x:v>764</x:v>
+      </x:c>
+      <x:c r="B167" s="1">
+        <x:v>300000</x:v>
+      </x:c>
+      <x:c r="C167" s="1" t="s">
+        <x:v>2587</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" spans="1:3">
+      <x:c r="A168" s="1" t="s">
         <x:v>836</x:v>
       </x:c>
-      <x:c r="B167" s="1">
+      <x:c r="B168" s="1">
         <x:v>487174</x:v>
       </x:c>
-      <x:c r="C167" s="1" t="s">
+      <x:c r="C168" s="1" t="s">
         <x:v>2587</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -41382,10 +41382,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C361" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>1724</x:v>
       </x:c>
       <x:c r="D361" s="1" t="s">
-        <x:v>929</x:v>
+        <x:v>1725</x:v>
       </x:c>
       <x:c r="E361" s="1" t="s">
         <x:v>930</x:v>
@@ -41397,7 +41397,7 @@
         <x:v>2209</x:v>
       </x:c>
       <x:c r="H361" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="362" spans="1:8">
@@ -41408,10 +41408,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C362" s="1" t="s">
-        <x:v>1724</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="D362" s="1" t="s">
-        <x:v>1725</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="E362" s="1" t="s">
         <x:v>930</x:v>
@@ -41423,7 +41423,7 @@
         <x:v>2209</x:v>
       </x:c>
       <x:c r="H362" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="363" spans="1:8">
@@ -60982,7 +60982,7 @@
         <x:v>2629</x:v>
       </x:c>
       <x:c r="I18" s="1">
-        <x:v>75206</x:v>
+        <x:v>150412</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
         <x:v>2587</x:v>
@@ -61087,7 +61087,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I21" s="1">
-        <x:v>12894063</x:v>
+        <x:v>19706265</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
         <x:v>2618</x:v>
@@ -61472,7 +61472,7 @@
         <x:v>2607</x:v>
       </x:c>
       <x:c r="I32" s="1">
-        <x:v>75000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
         <x:v>2587</x:v>
@@ -61962,7 +61962,7 @@
         <x:v>2629</x:v>
       </x:c>
       <x:c r="I46" s="1">
-        <x:v>74983</x:v>
+        <x:v>149966</x:v>
       </x:c>
       <x:c r="J46" s="1" t="s">
         <x:v>2587</x:v>
@@ -62067,7 +62067,7 @@
         <x:v>2607</x:v>
       </x:c>
       <x:c r="I49" s="1">
-        <x:v>76342</x:v>
+        <x:v>152684</x:v>
       </x:c>
       <x:c r="J49" s="1" t="s">
         <x:v>2587</x:v>
@@ -62207,7 +62207,7 @@
         <x:v>2673</x:v>
       </x:c>
       <x:c r="I53" s="1">
-        <x:v>76113</x:v>
+        <x:v>152226</x:v>
       </x:c>
       <x:c r="J53" s="1" t="s">
         <x:v>2587</x:v>
@@ -62242,7 +62242,7 @@
         <x:v>2605</x:v>
       </x:c>
       <x:c r="I54" s="1">
-        <x:v>74753</x:v>
+        <x:v>149506</x:v>
       </x:c>
       <x:c r="J54" s="1" t="s">
         <x:v>2587</x:v>
@@ -62942,7 +62942,7 @@
         <x:v>2613</x:v>
       </x:c>
       <x:c r="I74" s="1">
-        <x:v>74932</x:v>
+        <x:v>149864</x:v>
       </x:c>
       <x:c r="J74" s="1" t="s">
         <x:v>2587</x:v>
@@ -62977,7 +62977,7 @@
         <x:v>2684</x:v>
       </x:c>
       <x:c r="I75" s="1">
-        <x:v>75000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="J75" s="1" t="s">
         <x:v>2587</x:v>
@@ -63397,7 +63397,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I87" s="1">
-        <x:v>33778233</x:v>
+        <x:v>36054435</x:v>
       </x:c>
       <x:c r="J87" s="1" t="s">
         <x:v>2587</x:v>
@@ -63502,7 +63502,7 @@
         <x:v>2590</x:v>
       </x:c>
       <x:c r="I90" s="1">
-        <x:v>74699</x:v>
+        <x:v>149398</x:v>
       </x:c>
       <x:c r="J90" s="1" t="s">
         <x:v>2587</x:v>
@@ -63572,7 +63572,7 @@
         <x:v>2636</x:v>
       </x:c>
       <x:c r="I92" s="1">
-        <x:v>75227</x:v>
+        <x:v>150454</x:v>
       </x:c>
       <x:c r="J92" s="1" t="s">
         <x:v>2587</x:v>
@@ -64062,7 +64062,7 @@
         <x:v>2590</x:v>
       </x:c>
       <x:c r="I106" s="1">
-        <x:v>74602</x:v>
+        <x:v>149204</x:v>
       </x:c>
       <x:c r="J106" s="1" t="s">
         <x:v>2587</x:v>
@@ -64132,7 +64132,7 @@
         <x:v>2607</x:v>
       </x:c>
       <x:c r="I108" s="1">
-        <x:v>76114</x:v>
+        <x:v>152228</x:v>
       </x:c>
       <x:c r="J108" s="1" t="s">
         <x:v>2587</x:v>
@@ -64202,7 +64202,7 @@
         <x:v>2724</x:v>
       </x:c>
       <x:c r="I110" s="1">
-        <x:v>75226</x:v>
+        <x:v>150452</x:v>
       </x:c>
       <x:c r="J110" s="1" t="s">
         <x:v>2587</x:v>
@@ -65182,7 +65182,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I138" s="1">
-        <x:v>6723910</x:v>
+        <x:v>10825942</x:v>
       </x:c>
       <x:c r="J138" s="1" t="s">
         <x:v>2618</x:v>
@@ -65217,7 +65217,7 @@
         <x:v>2755</x:v>
       </x:c>
       <x:c r="I139" s="1">
-        <x:v>74692</x:v>
+        <x:v>149384</x:v>
       </x:c>
       <x:c r="J139" s="1" t="s">
         <x:v>2587</x:v>
@@ -65497,7 +65497,7 @@
         <x:v>2762</x:v>
       </x:c>
       <x:c r="I147" s="1">
-        <x:v>75000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="J147" s="1" t="s">
         <x:v>2587</x:v>
@@ -65602,7 +65602,7 @@
         <x:v>2681</x:v>
       </x:c>
       <x:c r="I150" s="1">
-        <x:v>75844</x:v>
+        <x:v>151688</x:v>
       </x:c>
       <x:c r="J150" s="1" t="s">
         <x:v>2587</x:v>
@@ -65742,7 +65742,7 @@
         <x:v>2673</x:v>
       </x:c>
       <x:c r="I154" s="1">
-        <x:v>75320</x:v>
+        <x:v>150604</x:v>
       </x:c>
       <x:c r="J154" s="1" t="s">
         <x:v>2587</x:v>
@@ -65812,7 +65812,7 @@
         <x:v>2590</x:v>
       </x:c>
       <x:c r="I156" s="1">
-        <x:v>74382</x:v>
+        <x:v>148764</x:v>
       </x:c>
       <x:c r="J156" s="1" t="s">
         <x:v>2587</x:v>
@@ -65917,7 +65917,7 @@
         <x:v>2613</x:v>
       </x:c>
       <x:c r="I159" s="1">
-        <x:v>75281</x:v>
+        <x:v>150562</x:v>
       </x:c>
       <x:c r="J159" s="1" t="s">
         <x:v>2587</x:v>
@@ -65987,7 +65987,7 @@
         <x:v>2673</x:v>
       </x:c>
       <x:c r="I161" s="1">
-        <x:v>74852</x:v>
+        <x:v>149704</x:v>
       </x:c>
       <x:c r="J161" s="1" t="s">
         <x:v>2587</x:v>
@@ -66127,7 +66127,7 @@
         <x:v>2613</x:v>
       </x:c>
       <x:c r="I165" s="1">
-        <x:v>75617</x:v>
+        <x:v>151234</x:v>
       </x:c>
       <x:c r="J165" s="1" t="s">
         <x:v>2587</x:v>
@@ -66547,7 +66547,7 @@
         <x:v>2684</x:v>
       </x:c>
       <x:c r="I177" s="1">
-        <x:v>75332</x:v>
+        <x:v>150664</x:v>
       </x:c>
       <x:c r="J177" s="1" t="s">
         <x:v>2587</x:v>
@@ -66757,7 +66757,7 @@
         <x:v>2664</x:v>
       </x:c>
       <x:c r="I183" s="1">
-        <x:v>73673</x:v>
+        <x:v>147346</x:v>
       </x:c>
       <x:c r="J183" s="1" t="s">
         <x:v>2587</x:v>
@@ -67861,7 +67861,7 @@
         <x:v>2629</x:v>
       </x:c>
       <x:c r="I17" s="1">
-        <x:v>75206</x:v>
+        <x:v>150412</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
         <x:v>2587</x:v>
@@ -67957,7 +67957,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>12894063</x:v>
+        <x:v>19706265</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
         <x:v>2618</x:v>
@@ -68309,7 +68309,7 @@
         <x:v>2607</x:v>
       </x:c>
       <x:c r="I31" s="1">
-        <x:v>75000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="J31" s="1" t="s">
         <x:v>2587</x:v>
@@ -68757,7 +68757,7 @@
         <x:v>2629</x:v>
       </x:c>
       <x:c r="I45" s="1">
-        <x:v>584942</x:v>
+        <x:v>659925</x:v>
       </x:c>
       <x:c r="J45" s="1" t="s">
         <x:v>2587</x:v>
@@ -68853,7 +68853,7 @@
         <x:v>2607</x:v>
       </x:c>
       <x:c r="I48" s="1">
-        <x:v>76342</x:v>
+        <x:v>152684</x:v>
       </x:c>
       <x:c r="J48" s="1" t="s">
         <x:v>2587</x:v>
@@ -68949,7 +68949,7 @@
         <x:v>2673</x:v>
       </x:c>
       <x:c r="I51" s="1">
-        <x:v>76113</x:v>
+        <x:v>152226</x:v>
       </x:c>
       <x:c r="J51" s="1" t="s">
         <x:v>2587</x:v>
@@ -68981,7 +68981,7 @@
         <x:v>2605</x:v>
       </x:c>
       <x:c r="I52" s="1">
-        <x:v>74753</x:v>
+        <x:v>149506</x:v>
       </x:c>
       <x:c r="J52" s="1" t="s">
         <x:v>2587</x:v>
@@ -69589,7 +69589,7 @@
         <x:v>2613</x:v>
       </x:c>
       <x:c r="I71" s="1">
-        <x:v>74932</x:v>
+        <x:v>149864</x:v>
       </x:c>
       <x:c r="J71" s="1" t="s">
         <x:v>2587</x:v>
@@ -69621,7 +69621,7 @@
         <x:v>2684</x:v>
       </x:c>
       <x:c r="I72" s="1">
-        <x:v>75000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="J72" s="1" t="s">
         <x:v>2587</x:v>
@@ -69941,7 +69941,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I82" s="1">
-        <x:v>33778233</x:v>
+        <x:v>36054435</x:v>
       </x:c>
       <x:c r="J82" s="1" t="s">
         <x:v>2587</x:v>
@@ -70005,7 +70005,7 @@
         <x:v>2590</x:v>
       </x:c>
       <x:c r="I84" s="1">
-        <x:v>1383600</x:v>
+        <x:v>1458299</x:v>
       </x:c>
       <x:c r="J84" s="1" t="s">
         <x:v>2587</x:v>
@@ -70037,7 +70037,7 @@
         <x:v>2636</x:v>
       </x:c>
       <x:c r="I85" s="1">
-        <x:v>75227</x:v>
+        <x:v>150454</x:v>
       </x:c>
       <x:c r="J85" s="1" t="s">
         <x:v>2587</x:v>
@@ -70485,7 +70485,7 @@
         <x:v>2590</x:v>
       </x:c>
       <x:c r="I99" s="1">
-        <x:v>74602</x:v>
+        <x:v>149204</x:v>
       </x:c>
       <x:c r="J99" s="1" t="s">
         <x:v>2587</x:v>
@@ -70549,7 +70549,7 @@
         <x:v>2607</x:v>
       </x:c>
       <x:c r="I101" s="1">
-        <x:v>76114</x:v>
+        <x:v>152228</x:v>
       </x:c>
       <x:c r="J101" s="1" t="s">
         <x:v>2587</x:v>
@@ -70613,7 +70613,7 @@
         <x:v>2724</x:v>
       </x:c>
       <x:c r="I103" s="1">
-        <x:v>75226</x:v>
+        <x:v>150452</x:v>
       </x:c>
       <x:c r="J103" s="1" t="s">
         <x:v>2587</x:v>
@@ -71445,7 +71445,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I129" s="1">
-        <x:v>6723910</x:v>
+        <x:v>10825942</x:v>
       </x:c>
       <x:c r="J129" s="1" t="s">
         <x:v>2618</x:v>
@@ -71477,7 +71477,7 @@
         <x:v>2755</x:v>
       </x:c>
       <x:c r="I130" s="1">
-        <x:v>74692</x:v>
+        <x:v>149384</x:v>
       </x:c>
       <x:c r="J130" s="1" t="s">
         <x:v>2587</x:v>
@@ -71733,7 +71733,7 @@
         <x:v>2762</x:v>
       </x:c>
       <x:c r="I138" s="1">
-        <x:v>75000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="J138" s="1" t="s">
         <x:v>2587</x:v>
@@ -71829,7 +71829,7 @@
         <x:v>2681</x:v>
       </x:c>
       <x:c r="I141" s="1">
-        <x:v>75844</x:v>
+        <x:v>151688</x:v>
       </x:c>
       <x:c r="J141" s="1" t="s">
         <x:v>2587</x:v>
@@ -71957,7 +71957,7 @@
         <x:v>2673</x:v>
       </x:c>
       <x:c r="I145" s="1">
-        <x:v>75320</x:v>
+        <x:v>150604</x:v>
       </x:c>
       <x:c r="J145" s="1" t="s">
         <x:v>2587</x:v>
@@ -72021,7 +72021,7 @@
         <x:v>2590</x:v>
       </x:c>
       <x:c r="I147" s="1">
-        <x:v>74382</x:v>
+        <x:v>148764</x:v>
       </x:c>
       <x:c r="J147" s="1" t="s">
         <x:v>2587</x:v>
@@ -72117,7 +72117,7 @@
         <x:v>2613</x:v>
       </x:c>
       <x:c r="I150" s="1">
-        <x:v>75281</x:v>
+        <x:v>150562</x:v>
       </x:c>
       <x:c r="J150" s="1" t="s">
         <x:v>2587</x:v>
@@ -72181,7 +72181,7 @@
         <x:v>2673</x:v>
       </x:c>
       <x:c r="I152" s="1">
-        <x:v>74852</x:v>
+        <x:v>149704</x:v>
       </x:c>
       <x:c r="J152" s="1" t="s">
         <x:v>2587</x:v>
@@ -72309,7 +72309,7 @@
         <x:v>2613</x:v>
       </x:c>
       <x:c r="I156" s="1">
-        <x:v>75617</x:v>
+        <x:v>151234</x:v>
       </x:c>
       <x:c r="J156" s="1" t="s">
         <x:v>2587</x:v>
@@ -72661,7 +72661,7 @@
         <x:v>2684</x:v>
       </x:c>
       <x:c r="I167" s="1">
-        <x:v>182279</x:v>
+        <x:v>257611</x:v>
       </x:c>
       <x:c r="J167" s="1" t="s">
         <x:v>2587</x:v>
@@ -72789,7 +72789,7 @@
         <x:v>2664</x:v>
       </x:c>
       <x:c r="I171" s="1">
-        <x:v>73673</x:v>
+        <x:v>147346</x:v>
       </x:c>
       <x:c r="J171" s="1" t="s">
         <x:v>2587</x:v>
@@ -73406,7 +73406,7 @@
         <x:v>367</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>75206</x:v>
+        <x:v>150412</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>2587</x:v>
@@ -73428,7 +73428,7 @@
         <x:v>555</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>16401247</x:v>
+        <x:v>23213449</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>2618</x:v>
@@ -73538,7 +73538,7 @@
         <x:v>184</x:v>
       </x:c>
       <x:c r="B28" s="1">
-        <x:v>75000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>2587</x:v>
@@ -73692,7 +73692,7 @@
         <x:v>1822</x:v>
       </x:c>
       <x:c r="B42" s="1">
-        <x:v>584942</x:v>
+        <x:v>659925</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
         <x:v>2587</x:v>
@@ -73714,7 +73714,7 @@
         <x:v>640</x:v>
       </x:c>
       <x:c r="B44" s="1">
-        <x:v>194376</x:v>
+        <x:v>270718</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
         <x:v>2587</x:v>
@@ -73747,7 +73747,7 @@
         <x:v>2672</x:v>
       </x:c>
       <x:c r="B47" s="1">
-        <x:v>76113</x:v>
+        <x:v>152226</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
         <x:v>2587</x:v>
@@ -73758,7 +73758,7 @@
         <x:v>2675</x:v>
       </x:c>
       <x:c r="B48" s="1">
-        <x:v>74753</x:v>
+        <x:v>149506</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
         <x:v>2587</x:v>
@@ -73945,7 +73945,7 @@
         <x:v>1344</x:v>
       </x:c>
       <x:c r="B65" s="1">
-        <x:v>74932</x:v>
+        <x:v>149864</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
         <x:v>2587</x:v>
@@ -73956,7 +73956,7 @@
         <x:v>2701</x:v>
       </x:c>
       <x:c r="B66" s="1">
-        <x:v>75000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
         <x:v>2587</x:v>
@@ -74022,7 +74022,7 @@
         <x:v>936</x:v>
       </x:c>
       <x:c r="B72" s="1">
-        <x:v>36255606</x:v>
+        <x:v>38531808</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
         <x:v>2587</x:v>
@@ -74044,7 +74044,7 @@
         <x:v>263</x:v>
       </x:c>
       <x:c r="B74" s="1">
-        <x:v>1383600</x:v>
+        <x:v>1458299</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
         <x:v>2587</x:v>
@@ -74055,7 +74055,7 @@
         <x:v>1037</x:v>
       </x:c>
       <x:c r="B75" s="1">
-        <x:v>75227</x:v>
+        <x:v>150454</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
         <x:v>2587</x:v>
@@ -74209,7 +74209,7 @@
         <x:v>1205</x:v>
       </x:c>
       <x:c r="B89" s="1">
-        <x:v>74602</x:v>
+        <x:v>149204</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
         <x:v>2587</x:v>
@@ -74231,7 +74231,7 @@
         <x:v>758</x:v>
       </x:c>
       <x:c r="B91" s="1">
-        <x:v>76114</x:v>
+        <x:v>152228</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
         <x:v>2587</x:v>
@@ -74253,7 +74253,7 @@
         <x:v>1178</x:v>
       </x:c>
       <x:c r="B93" s="1">
-        <x:v>75226</x:v>
+        <x:v>150452</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
         <x:v>2587</x:v>
@@ -74517,7 +74517,7 @@
         <x:v>2753</x:v>
       </x:c>
       <x:c r="B117" s="1">
-        <x:v>6723910</x:v>
+        <x:v>10825942</x:v>
       </x:c>
       <x:c r="C117" s="1" t="s">
         <x:v>2618</x:v>
@@ -74528,7 +74528,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="B118" s="1">
-        <x:v>74692</x:v>
+        <x:v>149384</x:v>
       </x:c>
       <x:c r="C118" s="1" t="s">
         <x:v>2587</x:v>
@@ -74605,7 +74605,7 @@
         <x:v>2768</x:v>
       </x:c>
       <x:c r="B125" s="1">
-        <x:v>75000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="C125" s="1" t="s">
         <x:v>2587</x:v>
@@ -74638,7 +74638,7 @@
         <x:v>888</x:v>
       </x:c>
       <x:c r="B128" s="1">
-        <x:v>75844</x:v>
+        <x:v>151688</x:v>
       </x:c>
       <x:c r="C128" s="1" t="s">
         <x:v>2587</x:v>
@@ -74682,7 +74682,7 @@
         <x:v>493</x:v>
       </x:c>
       <x:c r="B132" s="1">
-        <x:v>75320</x:v>
+        <x:v>150604</x:v>
       </x:c>
       <x:c r="C132" s="1" t="s">
         <x:v>2587</x:v>
@@ -74704,7 +74704,7 @@
         <x:v>2775</x:v>
       </x:c>
       <x:c r="B134" s="1">
-        <x:v>74382</x:v>
+        <x:v>148764</x:v>
       </x:c>
       <x:c r="C134" s="1" t="s">
         <x:v>2587</x:v>
@@ -74737,7 +74737,7 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="B137" s="1">
-        <x:v>75281</x:v>
+        <x:v>150562</x:v>
       </x:c>
       <x:c r="C137" s="1" t="s">
         <x:v>2587</x:v>
@@ -74759,7 +74759,7 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B139" s="1">
-        <x:v>74852</x:v>
+        <x:v>149704</x:v>
       </x:c>
       <x:c r="C139" s="1" t="s">
         <x:v>2587</x:v>
@@ -74803,7 +74803,7 @@
         <x:v>966</x:v>
       </x:c>
       <x:c r="B143" s="1">
-        <x:v>75617</x:v>
+        <x:v>151234</x:v>
       </x:c>
       <x:c r="C143" s="1" t="s">
         <x:v>2587</x:v>
@@ -74913,7 +74913,7 @@
         <x:v>2793</x:v>
       </x:c>
       <x:c r="B153" s="1">
-        <x:v>182279</x:v>
+        <x:v>257611</x:v>
       </x:c>
       <x:c r="C153" s="1" t="s">
         <x:v>2587</x:v>
@@ -74957,7 +74957,7 @@
         <x:v>736</x:v>
       </x:c>
       <x:c r="B157" s="1">
-        <x:v>73673</x:v>
+        <x:v>147346</x:v>
       </x:c>
       <x:c r="C157" s="1" t="s">
         <x:v>2587</x:v>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -41382,10 +41382,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C361" s="1" t="s">
-        <x:v>1724</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="D361" s="1" t="s">
-        <x:v>1725</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="E361" s="1" t="s">
         <x:v>930</x:v>
@@ -41397,7 +41397,7 @@
         <x:v>2209</x:v>
       </x:c>
       <x:c r="H361" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="362" spans="1:8">
@@ -41408,10 +41408,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C362" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>1724</x:v>
       </x:c>
       <x:c r="D362" s="1" t="s">
-        <x:v>929</x:v>
+        <x:v>1725</x:v>
       </x:c>
       <x:c r="E362" s="1" t="s">
         <x:v>930</x:v>
@@ -41423,7 +41423,7 @@
         <x:v>2209</x:v>
       </x:c>
       <x:c r="H362" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="363" spans="1:8">
@@ -60492,7 +60492,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I4" s="1">
-        <x:v>145958</x:v>
+        <x:v>146187</x:v>
       </x:c>
       <x:c r="J4" s="1" t="s">
         <x:v>2587</x:v>
@@ -61052,7 +61052,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>3507184</x:v>
+        <x:v>4040310</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
         <x:v>2618</x:v>
@@ -63432,7 +63432,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I88" s="1">
-        <x:v>2477373</x:v>
+        <x:v>2974411</x:v>
       </x:c>
       <x:c r="J88" s="1" t="s">
         <x:v>2587</x:v>
@@ -65322,7 +65322,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I142" s="1">
-        <x:v>4075</x:v>
+        <x:v>40704</x:v>
       </x:c>
       <x:c r="J142" s="1" t="s">
         <x:v>2587</x:v>
@@ -66652,7 +66652,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I180" s="1">
-        <x:v>77424</x:v>
+        <x:v>114053</x:v>
       </x:c>
       <x:c r="J180" s="1" t="s">
         <x:v>2618</x:v>
@@ -67072,7 +67072,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I192" s="1">
-        <x:v>429577</x:v>
+        <x:v>433936</x:v>
       </x:c>
       <x:c r="J192" s="1" t="s">
         <x:v>2618</x:v>
@@ -67445,7 +67445,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I4" s="1">
-        <x:v>145958</x:v>
+        <x:v>146187</x:v>
       </x:c>
       <x:c r="J4" s="1" t="s">
         <x:v>2587</x:v>
@@ -67925,7 +67925,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I19" s="1">
-        <x:v>3507184</x:v>
+        <x:v>4040310</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
         <x:v>2618</x:v>
@@ -69909,7 +69909,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I81" s="1">
-        <x:v>2477373</x:v>
+        <x:v>2974411</x:v>
       </x:c>
       <x:c r="J81" s="1" t="s">
         <x:v>2587</x:v>
@@ -71573,7 +71573,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I133" s="1">
-        <x:v>4075</x:v>
+        <x:v>40704</x:v>
       </x:c>
       <x:c r="J133" s="1" t="s">
         <x:v>2587</x:v>
@@ -72725,7 +72725,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I169" s="1">
-        <x:v>77424</x:v>
+        <x:v>114053</x:v>
       </x:c>
       <x:c r="J169" s="1" t="s">
         <x:v>2618</x:v>
@@ -73013,7 +73013,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I178" s="1">
-        <x:v>429577</x:v>
+        <x:v>433936</x:v>
       </x:c>
       <x:c r="J178" s="1" t="s">
         <x:v>2618</x:v>
@@ -73274,7 +73274,7 @@
         <x:v>148</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>145958</x:v>
+        <x:v>146187</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>2587</x:v>
@@ -73428,7 +73428,7 @@
         <x:v>555</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>23213449</x:v>
+        <x:v>23746575</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>2618</x:v>
@@ -74022,7 +74022,7 @@
         <x:v>936</x:v>
       </x:c>
       <x:c r="B72" s="1">
-        <x:v>38531808</x:v>
+        <x:v>39028846</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
         <x:v>2587</x:v>
@@ -74550,7 +74550,7 @@
         <x:v>2759</x:v>
       </x:c>
       <x:c r="B120" s="1">
-        <x:v>2754075</x:v>
+        <x:v>2790704</x:v>
       </x:c>
       <x:c r="C120" s="1" t="s">
         <x:v>2587</x:v>
@@ -74935,7 +74935,7 @@
         <x:v>2795</x:v>
       </x:c>
       <x:c r="B155" s="1">
-        <x:v>77424</x:v>
+        <x:v>114053</x:v>
       </x:c>
       <x:c r="C155" s="1" t="s">
         <x:v>2618</x:v>
@@ -75012,7 +75012,7 @@
         <x:v>2803</x:v>
       </x:c>
       <x:c r="B162" s="1">
-        <x:v>429577</x:v>
+        <x:v>433936</x:v>
       </x:c>
       <x:c r="C162" s="1" t="s">
         <x:v>2618</x:v>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -37638,10 +37638,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="C217" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="D217" s="1" t="s">
-        <x:v>642</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="E217" s="1" t="s">
         <x:v>640</x:v>
@@ -37653,7 +37653,7 @@
         <x:v>2110</x:v>
       </x:c>
       <x:c r="H217" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="218" spans="1:8">
@@ -37664,10 +37664,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="C218" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="D218" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="E218" s="1" t="s">
         <x:v>640</x:v>
@@ -37679,7 +37679,7 @@
         <x:v>2110</x:v>
       </x:c>
       <x:c r="H218" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="219" spans="1:8">
@@ -60492,7 +60492,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I4" s="1">
-        <x:v>146187</x:v>
+        <x:v>146408</x:v>
       </x:c>
       <x:c r="J4" s="1" t="s">
         <x:v>2587</x:v>
@@ -67072,7 +67072,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I192" s="1">
-        <x:v>433936</x:v>
+        <x:v>438132</x:v>
       </x:c>
       <x:c r="J192" s="1" t="s">
         <x:v>2618</x:v>
@@ -67177,7 +67177,7 @@
         <x:v>2664</x:v>
       </x:c>
       <x:c r="I195" s="1">
-        <x:v>381352</x:v>
+        <x:v>432714</x:v>
       </x:c>
       <x:c r="J195" s="1" t="s">
         <x:v>2587</x:v>
@@ -67445,7 +67445,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I4" s="1">
-        <x:v>146187</x:v>
+        <x:v>146408</x:v>
       </x:c>
       <x:c r="J4" s="1" t="s">
         <x:v>2587</x:v>
@@ -73013,7 +73013,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I178" s="1">
-        <x:v>433936</x:v>
+        <x:v>438132</x:v>
       </x:c>
       <x:c r="J178" s="1" t="s">
         <x:v>2618</x:v>
@@ -73109,7 +73109,7 @@
         <x:v>2664</x:v>
       </x:c>
       <x:c r="I181" s="1">
-        <x:v>381352</x:v>
+        <x:v>432714</x:v>
       </x:c>
       <x:c r="J181" s="1" t="s">
         <x:v>2587</x:v>
@@ -73274,7 +73274,7 @@
         <x:v>148</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>146187</x:v>
+        <x:v>146408</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>2587</x:v>
@@ -75012,7 +75012,7 @@
         <x:v>2803</x:v>
       </x:c>
       <x:c r="B162" s="1">
-        <x:v>433936</x:v>
+        <x:v>438132</x:v>
       </x:c>
       <x:c r="C162" s="1" t="s">
         <x:v>2618</x:v>
@@ -75045,7 +75045,7 @@
         <x:v>2807</x:v>
       </x:c>
       <x:c r="B165" s="1">
-        <x:v>381352</x:v>
+        <x:v>432714</x:v>
       </x:c>
       <x:c r="C165" s="1" t="s">
         <x:v>2587</x:v>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -37638,10 +37638,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="C217" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="D217" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="E217" s="1" t="s">
         <x:v>640</x:v>
@@ -37653,7 +37653,7 @@
         <x:v>2110</x:v>
       </x:c>
       <x:c r="H217" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="218" spans="1:8">
@@ -37664,10 +37664,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="C218" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="D218" s="1" t="s">
-        <x:v>642</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="E218" s="1" t="s">
         <x:v>640</x:v>
@@ -37679,7 +37679,7 @@
         <x:v>2110</x:v>
       </x:c>
       <x:c r="H218" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="219" spans="1:8">
@@ -60492,7 +60492,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I4" s="1">
-        <x:v>146408</x:v>
+        <x:v>165925</x:v>
       </x:c>
       <x:c r="J4" s="1" t="s">
         <x:v>2587</x:v>
@@ -61052,7 +61052,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>4040310</x:v>
+        <x:v>4229538</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
         <x:v>2618</x:v>
@@ -63432,7 +63432,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I88" s="1">
-        <x:v>2974411</x:v>
+        <x:v>3020793</x:v>
       </x:c>
       <x:c r="J88" s="1" t="s">
         <x:v>2587</x:v>
@@ -65322,7 +65322,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I142" s="1">
-        <x:v>40704</x:v>
+        <x:v>165588</x:v>
       </x:c>
       <x:c r="J142" s="1" t="s">
         <x:v>2587</x:v>
@@ -66652,7 +66652,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I180" s="1">
-        <x:v>114053</x:v>
+        <x:v>392890</x:v>
       </x:c>
       <x:c r="J180" s="1" t="s">
         <x:v>2618</x:v>
@@ -67072,7 +67072,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I192" s="1">
-        <x:v>438132</x:v>
+        <x:v>474362</x:v>
       </x:c>
       <x:c r="J192" s="1" t="s">
         <x:v>2618</x:v>
@@ -67445,7 +67445,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I4" s="1">
-        <x:v>146408</x:v>
+        <x:v>165925</x:v>
       </x:c>
       <x:c r="J4" s="1" t="s">
         <x:v>2587</x:v>
@@ -67925,7 +67925,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I19" s="1">
-        <x:v>4040310</x:v>
+        <x:v>4229538</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
         <x:v>2618</x:v>
@@ -69909,7 +69909,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I81" s="1">
-        <x:v>2974411</x:v>
+        <x:v>3020793</x:v>
       </x:c>
       <x:c r="J81" s="1" t="s">
         <x:v>2587</x:v>
@@ -71573,7 +71573,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I133" s="1">
-        <x:v>40704</x:v>
+        <x:v>165588</x:v>
       </x:c>
       <x:c r="J133" s="1" t="s">
         <x:v>2587</x:v>
@@ -72725,7 +72725,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I169" s="1">
-        <x:v>114053</x:v>
+        <x:v>392890</x:v>
       </x:c>
       <x:c r="J169" s="1" t="s">
         <x:v>2618</x:v>
@@ -73013,7 +73013,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I178" s="1">
-        <x:v>438132</x:v>
+        <x:v>474362</x:v>
       </x:c>
       <x:c r="J178" s="1" t="s">
         <x:v>2618</x:v>
@@ -73274,7 +73274,7 @@
         <x:v>148</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>146408</x:v>
+        <x:v>165925</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>2587</x:v>
@@ -73428,7 +73428,7 @@
         <x:v>555</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>23746575</x:v>
+        <x:v>23935803</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>2618</x:v>
@@ -74022,7 +74022,7 @@
         <x:v>936</x:v>
       </x:c>
       <x:c r="B72" s="1">
-        <x:v>39028846</x:v>
+        <x:v>39075228</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
         <x:v>2587</x:v>
@@ -74550,7 +74550,7 @@
         <x:v>2759</x:v>
       </x:c>
       <x:c r="B120" s="1">
-        <x:v>2790704</x:v>
+        <x:v>2915588</x:v>
       </x:c>
       <x:c r="C120" s="1" t="s">
         <x:v>2587</x:v>
@@ -74935,7 +74935,7 @@
         <x:v>2795</x:v>
       </x:c>
       <x:c r="B155" s="1">
-        <x:v>114053</x:v>
+        <x:v>392890</x:v>
       </x:c>
       <x:c r="C155" s="1" t="s">
         <x:v>2618</x:v>
@@ -75012,7 +75012,7 @@
         <x:v>2803</x:v>
       </x:c>
       <x:c r="B162" s="1">
-        <x:v>438132</x:v>
+        <x:v>474362</x:v>
       </x:c>
       <x:c r="C162" s="1" t="s">
         <x:v>2618</x:v>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -37638,10 +37638,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="C217" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="D217" s="1" t="s">
-        <x:v>642</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="E217" s="1" t="s">
         <x:v>640</x:v>
@@ -37653,7 +37653,7 @@
         <x:v>2110</x:v>
       </x:c>
       <x:c r="H217" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="218" spans="1:8">
@@ -37664,10 +37664,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="C218" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="D218" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="E218" s="1" t="s">
         <x:v>640</x:v>
@@ -37679,7 +37679,7 @@
         <x:v>2110</x:v>
       </x:c>
       <x:c r="H218" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="219" spans="1:8">
@@ -41382,10 +41382,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C361" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>1724</x:v>
       </x:c>
       <x:c r="D361" s="1" t="s">
-        <x:v>929</x:v>
+        <x:v>1725</x:v>
       </x:c>
       <x:c r="E361" s="1" t="s">
         <x:v>930</x:v>
@@ -41397,7 +41397,7 @@
         <x:v>2209</x:v>
       </x:c>
       <x:c r="H361" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="362" spans="1:8">
@@ -41408,10 +41408,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C362" s="1" t="s">
-        <x:v>1724</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="D362" s="1" t="s">
-        <x:v>1725</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="E362" s="1" t="s">
         <x:v>930</x:v>
@@ -41423,7 +41423,7 @@
         <x:v>2209</x:v>
       </x:c>
       <x:c r="H362" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="363" spans="1:8">

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -41382,10 +41382,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C361" s="1" t="s">
-        <x:v>1724</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="D361" s="1" t="s">
-        <x:v>1725</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="E361" s="1" t="s">
         <x:v>930</x:v>
@@ -41397,7 +41397,7 @@
         <x:v>2209</x:v>
       </x:c>
       <x:c r="H361" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="362" spans="1:8">
@@ -41408,10 +41408,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C362" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>1724</x:v>
       </x:c>
       <x:c r="D362" s="1" t="s">
-        <x:v>929</x:v>
+        <x:v>1725</x:v>
       </x:c>
       <x:c r="E362" s="1" t="s">
         <x:v>930</x:v>
@@ -41423,7 +41423,7 @@
         <x:v>2209</x:v>
       </x:c>
       <x:c r="H362" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="363" spans="1:8">
@@ -67177,7 +67177,7 @@
         <x:v>2664</x:v>
       </x:c>
       <x:c r="I195" s="1">
-        <x:v>432714</x:v>
+        <x:v>484076</x:v>
       </x:c>
       <x:c r="J195" s="1" t="s">
         <x:v>2587</x:v>
@@ -73109,7 +73109,7 @@
         <x:v>2664</x:v>
       </x:c>
       <x:c r="I181" s="1">
-        <x:v>432714</x:v>
+        <x:v>484076</x:v>
       </x:c>
       <x:c r="J181" s="1" t="s">
         <x:v>2587</x:v>
@@ -75045,7 +75045,7 @@
         <x:v>2807</x:v>
       </x:c>
       <x:c r="B165" s="1">
-        <x:v>432714</x:v>
+        <x:v>484076</x:v>
       </x:c>
       <x:c r="C165" s="1" t="s">
         <x:v>2587</x:v>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -63397,7 +63397,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I87" s="1">
-        <x:v>36054435</x:v>
+        <x:v>36874167</x:v>
       </x:c>
       <x:c r="J87" s="1" t="s">
         <x:v>2587</x:v>
@@ -65182,7 +65182,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I138" s="1">
-        <x:v>10825942</x:v>
+        <x:v>13476278</x:v>
       </x:c>
       <x:c r="J138" s="1" t="s">
         <x:v>2618</x:v>
@@ -67177,7 +67177,7 @@
         <x:v>2664</x:v>
       </x:c>
       <x:c r="I195" s="1">
-        <x:v>484076</x:v>
+        <x:v>535438</x:v>
       </x:c>
       <x:c r="J195" s="1" t="s">
         <x:v>2587</x:v>
@@ -69941,7 +69941,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I82" s="1">
-        <x:v>36054435</x:v>
+        <x:v>36874167</x:v>
       </x:c>
       <x:c r="J82" s="1" t="s">
         <x:v>2587</x:v>
@@ -71445,7 +71445,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="I129" s="1">
-        <x:v>10825942</x:v>
+        <x:v>13476278</x:v>
       </x:c>
       <x:c r="J129" s="1" t="s">
         <x:v>2618</x:v>
@@ -73109,7 +73109,7 @@
         <x:v>2664</x:v>
       </x:c>
       <x:c r="I181" s="1">
-        <x:v>484076</x:v>
+        <x:v>535438</x:v>
       </x:c>
       <x:c r="J181" s="1" t="s">
         <x:v>2587</x:v>
@@ -74022,7 +74022,7 @@
         <x:v>936</x:v>
       </x:c>
       <x:c r="B72" s="1">
-        <x:v>39075228</x:v>
+        <x:v>39894960</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
         <x:v>2587</x:v>
@@ -74517,7 +74517,7 @@
         <x:v>2753</x:v>
       </x:c>
       <x:c r="B117" s="1">
-        <x:v>10825942</x:v>
+        <x:v>13476278</x:v>
       </x:c>
       <x:c r="C117" s="1" t="s">
         <x:v>2618</x:v>
@@ -75045,7 +75045,7 @@
         <x:v>2807</x:v>
       </x:c>
       <x:c r="B165" s="1">
-        <x:v>484076</x:v>
+        <x:v>535438</x:v>
       </x:c>
       <x:c r="C165" s="1" t="s">
         <x:v>2587</x:v>
